--- a/TestData/Testcase.xlsx
+++ b/TestData/Testcase.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khoa\sqa-testing-lab\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\source\repos\sqa-testing-lab\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE58FB3-2D60-4EFB-9BE2-E4A1E95789BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F53E536-D333-444C-985A-8A2A5B7C1163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{23F3E367-7927-4520-A748-866283E286BB}"/>
   </bookViews>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="839">
   <si>
     <t>Tên dự án:</t>
   </si>
@@ -3863,7 +3863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4053,229 +4053,301 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4317,76 +4389,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4768,7 +4771,7 @@
     <col min="11" max="11" width="15.6640625" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="10.21875" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="173"/>
+    <col min="14" max="14" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -4912,55 +4915,55 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="71"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="79"/>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="80" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="73"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="81"/>
     </row>
     <row r="9" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="94">
+      <c r="A9" s="99">
         <v>1</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="102" t="s">
+      <c r="C9" s="95" t="s">
         <v>193</v>
       </c>
-      <c r="D9" s="102" t="s">
+      <c r="D9" s="95" t="s">
         <v>196</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="95" t="s">
         <v>197</v>
       </c>
       <c r="F9" s="22">
@@ -4972,19 +4975,19 @@
       <c r="H9" s="21"/>
       <c r="I9" s="33"/>
       <c r="J9" s="23"/>
-      <c r="K9" s="174"/>
-      <c r="L9" s="168"/>
-      <c r="M9" s="168"/>
-      <c r="N9" s="172" t="s">
+      <c r="K9" s="68"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="70" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="85"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
       <c r="F10" s="24">
         <v>2</v>
       </c>
@@ -4996,17 +4999,17 @@
       </c>
       <c r="I10" s="34"/>
       <c r="J10" s="35"/>
-      <c r="K10" s="174"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="168"/>
-      <c r="N10" s="172"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="70"/>
     </row>
     <row r="11" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="86"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
       <c r="F11" s="26">
         <v>3</v>
       </c>
@@ -5018,25 +5021,25 @@
         <v>198</v>
       </c>
       <c r="J11" s="37"/>
-      <c r="K11" s="174"/>
-      <c r="L11" s="168"/>
-      <c r="M11" s="168"/>
-      <c r="N11" s="172"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="70"/>
     </row>
     <row r="12" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="82">
+      <c r="A12" s="74">
         <v>2</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="72" t="s">
         <v>776</v>
       </c>
       <c r="F12" s="24">
@@ -5048,19 +5051,17 @@
       <c r="H12" s="25"/>
       <c r="I12" s="34"/>
       <c r="J12" s="29"/>
-      <c r="K12" s="174"/>
-      <c r="L12" s="168"/>
-      <c r="M12" s="168"/>
-      <c r="N12" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K12" s="68"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="70"/>
     </row>
     <row r="13" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
+      <c r="A13" s="119"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
       <c r="F13" s="26">
         <v>2</v>
       </c>
@@ -5072,17 +5073,17 @@
       </c>
       <c r="I13" s="36"/>
       <c r="J13" s="37"/>
-      <c r="K13" s="174"/>
-      <c r="L13" s="168"/>
-      <c r="M13" s="168"/>
-      <c r="N13" s="172"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="70"/>
     </row>
     <row r="14" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="83"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="24">
         <v>3</v>
       </c>
@@ -5094,25 +5095,25 @@
         <v>201</v>
       </c>
       <c r="J14" s="35"/>
-      <c r="K14" s="174"/>
-      <c r="L14" s="168"/>
-      <c r="M14" s="168"/>
-      <c r="N14" s="172"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="70"/>
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="93">
+      <c r="A15" s="85">
         <v>3</v>
       </c>
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="87" t="s">
         <v>204</v>
       </c>
       <c r="F15" s="26">
@@ -5126,19 +5127,17 @@
       </c>
       <c r="I15" s="36"/>
       <c r="J15" s="37"/>
-      <c r="K15" s="174"/>
-      <c r="L15" s="168"/>
-      <c r="M15" s="168"/>
-      <c r="N15" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K15" s="68"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="70"/>
     </row>
     <row r="16" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="85"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
       <c r="F16" s="24">
         <v>2</v>
       </c>
@@ -5150,17 +5149,17 @@
       </c>
       <c r="I16" s="34"/>
       <c r="J16" s="35"/>
-      <c r="K16" s="174"/>
-      <c r="L16" s="168"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="172"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="70"/>
     </row>
     <row r="17" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="86"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="26">
         <v>3</v>
       </c>
@@ -5172,25 +5171,25 @@
         <v>205</v>
       </c>
       <c r="J17" s="37"/>
-      <c r="K17" s="174"/>
-      <c r="L17" s="168"/>
-      <c r="M17" s="168"/>
-      <c r="N17" s="172"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="70"/>
     </row>
     <row r="18" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="82">
+      <c r="A18" s="74">
         <v>4</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="68" t="s">
+      <c r="D18" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="68" t="s">
+      <c r="E18" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F18" s="24">
@@ -5204,19 +5203,17 @@
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="35"/>
-      <c r="K18" s="174"/>
-      <c r="L18" s="168"/>
-      <c r="M18" s="168"/>
-      <c r="N18" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K18" s="68"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="70"/>
     </row>
     <row r="19" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="83"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
+      <c r="A19" s="75"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="26">
         <v>2</v>
       </c>
@@ -5228,25 +5225,25 @@
         <v>208</v>
       </c>
       <c r="J19" s="37"/>
-      <c r="K19" s="174"/>
-      <c r="L19" s="168"/>
-      <c r="M19" s="168"/>
-      <c r="N19" s="172"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="70"/>
     </row>
     <row r="20" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="82">
+      <c r="A20" s="74">
         <v>5</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="72" t="s">
         <v>209</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="72" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F20" s="24">
@@ -5260,17 +5257,17 @@
       </c>
       <c r="I20" s="34"/>
       <c r="J20" s="35"/>
-      <c r="K20" s="174"/>
-      <c r="L20" s="168"/>
-      <c r="M20" s="168"/>
-      <c r="N20" s="172"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="70"/>
     </row>
     <row r="21" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="83"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="A21" s="75"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
       <c r="F21" s="26">
         <v>2</v>
       </c>
@@ -5282,27 +5279,25 @@
         <v>211</v>
       </c>
       <c r="J21" s="37"/>
-      <c r="K21" s="174"/>
-      <c r="L21" s="168"/>
-      <c r="M21" s="168"/>
-      <c r="N21" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K21" s="68"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="70"/>
     </row>
     <row r="22" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82">
+      <c r="A22" s="74">
         <v>6</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="72" t="s">
         <v>212</v>
       </c>
-      <c r="D22" s="68" t="s">
+      <c r="D22" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F22" s="24">
@@ -5316,17 +5311,17 @@
       </c>
       <c r="I22" s="34"/>
       <c r="J22" s="35"/>
-      <c r="K22" s="174"/>
-      <c r="L22" s="168"/>
-      <c r="M22" s="168"/>
-      <c r="N22" s="172"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="70"/>
     </row>
     <row r="23" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="83"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="26">
         <v>2</v>
       </c>
@@ -5338,25 +5333,25 @@
         <v>214</v>
       </c>
       <c r="J23" s="37"/>
-      <c r="K23" s="174"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="168"/>
-      <c r="N23" s="172"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="70"/>
     </row>
     <row r="24" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82">
+      <c r="A24" s="74">
         <v>7</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="72" t="s">
         <v>215</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F24" s="24">
@@ -5370,19 +5365,17 @@
       </c>
       <c r="I24" s="34"/>
       <c r="J24" s="35"/>
-      <c r="K24" s="174"/>
-      <c r="L24" s="168"/>
-      <c r="M24" s="168"/>
-      <c r="N24" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K24" s="68"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="70"/>
     </row>
     <row r="25" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
       <c r="F25" s="26">
         <v>2</v>
       </c>
@@ -5394,25 +5387,25 @@
         <v>216</v>
       </c>
       <c r="J25" s="37"/>
-      <c r="K25" s="174"/>
-      <c r="L25" s="168"/>
-      <c r="M25" s="168"/>
-      <c r="N25" s="172"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="70"/>
     </row>
     <row r="26" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="82">
+      <c r="A26" s="74">
         <v>8</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F26" s="24">
@@ -5426,19 +5419,17 @@
       </c>
       <c r="I26" s="34"/>
       <c r="J26" s="35"/>
-      <c r="K26" s="174"/>
-      <c r="L26" s="168"/>
-      <c r="M26" s="168"/>
-      <c r="N26" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K26" s="68"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="70"/>
     </row>
     <row r="27" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="83"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="26">
         <v>2</v>
       </c>
@@ -5450,25 +5441,25 @@
         <v>219</v>
       </c>
       <c r="J27" s="37"/>
-      <c r="K27" s="174"/>
-      <c r="L27" s="168"/>
-      <c r="M27" s="168"/>
-      <c r="N27" s="172"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="70"/>
     </row>
     <row r="28" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="82">
+      <c r="A28" s="74">
         <v>9</v>
       </c>
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="72" t="s">
         <v>221</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F28" s="24">
@@ -5482,19 +5473,17 @@
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="168"/>
-      <c r="M28" s="168"/>
-      <c r="N28" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K28" s="68"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="70"/>
     </row>
     <row r="29" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="83"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="A29" s="75"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
       <c r="F29" s="26">
         <v>2</v>
       </c>
@@ -5506,25 +5495,25 @@
         <v>222</v>
       </c>
       <c r="J29" s="37"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="168"/>
-      <c r="M29" s="168"/>
-      <c r="N29" s="172"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="70"/>
     </row>
     <row r="30" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="82">
+      <c r="A30" s="74">
         <v>10</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="72" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="E30" s="68" t="s">
+      <c r="E30" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F30" s="24">
@@ -5538,19 +5527,17 @@
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="35"/>
-      <c r="K30" s="174"/>
-      <c r="L30" s="168"/>
-      <c r="M30" s="168"/>
-      <c r="N30" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K30" s="68"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="70"/>
     </row>
     <row r="31" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="83"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="26">
         <v>2</v>
       </c>
@@ -5562,25 +5549,25 @@
         <v>225</v>
       </c>
       <c r="J31" s="37"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="168"/>
-      <c r="M31" s="168"/>
-      <c r="N31" s="172"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="70"/>
     </row>
     <row r="32" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="82">
+      <c r="A32" s="74">
         <v>11</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="B32" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="72" t="s">
         <v>227</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F32" s="24">
@@ -5592,19 +5579,17 @@
       <c r="H32" s="25"/>
       <c r="I32" s="34"/>
       <c r="J32" s="29"/>
-      <c r="K32" s="174"/>
-      <c r="L32" s="168"/>
-      <c r="M32" s="168"/>
-      <c r="N32" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K32" s="68"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="70"/>
     </row>
     <row r="33" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="83"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
       <c r="F33" s="26">
         <v>2</v>
       </c>
@@ -5616,25 +5601,25 @@
         <v>228</v>
       </c>
       <c r="J33" s="37"/>
-      <c r="K33" s="174"/>
-      <c r="L33" s="168"/>
-      <c r="M33" s="168"/>
-      <c r="N33" s="172"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="67"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="70"/>
     </row>
     <row r="34" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="82">
+      <c r="A34" s="74">
         <v>12</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="D34" s="68" t="s">
+      <c r="D34" s="72" t="s">
         <v>230</v>
       </c>
-      <c r="E34" s="68" t="s">
+      <c r="E34" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F34" s="24">
@@ -5648,19 +5633,17 @@
       </c>
       <c r="I34" s="34"/>
       <c r="J34" s="35"/>
-      <c r="K34" s="174"/>
-      <c r="L34" s="168"/>
-      <c r="M34" s="168"/>
-      <c r="N34" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K34" s="68"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="70"/>
     </row>
     <row r="35" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="83"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="26">
         <v>2</v>
       </c>
@@ -5672,25 +5655,25 @@
         <v>231</v>
       </c>
       <c r="J35" s="37"/>
-      <c r="K35" s="174"/>
-      <c r="L35" s="168"/>
-      <c r="M35" s="168"/>
-      <c r="N35" s="172"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="70"/>
     </row>
     <row r="36" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="82">
+      <c r="A36" s="74">
         <v>13</v>
       </c>
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="72" t="s">
         <v>232</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="72" t="s">
         <v>233</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F36" s="24">
@@ -5704,19 +5687,17 @@
       </c>
       <c r="I36" s="34"/>
       <c r="J36" s="35"/>
-      <c r="K36" s="174"/>
-      <c r="L36" s="168"/>
-      <c r="M36" s="168"/>
-      <c r="N36" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K36" s="68"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="70"/>
     </row>
     <row r="37" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="83"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="26">
         <v>2</v>
       </c>
@@ -5728,10 +5709,10 @@
         <v>234</v>
       </c>
       <c r="J37" s="37"/>
-      <c r="K37" s="174"/>
-      <c r="L37" s="168"/>
-      <c r="M37" s="168"/>
-      <c r="N37" s="172"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="70"/>
     </row>
     <row r="38" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="28">
@@ -5760,24 +5741,21 @@
         <v>237</v>
       </c>
       <c r="J38" s="35"/>
-      <c r="N38" s="173" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="39" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="93">
+      <c r="A39" s="85">
         <v>15</v>
       </c>
-      <c r="B39" s="65" t="s">
+      <c r="B39" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="87" t="s">
         <v>238</v>
       </c>
-      <c r="D39" s="65" t="s">
+      <c r="D39" s="87" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="65" t="s">
+      <c r="E39" s="87" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="26">
@@ -5791,19 +5769,17 @@
       </c>
       <c r="I39" s="36"/>
       <c r="J39" s="37"/>
-      <c r="K39" s="174"/>
-      <c r="L39" s="168"/>
-      <c r="M39" s="168"/>
-      <c r="N39" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K39" s="68"/>
+      <c r="L39" s="67"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="70"/>
     </row>
     <row r="40" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
+      <c r="A40" s="92"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
       <c r="F40" s="31">
         <v>2</v>
       </c>
@@ -5815,43 +5791,43 @@
         <v>240</v>
       </c>
       <c r="J40" s="57"/>
-      <c r="K40" s="174"/>
-      <c r="L40" s="168"/>
-      <c r="M40" s="168"/>
-      <c r="N40" s="172"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="70"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="169" t="s">
+      <c r="A41" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="170"/>
-      <c r="C41" s="170"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="170"/>
-      <c r="F41" s="170"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="170"/>
-      <c r="I41" s="170"/>
-      <c r="J41" s="170"/>
-      <c r="K41" s="170"/>
-      <c r="L41" s="170"/>
-      <c r="M41" s="170"/>
-      <c r="N41" s="171"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83"/>
+      <c r="N41" s="84"/>
     </row>
     <row r="42" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="84">
+      <c r="A42" s="148">
         <v>16</v>
       </c>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="147" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="147" t="s">
         <v>194</v>
       </c>
-      <c r="D42" s="87" t="s">
+      <c r="D42" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="87" t="s">
+      <c r="E42" s="147" t="s">
         <v>256</v>
       </c>
       <c r="F42" s="44">
@@ -5865,17 +5841,17 @@
       </c>
       <c r="I42" s="45"/>
       <c r="J42" s="46"/>
-      <c r="K42" s="176"/>
-      <c r="N42" s="175" t="s">
+      <c r="K42" s="71"/>
+      <c r="N42" s="69" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="85"/>
-      <c r="B43" s="66"/>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
       <c r="F43" s="24">
         <v>2</v>
       </c>
@@ -5887,15 +5863,15 @@
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="35"/>
-      <c r="K43" s="174"/>
-      <c r="N43" s="172"/>
+      <c r="K43" s="68"/>
+      <c r="N43" s="70"/>
     </row>
     <row r="44" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="86"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
       <c r="F44" s="26">
         <v>3</v>
       </c>
@@ -5907,23 +5883,23 @@
         <v>262</v>
       </c>
       <c r="J44" s="37"/>
-      <c r="K44" s="174"/>
-      <c r="N44" s="172"/>
+      <c r="K44" s="68"/>
+      <c r="N44" s="70"/>
     </row>
     <row r="45" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="82">
+      <c r="A45" s="74">
         <v>17</v>
       </c>
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="72" t="s">
         <v>263</v>
       </c>
-      <c r="D45" s="68" t="s">
+      <c r="D45" s="72" t="s">
         <v>264</v>
       </c>
-      <c r="E45" s="68" t="s">
+      <c r="E45" s="72" t="s">
         <v>256</v>
       </c>
       <c r="F45" s="24">
@@ -5937,17 +5913,15 @@
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="29"/>
-      <c r="K45" s="174"/>
-      <c r="N45" s="175" t="s">
-        <v>838</v>
-      </c>
+      <c r="K45" s="68"/>
+      <c r="N45" s="69"/>
     </row>
     <row r="46" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="88"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
+      <c r="A46" s="119"/>
+      <c r="B46" s="120"/>
+      <c r="C46" s="120"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="120"/>
       <c r="F46" s="26">
         <v>2</v>
       </c>
@@ -5959,15 +5933,15 @@
       </c>
       <c r="I46" s="36"/>
       <c r="J46" s="37"/>
-      <c r="K46" s="174"/>
-      <c r="N46" s="172"/>
+      <c r="K46" s="68"/>
+      <c r="N46" s="70"/>
     </row>
     <row r="47" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
-      <c r="B47" s="69"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
+      <c r="A47" s="75"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
       <c r="F47" s="24">
         <v>3</v>
       </c>
@@ -5979,23 +5953,23 @@
         <v>268</v>
       </c>
       <c r="J47" s="35"/>
-      <c r="K47" s="174"/>
-      <c r="N47" s="172"/>
+      <c r="K47" s="68"/>
+      <c r="N47" s="70"/>
     </row>
     <row r="48" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="93">
+      <c r="A48" s="85">
         <v>18</v>
       </c>
-      <c r="B48" s="65" t="s">
+      <c r="B48" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="C48" s="65" t="s">
+      <c r="C48" s="87" t="s">
         <v>269</v>
       </c>
-      <c r="D48" s="65" t="s">
+      <c r="D48" s="87" t="s">
         <v>270</v>
       </c>
-      <c r="E48" s="65" t="s">
+      <c r="E48" s="87" t="s">
         <v>271</v>
       </c>
       <c r="F48" s="26">
@@ -6009,17 +5983,15 @@
       </c>
       <c r="I48" s="36"/>
       <c r="J48" s="37"/>
-      <c r="K48" s="174"/>
-      <c r="N48" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K48" s="68"/>
+      <c r="N48" s="70"/>
     </row>
     <row r="49" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="86"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
       <c r="F49" s="24">
         <v>2</v>
       </c>
@@ -6031,8 +6003,8 @@
         <v>268</v>
       </c>
       <c r="J49" s="35"/>
-      <c r="K49" s="174"/>
-      <c r="N49" s="172"/>
+      <c r="K49" s="68"/>
+      <c r="N49" s="70"/>
     </row>
     <row r="50" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="30">
@@ -6063,9 +6035,6 @@
         <v>279</v>
       </c>
       <c r="J50" s="38"/>
-      <c r="N50" s="173" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="51" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="28">
@@ -6094,7 +6063,7 @@
         <v>284</v>
       </c>
       <c r="J51" s="35"/>
-      <c r="N51" s="173" t="s">
+      <c r="N51" s="65" t="s">
         <v>838</v>
       </c>
     </row>
@@ -6125,24 +6094,21 @@
         <v>289</v>
       </c>
       <c r="J52" s="38"/>
-      <c r="N52" s="173" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="53" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82">
+      <c r="A53" s="74">
         <v>22</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="D53" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="E53" s="68" t="s">
+      <c r="E53" s="72" t="s">
         <v>292</v>
       </c>
       <c r="F53" s="24">
@@ -6154,17 +6120,15 @@
       <c r="H53" s="25"/>
       <c r="I53" s="34"/>
       <c r="J53" s="35"/>
-      <c r="K53" s="174"/>
-      <c r="N53" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K53" s="68"/>
+      <c r="N53" s="70"/>
     </row>
     <row r="54" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
-      <c r="B54" s="69"/>
-      <c r="C54" s="69"/>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
+      <c r="A54" s="75"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
       <c r="F54" s="26">
         <v>2</v>
       </c>
@@ -6176,8 +6140,8 @@
         <v>295</v>
       </c>
       <c r="J54" s="37"/>
-      <c r="K54" s="174"/>
-      <c r="N54" s="172"/>
+      <c r="K54" s="68"/>
+      <c r="N54" s="70"/>
     </row>
     <row r="55" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="28">
@@ -6206,24 +6170,21 @@
         <v>300</v>
       </c>
       <c r="J55" s="29"/>
-      <c r="N55" s="173" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="56" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="93">
+      <c r="A56" s="85">
         <v>24</v>
       </c>
-      <c r="B56" s="65" t="s">
+      <c r="B56" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="65" t="s">
+      <c r="C56" s="87" t="s">
         <v>301</v>
       </c>
-      <c r="D56" s="65" t="s">
+      <c r="D56" s="87" t="s">
         <v>302</v>
       </c>
-      <c r="E56" s="65" t="s">
+      <c r="E56" s="87" t="s">
         <v>303</v>
       </c>
       <c r="F56" s="26">
@@ -6237,17 +6198,15 @@
       </c>
       <c r="I56" s="36"/>
       <c r="J56" s="37"/>
-      <c r="K56" s="174"/>
-      <c r="N56" s="172" t="s">
-        <v>838</v>
-      </c>
+      <c r="K56" s="68"/>
+      <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="86"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
       <c r="F57" s="24">
         <v>2</v>
       </c>
@@ -6259,8 +6218,8 @@
         <v>306</v>
       </c>
       <c r="J57" s="35"/>
-      <c r="K57" s="174"/>
-      <c r="N57" s="172"/>
+      <c r="K57" s="68"/>
+      <c r="N57" s="70"/>
     </row>
     <row r="58" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="39">
@@ -6289,42 +6248,39 @@
         <v>311</v>
       </c>
       <c r="J58" s="42"/>
-      <c r="N58" s="173" t="s">
-        <v>838</v>
-      </c>
     </row>
     <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="81" t="s">
+      <c r="A59" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="B59" s="81"/>
-      <c r="C59" s="81"/>
-      <c r="D59" s="81"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="81"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="81"/>
-      <c r="L59" s="81"/>
-      <c r="M59" s="81"/>
-      <c r="N59" s="81"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="66"/>
+      <c r="K59" s="66"/>
+      <c r="L59" s="66"/>
+      <c r="M59" s="66"/>
+      <c r="N59" s="66"/>
     </row>
     <row r="60" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="94">
+      <c r="A60" s="99">
         <v>26</v>
       </c>
-      <c r="B60" s="102" t="s">
+      <c r="B60" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="95" t="s">
         <v>312</v>
       </c>
-      <c r="D60" s="102" t="s">
+      <c r="D60" s="95" t="s">
         <v>313</v>
       </c>
-      <c r="E60" s="102" t="s">
+      <c r="E60" s="95" t="s">
         <v>314</v>
       </c>
       <c r="F60" s="22">
@@ -6336,13 +6292,16 @@
       <c r="H60" s="47"/>
       <c r="I60" s="33"/>
       <c r="J60" s="23"/>
+      <c r="N60" s="70" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="61" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="86"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
       <c r="F61" s="24">
         <v>2</v>
       </c>
@@ -6354,21 +6313,22 @@
         <v>317</v>
       </c>
       <c r="J61" s="35"/>
+      <c r="N61" s="70"/>
     </row>
     <row r="62" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="93">
+      <c r="A62" s="85">
         <v>27</v>
       </c>
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="87" t="s">
         <v>318</v>
       </c>
-      <c r="D62" s="65" t="s">
+      <c r="D62" s="87" t="s">
         <v>319</v>
       </c>
-      <c r="E62" s="65" t="s">
+      <c r="E62" s="87" t="s">
         <v>320</v>
       </c>
       <c r="F62" s="26">
@@ -6380,13 +6340,16 @@
       <c r="H62" s="49"/>
       <c r="I62" s="36"/>
       <c r="J62" s="37"/>
+      <c r="N62" s="70" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="86"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
       <c r="F63" s="24">
         <v>2</v>
       </c>
@@ -6398,21 +6361,22 @@
         <v>323</v>
       </c>
       <c r="J63" s="35"/>
+      <c r="N63" s="70"/>
     </row>
     <row r="64" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="93">
+      <c r="A64" s="85">
         <v>28</v>
       </c>
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="87" t="s">
         <v>324</v>
       </c>
-      <c r="D64" s="65" t="s">
+      <c r="D64" s="87" t="s">
         <v>325</v>
       </c>
-      <c r="E64" s="65" t="s">
+      <c r="E64" s="87" t="s">
         <v>326</v>
       </c>
       <c r="F64" s="26">
@@ -6426,13 +6390,16 @@
       </c>
       <c r="I64" s="36"/>
       <c r="J64" s="37"/>
-    </row>
-    <row r="65" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N64" s="70" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="67"/>
-      <c r="C65" s="67"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
+      <c r="D65" s="89"/>
+      <c r="E65" s="89"/>
       <c r="F65" s="24">
         <v>2</v>
       </c>
@@ -6444,8 +6411,9 @@
         <v>330</v>
       </c>
       <c r="J65" s="35"/>
-    </row>
-    <row r="66" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N65" s="70"/>
+    </row>
+    <row r="66" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="30">
         <v>29</v>
       </c>
@@ -6473,20 +6441,20 @@
       </c>
       <c r="J66" s="38"/>
     </row>
-    <row r="67" spans="1:10" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="82">
+    <row r="67" spans="1:14" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="74">
         <v>30</v>
       </c>
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="72" t="s">
         <v>334</v>
       </c>
-      <c r="D67" s="68" t="s">
+      <c r="D67" s="72" t="s">
         <v>335</v>
       </c>
-      <c r="E67" s="68" t="s">
+      <c r="E67" s="72" t="s">
         <v>336</v>
       </c>
       <c r="F67" s="24">
@@ -6499,12 +6467,12 @@
       <c r="I67" s="34"/>
       <c r="J67" s="35"/>
     </row>
-    <row r="68" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="83"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="69"/>
-      <c r="E68" s="69"/>
+    <row r="68" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="75"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
       <c r="F68" s="26">
         <v>2</v>
       </c>
@@ -6517,20 +6485,20 @@
       </c>
       <c r="J68" s="37"/>
     </row>
-    <row r="69" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82">
+    <row r="69" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="74">
         <v>31</v>
       </c>
-      <c r="B69" s="68" t="s">
+      <c r="B69" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="68" t="s">
+      <c r="C69" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="D69" s="68" t="s">
+      <c r="D69" s="72" t="s">
         <v>340</v>
       </c>
-      <c r="E69" s="68" t="s">
+      <c r="E69" s="72" t="s">
         <v>326</v>
       </c>
       <c r="F69" s="24">
@@ -6543,12 +6511,12 @@
       <c r="I69" s="34"/>
       <c r="J69" s="35"/>
     </row>
-    <row r="70" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
-      <c r="B70" s="69"/>
-      <c r="C70" s="69"/>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
+    <row r="70" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="75"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
       <c r="F70" s="26">
         <v>2</v>
       </c>
@@ -6561,7 +6529,7 @@
       </c>
       <c r="J70" s="37"/>
     </row>
-    <row r="71" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="28">
         <v>32</v>
       </c>
@@ -6589,7 +6557,7 @@
       </c>
       <c r="J71" s="35"/>
     </row>
-    <row r="72" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="39">
         <v>33</v>
       </c>
@@ -6616,35 +6584,42 @@
         <v>352</v>
       </c>
       <c r="J72" s="52"/>
-    </row>
-    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="81" t="s">
+      <c r="N72" s="65" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="177" t="s">
         <v>183</v>
       </c>
-      <c r="B73" s="81"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="81"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="81"/>
-      <c r="J73" s="81"/>
-    </row>
-    <row r="74" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="94">
+      <c r="B73" s="177"/>
+      <c r="C73" s="177"/>
+      <c r="D73" s="177"/>
+      <c r="E73" s="177"/>
+      <c r="F73" s="177"/>
+      <c r="G73" s="177"/>
+      <c r="H73" s="177"/>
+      <c r="I73" s="177"/>
+      <c r="J73" s="177"/>
+      <c r="K73" s="177"/>
+      <c r="L73" s="177"/>
+      <c r="M73" s="177"/>
+      <c r="N73" s="177"/>
+    </row>
+    <row r="74" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="99">
         <v>34</v>
       </c>
-      <c r="B74" s="102" t="s">
+      <c r="B74" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="102" t="s">
+      <c r="C74" s="95" t="s">
         <v>195</v>
       </c>
-      <c r="D74" s="102" t="s">
+      <c r="D74" s="95" t="s">
         <v>353</v>
       </c>
-      <c r="E74" s="102" t="s">
+      <c r="E74" s="95" t="s">
         <v>354</v>
       </c>
       <c r="F74" s="22">
@@ -6656,13 +6631,16 @@
       <c r="H74" s="47"/>
       <c r="I74" s="33"/>
       <c r="J74" s="23"/>
-    </row>
-    <row r="75" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="85"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="66"/>
+      <c r="N74" s="70" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="100"/>
+      <c r="B75" s="96"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
       <c r="F75" s="24">
         <v>2</v>
       </c>
@@ -6674,13 +6652,14 @@
       </c>
       <c r="I75" s="34"/>
       <c r="J75" s="35"/>
-    </row>
-    <row r="76" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85"/>
-      <c r="B76" s="66"/>
-      <c r="C76" s="66"/>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
+      <c r="N75" s="70"/>
+    </row>
+    <row r="76" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="100"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="96"/>
+      <c r="D76" s="96"/>
+      <c r="E76" s="96"/>
       <c r="F76" s="26">
         <v>3</v>
       </c>
@@ -6690,13 +6669,14 @@
       <c r="H76" s="49"/>
       <c r="I76" s="36"/>
       <c r="J76" s="37"/>
-    </row>
-    <row r="77" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N76" s="70"/>
+    </row>
+    <row r="77" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="86"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="67"/>
-      <c r="D77" s="67"/>
-      <c r="E77" s="67"/>
+      <c r="B77" s="89"/>
+      <c r="C77" s="89"/>
+      <c r="D77" s="89"/>
+      <c r="E77" s="89"/>
       <c r="F77" s="24">
         <v>4</v>
       </c>
@@ -6708,21 +6688,22 @@
         <v>360</v>
       </c>
       <c r="J77" s="35"/>
-    </row>
-    <row r="78" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="93">
+      <c r="N77" s="70"/>
+    </row>
+    <row r="78" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="85">
         <v>35</v>
       </c>
-      <c r="B78" s="65" t="s">
+      <c r="B78" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="C78" s="65" t="s">
+      <c r="C78" s="87" t="s">
         <v>361</v>
       </c>
-      <c r="D78" s="65" t="s">
+      <c r="D78" s="87" t="s">
         <v>362</v>
       </c>
-      <c r="E78" s="65" t="s">
+      <c r="E78" s="87" t="s">
         <v>354</v>
       </c>
       <c r="F78" s="26">
@@ -6734,13 +6715,16 @@
       <c r="H78" s="49"/>
       <c r="I78" s="36"/>
       <c r="J78" s="38"/>
-    </row>
-    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="66"/>
+      <c r="N78" s="70" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="100"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="96"/>
+      <c r="E79" s="96"/>
       <c r="F79" s="24">
         <v>2</v>
       </c>
@@ -6752,13 +6736,14 @@
       </c>
       <c r="I79" s="34"/>
       <c r="J79" s="35"/>
-    </row>
-    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
+      <c r="N79" s="70"/>
+    </row>
+    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="100"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="96"/>
+      <c r="E80" s="96"/>
       <c r="F80" s="26">
         <v>3</v>
       </c>
@@ -6768,13 +6753,14 @@
       <c r="H80" s="49"/>
       <c r="I80" s="36"/>
       <c r="J80" s="37"/>
-    </row>
-    <row r="81" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N80" s="70"/>
+    </row>
+    <row r="81" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="86"/>
-      <c r="B81" s="67"/>
-      <c r="C81" s="67"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
+      <c r="B81" s="89"/>
+      <c r="C81" s="89"/>
+      <c r="D81" s="89"/>
+      <c r="E81" s="89"/>
       <c r="F81" s="24">
         <v>4</v>
       </c>
@@ -6786,21 +6772,22 @@
         <v>366</v>
       </c>
       <c r="J81" s="35"/>
-    </row>
-    <row r="82" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="93">
+      <c r="N81" s="70"/>
+    </row>
+    <row r="82" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="85">
         <v>36</v>
       </c>
-      <c r="B82" s="65" t="s">
+      <c r="B82" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="C82" s="65" t="s">
+      <c r="C82" s="87" t="s">
         <v>367</v>
       </c>
-      <c r="D82" s="65" t="s">
+      <c r="D82" s="87" t="s">
         <v>368</v>
       </c>
-      <c r="E82" s="65" t="s">
+      <c r="E82" s="87" t="s">
         <v>369</v>
       </c>
       <c r="F82" s="26">
@@ -6815,12 +6802,12 @@
       <c r="I82" s="36"/>
       <c r="J82" s="37"/>
     </row>
-    <row r="83" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="86"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="89"/>
+      <c r="D83" s="89"/>
+      <c r="E83" s="89"/>
       <c r="F83" s="24">
         <v>2</v>
       </c>
@@ -6833,20 +6820,20 @@
       </c>
       <c r="J83" s="35"/>
     </row>
-    <row r="84" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93">
+    <row r="84" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="85">
         <v>37</v>
       </c>
-      <c r="B84" s="65" t="s">
+      <c r="B84" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="C84" s="65" t="s">
+      <c r="C84" s="87" t="s">
         <v>373</v>
       </c>
-      <c r="D84" s="65" t="s">
+      <c r="D84" s="87" t="s">
         <v>374</v>
       </c>
-      <c r="E84" s="65" t="s">
+      <c r="E84" s="87" t="s">
         <v>375</v>
       </c>
       <c r="F84" s="26">
@@ -6858,13 +6845,16 @@
       <c r="H84" s="49"/>
       <c r="I84" s="36"/>
       <c r="J84" s="38"/>
-    </row>
-    <row r="85" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N84" s="70" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="86"/>
-      <c r="B85" s="67"/>
-      <c r="C85" s="67"/>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
+      <c r="B85" s="89"/>
+      <c r="C85" s="89"/>
+      <c r="D85" s="89"/>
+      <c r="E85" s="89"/>
       <c r="F85" s="24">
         <v>2</v>
       </c>
@@ -6876,21 +6866,22 @@
         <v>377</v>
       </c>
       <c r="J85" s="35"/>
-    </row>
-    <row r="86" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="93">
+      <c r="N85" s="70"/>
+    </row>
+    <row r="86" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="85">
         <v>38</v>
       </c>
-      <c r="B86" s="65" t="s">
+      <c r="B86" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="C86" s="65" t="s">
+      <c r="C86" s="87" t="s">
         <v>378</v>
       </c>
-      <c r="D86" s="65" t="s">
+      <c r="D86" s="87" t="s">
         <v>379</v>
       </c>
-      <c r="E86" s="65" t="s">
+      <c r="E86" s="87" t="s">
         <v>380</v>
       </c>
       <c r="F86" s="26">
@@ -6905,12 +6896,12 @@
       <c r="I86" s="36"/>
       <c r="J86" s="37"/>
     </row>
-    <row r="87" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="86"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
+      <c r="B87" s="89"/>
+      <c r="C87" s="89"/>
+      <c r="D87" s="89"/>
+      <c r="E87" s="89"/>
       <c r="F87" s="24">
         <v>2</v>
       </c>
@@ -6923,7 +6914,7 @@
       </c>
       <c r="J87" s="35"/>
     </row>
-    <row r="88" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="30">
         <v>39</v>
       </c>
@@ -6951,20 +6942,20 @@
       </c>
       <c r="J88" s="38"/>
     </row>
-    <row r="89" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="82">
+    <row r="89" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="74">
         <v>40</v>
       </c>
-      <c r="B89" s="68" t="s">
+      <c r="B89" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="C89" s="68" t="s">
+      <c r="C89" s="72" t="s">
         <v>390</v>
       </c>
-      <c r="D89" s="68" t="s">
+      <c r="D89" s="72" t="s">
         <v>391</v>
       </c>
-      <c r="E89" s="68" t="s">
+      <c r="E89" s="72" t="s">
         <v>392</v>
       </c>
       <c r="F89" s="24">
@@ -6977,12 +6968,12 @@
       <c r="I89" s="34"/>
       <c r="J89" s="29"/>
     </row>
-    <row r="90" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="91"/>
-      <c r="B90" s="92"/>
-      <c r="C90" s="92"/>
-      <c r="D90" s="92"/>
-      <c r="E90" s="92"/>
+    <row r="90" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="105"/>
+      <c r="B90" s="101"/>
+      <c r="C90" s="101"/>
+      <c r="D90" s="101"/>
+      <c r="E90" s="101"/>
       <c r="F90" s="41">
         <v>2</v>
       </c>
@@ -6995,34 +6986,34 @@
       </c>
       <c r="J90" s="42"/>
     </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="90" t="s">
+    <row r="91" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="B91" s="90"/>
-      <c r="C91" s="90"/>
-      <c r="D91" s="90"/>
-      <c r="E91" s="90"/>
-      <c r="F91" s="90"/>
-      <c r="G91" s="90"/>
-      <c r="H91" s="90"/>
-      <c r="I91" s="90"/>
-      <c r="J91" s="90"/>
-    </row>
-    <row r="92" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="94">
+      <c r="B91" s="121"/>
+      <c r="C91" s="121"/>
+      <c r="D91" s="121"/>
+      <c r="E91" s="121"/>
+      <c r="F91" s="121"/>
+      <c r="G91" s="121"/>
+      <c r="H91" s="121"/>
+      <c r="I91" s="121"/>
+      <c r="J91" s="121"/>
+    </row>
+    <row r="92" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="99">
         <v>41</v>
       </c>
-      <c r="B92" s="95" t="s">
+      <c r="B92" s="106" t="s">
         <v>113</v>
       </c>
-      <c r="C92" s="102" t="s">
+      <c r="C92" s="95" t="s">
         <v>396</v>
       </c>
-      <c r="D92" s="102" t="s">
+      <c r="D92" s="95" t="s">
         <v>397</v>
       </c>
-      <c r="E92" s="102" t="s">
+      <c r="E92" s="95" t="s">
         <v>398</v>
       </c>
       <c r="F92" s="22">
@@ -7037,12 +7028,12 @@
       <c r="I92" s="33"/>
       <c r="J92" s="23"/>
     </row>
-    <row r="93" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="85"/>
-      <c r="B93" s="96"/>
-      <c r="C93" s="66"/>
-      <c r="D93" s="66"/>
-      <c r="E93" s="66"/>
+    <row r="93" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="100"/>
+      <c r="B93" s="142"/>
+      <c r="C93" s="96"/>
+      <c r="D93" s="96"/>
+      <c r="E93" s="96"/>
       <c r="F93" s="24">
         <v>2</v>
       </c>
@@ -7053,12 +7044,12 @@
       <c r="I93" s="34"/>
       <c r="J93" s="35"/>
     </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="86"/>
-      <c r="B94" s="97"/>
-      <c r="C94" s="67"/>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
+      <c r="B94" s="107"/>
+      <c r="C94" s="89"/>
+      <c r="D94" s="89"/>
+      <c r="E94" s="89"/>
       <c r="F94" s="26">
         <v>3</v>
       </c>
@@ -7071,20 +7062,20 @@
       </c>
       <c r="J94" s="37"/>
     </row>
-    <row r="95" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="82">
+    <row r="95" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="74">
         <v>42</v>
       </c>
-      <c r="B95" s="74" t="s">
+      <c r="B95" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="C95" s="68" t="s">
+      <c r="C95" s="72" t="s">
         <v>404</v>
       </c>
-      <c r="D95" s="68" t="s">
+      <c r="D95" s="72" t="s">
         <v>405</v>
       </c>
-      <c r="E95" s="68" t="s">
+      <c r="E95" s="72" t="s">
         <v>406</v>
       </c>
       <c r="F95" s="24">
@@ -7099,12 +7090,12 @@
       <c r="I95" s="34"/>
       <c r="J95" s="29"/>
     </row>
-    <row r="96" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="83"/>
-      <c r="B96" s="75"/>
-      <c r="C96" s="69"/>
-      <c r="D96" s="69"/>
-      <c r="E96" s="69"/>
+    <row r="96" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="75"/>
+      <c r="B96" s="98"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="73"/>
       <c r="F96" s="26">
         <v>2</v>
       </c>
@@ -7118,19 +7109,19 @@
       <c r="J96" s="37"/>
     </row>
     <row r="97" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="82">
+      <c r="A97" s="74">
         <v>43</v>
       </c>
-      <c r="B97" s="78" t="s">
+      <c r="B97" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="68" t="s">
+      <c r="C97" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="D97" s="68" t="s">
+      <c r="D97" s="72" t="s">
         <v>411</v>
       </c>
-      <c r="E97" s="68" t="s">
+      <c r="E97" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F97" s="24">
@@ -7146,11 +7137,11 @@
       <c r="J97" s="29"/>
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="83"/>
-      <c r="B98" s="79"/>
-      <c r="C98" s="69"/>
-      <c r="D98" s="69"/>
-      <c r="E98" s="69"/>
+      <c r="A98" s="75"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="73"/>
+      <c r="E98" s="73"/>
       <c r="F98" s="26">
         <v>2</v>
       </c>
@@ -7164,19 +7155,19 @@
       <c r="J98" s="37"/>
     </row>
     <row r="99" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="82">
+      <c r="A99" s="74">
         <v>44</v>
       </c>
-      <c r="B99" s="78" t="s">
+      <c r="B99" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C99" s="68" t="s">
+      <c r="C99" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="D99" s="68" t="s">
+      <c r="D99" s="72" t="s">
         <v>416</v>
       </c>
-      <c r="E99" s="68" t="s">
+      <c r="E99" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F99" s="24">
@@ -7192,11 +7183,11 @@
       <c r="J99" s="29"/>
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="83"/>
-      <c r="B100" s="79"/>
-      <c r="C100" s="69"/>
-      <c r="D100" s="69"/>
-      <c r="E100" s="69"/>
+      <c r="A100" s="75"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="73"/>
       <c r="F100" s="26">
         <v>2</v>
       </c>
@@ -7210,19 +7201,19 @@
       <c r="J100" s="37"/>
     </row>
     <row r="101" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="82">
+      <c r="A101" s="74">
         <v>45</v>
       </c>
-      <c r="B101" s="78" t="s">
+      <c r="B101" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C101" s="68" t="s">
+      <c r="C101" s="72" t="s">
         <v>420</v>
       </c>
-      <c r="D101" s="68" t="s">
+      <c r="D101" s="72" t="s">
         <v>421</v>
       </c>
-      <c r="E101" s="68" t="s">
+      <c r="E101" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F101" s="24">
@@ -7238,11 +7229,11 @@
       <c r="J101" s="35"/>
     </row>
     <row r="102" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="83"/>
-      <c r="B102" s="79"/>
-      <c r="C102" s="69"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="69"/>
+      <c r="A102" s="75"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
       <c r="F102" s="26">
         <v>2</v>
       </c>
@@ -7256,19 +7247,19 @@
       <c r="J102" s="37"/>
     </row>
     <row r="103" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="82">
+      <c r="A103" s="74">
         <v>46</v>
       </c>
-      <c r="B103" s="98" t="s">
+      <c r="B103" s="145" t="s">
         <v>125</v>
       </c>
-      <c r="C103" s="68" t="s">
+      <c r="C103" s="72" t="s">
         <v>425</v>
       </c>
-      <c r="D103" s="68" t="s">
+      <c r="D103" s="72" t="s">
         <v>426</v>
       </c>
-      <c r="E103" s="68" t="s">
+      <c r="E103" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F103" s="24">
@@ -7284,11 +7275,11 @@
       <c r="J103" s="35"/>
     </row>
     <row r="104" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="83"/>
-      <c r="B104" s="99"/>
-      <c r="C104" s="69"/>
-      <c r="D104" s="69"/>
-      <c r="E104" s="69"/>
+      <c r="A104" s="75"/>
+      <c r="B104" s="146"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="73"/>
       <c r="F104" s="26">
         <v>2</v>
       </c>
@@ -7302,19 +7293,19 @@
       <c r="J104" s="37"/>
     </row>
     <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="82">
+      <c r="A105" s="74">
         <v>47</v>
       </c>
-      <c r="B105" s="76" t="s">
+      <c r="B105" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C105" s="68" t="s">
+      <c r="C105" s="72" t="s">
         <v>430</v>
       </c>
-      <c r="D105" s="68" t="s">
+      <c r="D105" s="72" t="s">
         <v>431</v>
       </c>
-      <c r="E105" s="68" t="s">
+      <c r="E105" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F105" s="24">
@@ -7330,11 +7321,11 @@
       <c r="J105" s="35"/>
     </row>
     <row r="106" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="83"/>
-      <c r="B106" s="77"/>
-      <c r="C106" s="69"/>
-      <c r="D106" s="69"/>
-      <c r="E106" s="69"/>
+      <c r="A106" s="75"/>
+      <c r="B106" s="94"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="73"/>
+      <c r="E106" s="73"/>
       <c r="F106" s="26">
         <v>2</v>
       </c>
@@ -7348,19 +7339,19 @@
       <c r="J106" s="37"/>
     </row>
     <row r="107" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="82">
+      <c r="A107" s="74">
         <v>48</v>
       </c>
-      <c r="B107" s="76" t="s">
+      <c r="B107" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C107" s="68" t="s">
+      <c r="C107" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="D107" s="68" t="s">
+      <c r="D107" s="72" t="s">
         <v>436</v>
       </c>
-      <c r="E107" s="68" t="s">
+      <c r="E107" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F107" s="24">
@@ -7376,11 +7367,11 @@
       <c r="J107" s="35"/>
     </row>
     <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="83"/>
-      <c r="B108" s="77"/>
-      <c r="C108" s="69"/>
-      <c r="D108" s="69"/>
-      <c r="E108" s="69"/>
+      <c r="A108" s="75"/>
+      <c r="B108" s="94"/>
+      <c r="C108" s="73"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="73"/>
       <c r="F108" s="26">
         <v>2</v>
       </c>
@@ -7394,19 +7385,19 @@
       <c r="J108" s="37"/>
     </row>
     <row r="109" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="82">
+      <c r="A109" s="74">
         <v>49</v>
       </c>
-      <c r="B109" s="100" t="s">
+      <c r="B109" s="143" t="s">
         <v>122</v>
       </c>
-      <c r="C109" s="68" t="s">
+      <c r="C109" s="72" t="s">
         <v>440</v>
       </c>
-      <c r="D109" s="68" t="s">
+      <c r="D109" s="72" t="s">
         <v>441</v>
       </c>
-      <c r="E109" s="68" t="s">
+      <c r="E109" s="72" t="s">
         <v>442</v>
       </c>
       <c r="F109" s="24">
@@ -7422,11 +7413,11 @@
       <c r="J109" s="29"/>
     </row>
     <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="83"/>
-      <c r="B110" s="101"/>
-      <c r="C110" s="69"/>
-      <c r="D110" s="69"/>
-      <c r="E110" s="69"/>
+      <c r="A110" s="75"/>
+      <c r="B110" s="144"/>
+      <c r="C110" s="73"/>
+      <c r="D110" s="73"/>
+      <c r="E110" s="73"/>
       <c r="F110" s="26">
         <v>2</v>
       </c>
@@ -7440,19 +7431,19 @@
       <c r="J110" s="37"/>
     </row>
     <row r="111" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="82">
+      <c r="A111" s="74">
         <v>50</v>
       </c>
-      <c r="B111" s="100" t="s">
+      <c r="B111" s="143" t="s">
         <v>122</v>
       </c>
-      <c r="C111" s="68" t="s">
+      <c r="C111" s="72" t="s">
         <v>447</v>
       </c>
-      <c r="D111" s="68" t="s">
+      <c r="D111" s="72" t="s">
         <v>448</v>
       </c>
-      <c r="E111" s="68" t="s">
+      <c r="E111" s="72" t="s">
         <v>442</v>
       </c>
       <c r="F111" s="24">
@@ -7468,11 +7459,11 @@
       <c r="J111" s="29"/>
     </row>
     <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="83"/>
-      <c r="B112" s="101"/>
-      <c r="C112" s="69"/>
-      <c r="D112" s="69"/>
-      <c r="E112" s="69"/>
+      <c r="A112" s="75"/>
+      <c r="B112" s="144"/>
+      <c r="C112" s="73"/>
+      <c r="D112" s="73"/>
+      <c r="E112" s="73"/>
       <c r="F112" s="26">
         <v>2</v>
       </c>
@@ -7486,19 +7477,19 @@
       <c r="J112" s="37"/>
     </row>
     <row r="113" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="82">
+      <c r="A113" s="74">
         <v>51</v>
       </c>
-      <c r="B113" s="76" t="s">
+      <c r="B113" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C113" s="68" t="s">
+      <c r="C113" s="72" t="s">
         <v>450</v>
       </c>
-      <c r="D113" s="68" t="s">
+      <c r="D113" s="72" t="s">
         <v>451</v>
       </c>
-      <c r="E113" s="68" t="s">
+      <c r="E113" s="72" t="s">
         <v>452</v>
       </c>
       <c r="F113" s="24">
@@ -7514,11 +7505,11 @@
       <c r="J113" s="29"/>
     </row>
     <row r="114" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="83"/>
-      <c r="B114" s="77"/>
-      <c r="C114" s="69"/>
-      <c r="D114" s="69"/>
-      <c r="E114" s="69"/>
+      <c r="A114" s="75"/>
+      <c r="B114" s="94"/>
+      <c r="C114" s="73"/>
+      <c r="D114" s="73"/>
+      <c r="E114" s="73"/>
       <c r="F114" s="26">
         <v>2</v>
       </c>
@@ -7532,19 +7523,19 @@
       <c r="J114" s="37"/>
     </row>
     <row r="115" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="82">
+      <c r="A115" s="74">
         <v>52</v>
       </c>
-      <c r="B115" s="76" t="s">
+      <c r="B115" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C115" s="68" t="s">
+      <c r="C115" s="72" t="s">
         <v>456</v>
       </c>
-      <c r="D115" s="68" t="s">
+      <c r="D115" s="72" t="s">
         <v>457</v>
       </c>
-      <c r="E115" s="68" t="s">
+      <c r="E115" s="72" t="s">
         <v>458</v>
       </c>
       <c r="F115" s="24">
@@ -7558,11 +7549,11 @@
       <c r="J115" s="35"/>
     </row>
     <row r="116" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="83"/>
-      <c r="B116" s="77"/>
-      <c r="C116" s="69"/>
-      <c r="D116" s="69"/>
-      <c r="E116" s="69"/>
+      <c r="A116" s="75"/>
+      <c r="B116" s="94"/>
+      <c r="C116" s="73"/>
+      <c r="D116" s="73"/>
+      <c r="E116" s="73"/>
       <c r="F116" s="26">
         <v>2</v>
       </c>
@@ -7576,19 +7567,19 @@
       <c r="J116" s="37"/>
     </row>
     <row r="117" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="82">
+      <c r="A117" s="74">
         <v>53</v>
       </c>
-      <c r="B117" s="76" t="s">
+      <c r="B117" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C117" s="68" t="s">
+      <c r="C117" s="72" t="s">
         <v>462</v>
       </c>
-      <c r="D117" s="68" t="s">
+      <c r="D117" s="72" t="s">
         <v>463</v>
       </c>
-      <c r="E117" s="68" t="s">
+      <c r="E117" s="72" t="s">
         <v>458</v>
       </c>
       <c r="F117" s="24">
@@ -7602,11 +7593,11 @@
       <c r="J117" s="35"/>
     </row>
     <row r="118" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="83"/>
-      <c r="B118" s="77"/>
-      <c r="C118" s="69"/>
-      <c r="D118" s="69"/>
-      <c r="E118" s="69"/>
+      <c r="A118" s="75"/>
+      <c r="B118" s="94"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="73"/>
+      <c r="E118" s="73"/>
       <c r="F118" s="26">
         <v>2</v>
       </c>
@@ -7620,19 +7611,19 @@
       <c r="J118" s="37"/>
     </row>
     <row r="119" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="82">
+      <c r="A119" s="74">
         <v>54</v>
       </c>
-      <c r="B119" s="76" t="s">
+      <c r="B119" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C119" s="68" t="s">
+      <c r="C119" s="72" t="s">
         <v>466</v>
       </c>
-      <c r="D119" s="68" t="s">
+      <c r="D119" s="72" t="s">
         <v>467</v>
       </c>
-      <c r="E119" s="68" t="s">
+      <c r="E119" s="72" t="s">
         <v>468</v>
       </c>
       <c r="F119" s="24">
@@ -7646,11 +7637,11 @@
       <c r="J119" s="35"/>
     </row>
     <row r="120" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="83"/>
-      <c r="B120" s="77"/>
-      <c r="C120" s="69"/>
-      <c r="D120" s="69"/>
-      <c r="E120" s="69"/>
+      <c r="A120" s="75"/>
+      <c r="B120" s="94"/>
+      <c r="C120" s="73"/>
+      <c r="D120" s="73"/>
+      <c r="E120" s="73"/>
       <c r="F120" s="26">
         <v>2</v>
       </c>
@@ -7664,19 +7655,19 @@
       <c r="J120" s="37"/>
     </row>
     <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="82">
+      <c r="A121" s="74">
         <v>55</v>
       </c>
-      <c r="B121" s="78" t="s">
+      <c r="B121" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C121" s="68" t="s">
+      <c r="C121" s="72" t="s">
         <v>472</v>
       </c>
-      <c r="D121" s="68" t="s">
+      <c r="D121" s="72" t="s">
         <v>473</v>
       </c>
-      <c r="E121" s="68" t="s">
+      <c r="E121" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F121" s="24">
@@ -7692,11 +7683,11 @@
       <c r="J121" s="35"/>
     </row>
     <row r="122" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="83"/>
-      <c r="B122" s="79"/>
-      <c r="C122" s="69"/>
-      <c r="D122" s="69"/>
-      <c r="E122" s="69"/>
+      <c r="A122" s="75"/>
+      <c r="B122" s="77"/>
+      <c r="C122" s="73"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="73"/>
       <c r="F122" s="26">
         <v>2</v>
       </c>
@@ -7710,19 +7701,19 @@
       <c r="J122" s="37"/>
     </row>
     <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="82">
+      <c r="A123" s="74">
         <v>56</v>
       </c>
-      <c r="B123" s="76" t="s">
+      <c r="B123" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C123" s="68" t="s">
+      <c r="C123" s="72" t="s">
         <v>477</v>
       </c>
-      <c r="D123" s="68" t="s">
+      <c r="D123" s="72" t="s">
         <v>478</v>
       </c>
-      <c r="E123" s="68" t="s">
+      <c r="E123" s="72" t="s">
         <v>442</v>
       </c>
       <c r="F123" s="24">
@@ -7736,11 +7727,11 @@
       <c r="J123" s="29"/>
     </row>
     <row r="124" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="83"/>
-      <c r="B124" s="77"/>
-      <c r="C124" s="69"/>
-      <c r="D124" s="69"/>
-      <c r="E124" s="69"/>
+      <c r="A124" s="75"/>
+      <c r="B124" s="94"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
       <c r="F124" s="26">
         <v>2</v>
       </c>
@@ -7754,19 +7745,19 @@
       <c r="J124" s="37"/>
     </row>
     <row r="125" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="82">
+      <c r="A125" s="74">
         <v>57</v>
       </c>
-      <c r="B125" s="76" t="s">
+      <c r="B125" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C125" s="68" t="s">
+      <c r="C125" s="72" t="s">
         <v>482</v>
       </c>
-      <c r="D125" s="68" t="s">
+      <c r="D125" s="72" t="s">
         <v>483</v>
       </c>
-      <c r="E125" s="68" t="s">
+      <c r="E125" s="72" t="s">
         <v>484</v>
       </c>
       <c r="F125" s="24">
@@ -7780,11 +7771,11 @@
       <c r="J125" s="29"/>
     </row>
     <row r="126" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="83"/>
-      <c r="B126" s="77"/>
-      <c r="C126" s="69"/>
-      <c r="D126" s="69"/>
-      <c r="E126" s="69"/>
+      <c r="A126" s="75"/>
+      <c r="B126" s="94"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="73"/>
+      <c r="E126" s="73"/>
       <c r="F126" s="26">
         <v>2</v>
       </c>
@@ -7798,19 +7789,19 @@
       <c r="J126" s="37"/>
     </row>
     <row r="127" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="82">
+      <c r="A127" s="74">
         <v>58</v>
       </c>
-      <c r="B127" s="76" t="s">
+      <c r="B127" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="68" t="s">
+      <c r="C127" s="72" t="s">
         <v>488</v>
       </c>
-      <c r="D127" s="68" t="s">
+      <c r="D127" s="72" t="s">
         <v>489</v>
       </c>
-      <c r="E127" s="68" t="s">
+      <c r="E127" s="72" t="s">
         <v>354</v>
       </c>
       <c r="F127" s="24">
@@ -7826,11 +7817,11 @@
       <c r="J127" s="29"/>
     </row>
     <row r="128" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="83"/>
-      <c r="B128" s="77"/>
-      <c r="C128" s="69"/>
-      <c r="D128" s="69"/>
-      <c r="E128" s="69"/>
+      <c r="A128" s="75"/>
+      <c r="B128" s="94"/>
+      <c r="C128" s="73"/>
+      <c r="D128" s="73"/>
+      <c r="E128" s="73"/>
       <c r="F128" s="26">
         <v>2</v>
       </c>
@@ -7872,19 +7863,19 @@
       <c r="J129" s="29"/>
     </row>
     <row r="130" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="93">
+      <c r="A130" s="85">
         <v>60</v>
       </c>
-      <c r="B130" s="114" t="s">
+      <c r="B130" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="65" t="s">
+      <c r="C130" s="87" t="s">
         <v>498</v>
       </c>
-      <c r="D130" s="65" t="s">
+      <c r="D130" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="E130" s="65" t="s">
+      <c r="E130" s="87" t="s">
         <v>500</v>
       </c>
       <c r="F130" s="26">
@@ -7900,11 +7891,11 @@
       <c r="J130" s="38"/>
     </row>
     <row r="131" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="113"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="80"/>
-      <c r="D131" s="80"/>
-      <c r="E131" s="80"/>
+      <c r="A131" s="92"/>
+      <c r="B131" s="91"/>
+      <c r="C131" s="88"/>
+      <c r="D131" s="88"/>
+      <c r="E131" s="88"/>
       <c r="F131" s="31">
         <v>2</v>
       </c>
@@ -7918,33 +7909,33 @@
       <c r="J131" s="57"/>
     </row>
     <row r="132" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="81" t="s">
+      <c r="A132" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="B132" s="81"/>
-      <c r="C132" s="81"/>
-      <c r="D132" s="81"/>
-      <c r="E132" s="81"/>
-      <c r="F132" s="81"/>
-      <c r="G132" s="81"/>
-      <c r="H132" s="81"/>
-      <c r="I132" s="81"/>
-      <c r="J132" s="81"/>
+      <c r="B132" s="66"/>
+      <c r="C132" s="66"/>
+      <c r="D132" s="66"/>
+      <c r="E132" s="66"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="66"/>
+      <c r="H132" s="66"/>
+      <c r="I132" s="66"/>
+      <c r="J132" s="66"/>
     </row>
     <row r="133" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="94">
+      <c r="A133" s="99">
         <v>61</v>
       </c>
-      <c r="B133" s="102" t="s">
+      <c r="B133" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="C133" s="102" t="s">
+      <c r="C133" s="95" t="s">
         <v>503</v>
       </c>
-      <c r="D133" s="102" t="s">
+      <c r="D133" s="95" t="s">
         <v>504</v>
       </c>
-      <c r="E133" s="95" t="s">
+      <c r="E133" s="106" t="s">
         <v>505</v>
       </c>
       <c r="F133" s="22">
@@ -7960,11 +7951,11 @@
       <c r="J133" s="23"/>
     </row>
     <row r="134" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="85"/>
-      <c r="B134" s="66"/>
-      <c r="C134" s="66"/>
-      <c r="D134" s="66"/>
-      <c r="E134" s="96"/>
+      <c r="A134" s="100"/>
+      <c r="B134" s="96"/>
+      <c r="C134" s="96"/>
+      <c r="D134" s="96"/>
+      <c r="E134" s="142"/>
       <c r="F134" s="24">
         <v>2</v>
       </c>
@@ -7979,10 +7970,10 @@
     </row>
     <row r="135" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="86"/>
-      <c r="B135" s="67"/>
-      <c r="C135" s="67"/>
-      <c r="D135" s="67"/>
-      <c r="E135" s="97"/>
+      <c r="B135" s="89"/>
+      <c r="C135" s="89"/>
+      <c r="D135" s="89"/>
+      <c r="E135" s="107"/>
       <c r="F135" s="26">
         <v>3</v>
       </c>
@@ -7996,19 +7987,19 @@
       <c r="J135" s="37"/>
     </row>
     <row r="136" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="82">
+      <c r="A136" s="74">
         <v>62</v>
       </c>
-      <c r="B136" s="68" t="s">
+      <c r="B136" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C136" s="68" t="s">
+      <c r="C136" s="72" t="s">
         <v>509</v>
       </c>
-      <c r="D136" s="68" t="s">
+      <c r="D136" s="72" t="s">
         <v>510</v>
       </c>
-      <c r="E136" s="74" t="s">
+      <c r="E136" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F136" s="24">
@@ -8024,11 +8015,11 @@
       <c r="J136" s="29"/>
     </row>
     <row r="137" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="83"/>
-      <c r="B137" s="69"/>
-      <c r="C137" s="69"/>
-      <c r="D137" s="69"/>
-      <c r="E137" s="75"/>
+      <c r="A137" s="75"/>
+      <c r="B137" s="73"/>
+      <c r="C137" s="73"/>
+      <c r="D137" s="73"/>
+      <c r="E137" s="98"/>
       <c r="F137" s="26">
         <v>2</v>
       </c>
@@ -8042,19 +8033,19 @@
       <c r="J137" s="37"/>
     </row>
     <row r="138" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="82">
+      <c r="A138" s="74">
         <v>63</v>
       </c>
-      <c r="B138" s="68" t="s">
+      <c r="B138" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C138" s="68" t="s">
+      <c r="C138" s="72" t="s">
         <v>515</v>
       </c>
-      <c r="D138" s="68" t="s">
+      <c r="D138" s="72" t="s">
         <v>516</v>
       </c>
-      <c r="E138" s="74" t="s">
+      <c r="E138" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F138" s="24">
@@ -8070,11 +8061,11 @@
       <c r="J138" s="35"/>
     </row>
     <row r="139" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="83"/>
-      <c r="B139" s="69"/>
-      <c r="C139" s="69"/>
-      <c r="D139" s="69"/>
-      <c r="E139" s="75"/>
+      <c r="A139" s="75"/>
+      <c r="B139" s="73"/>
+      <c r="C139" s="73"/>
+      <c r="D139" s="73"/>
+      <c r="E139" s="98"/>
       <c r="F139" s="26">
         <v>2</v>
       </c>
@@ -8088,19 +8079,19 @@
       <c r="J139" s="37"/>
     </row>
     <row r="140" spans="1:10" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="82">
+      <c r="A140" s="74">
         <v>64</v>
       </c>
-      <c r="B140" s="68" t="s">
+      <c r="B140" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C140" s="68" t="s">
+      <c r="C140" s="72" t="s">
         <v>518</v>
       </c>
-      <c r="D140" s="68" t="s">
+      <c r="D140" s="72" t="s">
         <v>519</v>
       </c>
-      <c r="E140" s="74" t="s">
+      <c r="E140" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F140" s="24">
@@ -8116,11 +8107,11 @@
       <c r="J140" s="35"/>
     </row>
     <row r="141" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="83"/>
-      <c r="B141" s="69"/>
-      <c r="C141" s="69"/>
-      <c r="D141" s="69"/>
-      <c r="E141" s="75"/>
+      <c r="A141" s="75"/>
+      <c r="B141" s="73"/>
+      <c r="C141" s="73"/>
+      <c r="D141" s="73"/>
+      <c r="E141" s="98"/>
       <c r="F141" s="26">
         <v>2</v>
       </c>
@@ -8134,19 +8125,19 @@
       <c r="J141" s="37"/>
     </row>
     <row r="142" spans="1:10" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="82">
+      <c r="A142" s="74">
         <v>65</v>
       </c>
-      <c r="B142" s="68" t="s">
+      <c r="B142" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C142" s="68" t="s">
+      <c r="C142" s="72" t="s">
         <v>521</v>
       </c>
-      <c r="D142" s="68" t="s">
+      <c r="D142" s="72" t="s">
         <v>522</v>
       </c>
-      <c r="E142" s="74" t="s">
+      <c r="E142" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F142" s="24">
@@ -8162,11 +8153,11 @@
       <c r="J142" s="35"/>
     </row>
     <row r="143" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="83"/>
-      <c r="B143" s="69"/>
-      <c r="C143" s="69"/>
-      <c r="D143" s="69"/>
-      <c r="E143" s="75"/>
+      <c r="A143" s="75"/>
+      <c r="B143" s="73"/>
+      <c r="C143" s="73"/>
+      <c r="D143" s="73"/>
+      <c r="E143" s="98"/>
       <c r="F143" s="26">
         <v>2</v>
       </c>
@@ -8180,19 +8171,19 @@
       <c r="J143" s="37"/>
     </row>
     <row r="144" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="82">
+      <c r="A144" s="74">
         <v>66</v>
       </c>
-      <c r="B144" s="68" t="s">
+      <c r="B144" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C144" s="68" t="s">
+      <c r="C144" s="72" t="s">
         <v>524</v>
       </c>
-      <c r="D144" s="68" t="s">
+      <c r="D144" s="72" t="s">
         <v>525</v>
       </c>
-      <c r="E144" s="74" t="s">
+      <c r="E144" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F144" s="24">
@@ -8208,11 +8199,11 @@
       <c r="J144" s="35"/>
     </row>
     <row r="145" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="83"/>
-      <c r="B145" s="69"/>
-      <c r="C145" s="69"/>
-      <c r="D145" s="69"/>
-      <c r="E145" s="75"/>
+      <c r="A145" s="75"/>
+      <c r="B145" s="73"/>
+      <c r="C145" s="73"/>
+      <c r="D145" s="73"/>
+      <c r="E145" s="98"/>
       <c r="F145" s="26">
         <v>2</v>
       </c>
@@ -8226,19 +8217,19 @@
       <c r="J145" s="37"/>
     </row>
     <row r="146" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="82">
+      <c r="A146" s="74">
         <v>67</v>
       </c>
-      <c r="B146" s="68" t="s">
+      <c r="B146" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C146" s="68" t="s">
+      <c r="C146" s="72" t="s">
         <v>527</v>
       </c>
-      <c r="D146" s="68" t="s">
+      <c r="D146" s="72" t="s">
         <v>528</v>
       </c>
-      <c r="E146" s="74" t="s">
+      <c r="E146" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F146" s="24">
@@ -8254,11 +8245,11 @@
       <c r="J146" s="35"/>
     </row>
     <row r="147" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="83"/>
-      <c r="B147" s="69"/>
-      <c r="C147" s="69"/>
-      <c r="D147" s="69"/>
-      <c r="E147" s="75"/>
+      <c r="A147" s="75"/>
+      <c r="B147" s="73"/>
+      <c r="C147" s="73"/>
+      <c r="D147" s="73"/>
+      <c r="E147" s="98"/>
       <c r="F147" s="26">
         <v>2</v>
       </c>
@@ -8272,19 +8263,19 @@
       <c r="J147" s="37"/>
     </row>
     <row r="148" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="82">
+      <c r="A148" s="74">
         <v>68</v>
       </c>
-      <c r="B148" s="68" t="s">
+      <c r="B148" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C148" s="68" t="s">
+      <c r="C148" s="72" t="s">
         <v>530</v>
       </c>
-      <c r="D148" s="68" t="s">
+      <c r="D148" s="72" t="s">
         <v>531</v>
       </c>
-      <c r="E148" s="74" t="s">
+      <c r="E148" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F148" s="24">
@@ -8299,12 +8290,12 @@
       <c r="I148" s="34"/>
       <c r="J148" s="35"/>
     </row>
-    <row r="149" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="83"/>
-      <c r="B149" s="69"/>
-      <c r="C149" s="69"/>
-      <c r="D149" s="69"/>
-      <c r="E149" s="75"/>
+    <row r="149" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="75"/>
+      <c r="B149" s="73"/>
+      <c r="C149" s="73"/>
+      <c r="D149" s="73"/>
+      <c r="E149" s="98"/>
       <c r="F149" s="26">
         <v>2</v>
       </c>
@@ -8318,19 +8309,19 @@
       <c r="J149" s="37"/>
     </row>
     <row r="150" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="82">
+      <c r="A150" s="74">
         <v>69</v>
       </c>
-      <c r="B150" s="68" t="s">
+      <c r="B150" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="C150" s="68" t="s">
+      <c r="C150" s="72" t="s">
         <v>533</v>
       </c>
-      <c r="D150" s="68" t="s">
+      <c r="D150" s="72" t="s">
         <v>534</v>
       </c>
-      <c r="E150" s="74" t="s">
+      <c r="E150" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F150" s="24">
@@ -8346,11 +8337,11 @@
       <c r="J150" s="35"/>
     </row>
     <row r="151" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="83"/>
-      <c r="B151" s="69"/>
-      <c r="C151" s="69"/>
-      <c r="D151" s="69"/>
-      <c r="E151" s="75"/>
+      <c r="A151" s="75"/>
+      <c r="B151" s="73"/>
+      <c r="C151" s="73"/>
+      <c r="D151" s="73"/>
+      <c r="E151" s="98"/>
       <c r="F151" s="26">
         <v>2</v>
       </c>
@@ -8364,19 +8355,19 @@
       <c r="J151" s="37"/>
     </row>
     <row r="152" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="82">
+      <c r="A152" s="74">
         <v>70</v>
       </c>
-      <c r="B152" s="68" t="s">
+      <c r="B152" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C152" s="68" t="s">
+      <c r="C152" s="72" t="s">
         <v>537</v>
       </c>
-      <c r="D152" s="68" t="s">
+      <c r="D152" s="72" t="s">
         <v>538</v>
       </c>
-      <c r="E152" s="74" t="s">
+      <c r="E152" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F152" s="24">
@@ -8392,11 +8383,11 @@
       <c r="J152" s="35"/>
     </row>
     <row r="153" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="83"/>
-      <c r="B153" s="69"/>
-      <c r="C153" s="69"/>
-      <c r="D153" s="69"/>
-      <c r="E153" s="75"/>
+      <c r="A153" s="75"/>
+      <c r="B153" s="73"/>
+      <c r="C153" s="73"/>
+      <c r="D153" s="73"/>
+      <c r="E153" s="98"/>
       <c r="F153" s="26">
         <v>2</v>
       </c>
@@ -8410,19 +8401,19 @@
       <c r="J153" s="37"/>
     </row>
     <row r="154" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="82">
+      <c r="A154" s="74">
         <v>71</v>
       </c>
-      <c r="B154" s="68" t="s">
+      <c r="B154" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="C154" s="68" t="s">
+      <c r="C154" s="72" t="s">
         <v>540</v>
       </c>
-      <c r="D154" s="68" t="s">
+      <c r="D154" s="72" t="s">
         <v>541</v>
       </c>
-      <c r="E154" s="74" t="s">
+      <c r="E154" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F154" s="24">
@@ -8438,11 +8429,11 @@
       <c r="J154" s="35"/>
     </row>
     <row r="155" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="83"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="69"/>
-      <c r="E155" s="75"/>
+      <c r="A155" s="75"/>
+      <c r="B155" s="73"/>
+      <c r="C155" s="73"/>
+      <c r="D155" s="73"/>
+      <c r="E155" s="98"/>
       <c r="F155" s="26">
         <v>2</v>
       </c>
@@ -8456,19 +8447,19 @@
       <c r="J155" s="37"/>
     </row>
     <row r="156" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="82">
+      <c r="A156" s="74">
         <v>72</v>
       </c>
-      <c r="B156" s="68" t="s">
+      <c r="B156" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C156" s="68" t="s">
+      <c r="C156" s="72" t="s">
         <v>543</v>
       </c>
-      <c r="D156" s="68" t="s">
+      <c r="D156" s="72" t="s">
         <v>544</v>
       </c>
-      <c r="E156" s="74" t="s">
+      <c r="E156" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F156" s="24">
@@ -8484,11 +8475,11 @@
       <c r="J156" s="35"/>
     </row>
     <row r="157" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="83"/>
-      <c r="B157" s="69"/>
-      <c r="C157" s="69"/>
-      <c r="D157" s="69"/>
-      <c r="E157" s="75"/>
+      <c r="A157" s="75"/>
+      <c r="B157" s="73"/>
+      <c r="C157" s="73"/>
+      <c r="D157" s="73"/>
+      <c r="E157" s="98"/>
       <c r="F157" s="26">
         <v>2</v>
       </c>
@@ -8502,19 +8493,19 @@
       <c r="J157" s="37"/>
     </row>
     <row r="158" spans="1:10" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="82">
+      <c r="A158" s="74">
         <v>73</v>
       </c>
-      <c r="B158" s="68" t="s">
+      <c r="B158" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="C158" s="68" t="s">
+      <c r="C158" s="72" t="s">
         <v>546</v>
       </c>
-      <c r="D158" s="68" t="s">
+      <c r="D158" s="72" t="s">
         <v>547</v>
       </c>
-      <c r="E158" s="74" t="s">
+      <c r="E158" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F158" s="24">
@@ -8530,11 +8521,11 @@
       <c r="J158" s="35"/>
     </row>
     <row r="159" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="83"/>
-      <c r="B159" s="69"/>
-      <c r="C159" s="69"/>
-      <c r="D159" s="69"/>
-      <c r="E159" s="75"/>
+      <c r="A159" s="75"/>
+      <c r="B159" s="73"/>
+      <c r="C159" s="73"/>
+      <c r="D159" s="73"/>
+      <c r="E159" s="98"/>
       <c r="F159" s="26">
         <v>2</v>
       </c>
@@ -8548,19 +8539,19 @@
       <c r="J159" s="37"/>
     </row>
     <row r="160" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="82">
+      <c r="A160" s="74">
         <v>74</v>
       </c>
-      <c r="B160" s="68" t="s">
+      <c r="B160" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="C160" s="68" t="s">
+      <c r="C160" s="72" t="s">
         <v>549</v>
       </c>
-      <c r="D160" s="68" t="s">
+      <c r="D160" s="72" t="s">
         <v>550</v>
       </c>
-      <c r="E160" s="74" t="s">
+      <c r="E160" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F160" s="24">
@@ -8576,11 +8567,11 @@
       <c r="J160" s="35"/>
     </row>
     <row r="161" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="83"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="69"/>
-      <c r="E161" s="75"/>
+      <c r="A161" s="75"/>
+      <c r="B161" s="73"/>
+      <c r="C161" s="73"/>
+      <c r="D161" s="73"/>
+      <c r="E161" s="98"/>
       <c r="F161" s="26">
         <v>2</v>
       </c>
@@ -8594,19 +8585,19 @@
       <c r="J161" s="37"/>
     </row>
     <row r="162" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="82">
+      <c r="A162" s="74">
         <v>75</v>
       </c>
-      <c r="B162" s="68" t="s">
+      <c r="B162" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="C162" s="68" t="s">
+      <c r="C162" s="72" t="s">
         <v>552</v>
       </c>
-      <c r="D162" s="68" t="s">
+      <c r="D162" s="72" t="s">
         <v>553</v>
       </c>
-      <c r="E162" s="74" t="s">
+      <c r="E162" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F162" s="24">
@@ -8622,11 +8613,11 @@
       <c r="J162" s="35"/>
     </row>
     <row r="163" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="83"/>
-      <c r="B163" s="69"/>
-      <c r="C163" s="69"/>
-      <c r="D163" s="69"/>
-      <c r="E163" s="75"/>
+      <c r="A163" s="75"/>
+      <c r="B163" s="73"/>
+      <c r="C163" s="73"/>
+      <c r="D163" s="73"/>
+      <c r="E163" s="98"/>
       <c r="F163" s="26">
         <v>2</v>
       </c>
@@ -8640,19 +8631,19 @@
       <c r="J163" s="37"/>
     </row>
     <row r="164" spans="1:10" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="82">
+      <c r="A164" s="74">
         <v>76</v>
       </c>
-      <c r="B164" s="68" t="s">
+      <c r="B164" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="C164" s="68" t="s">
+      <c r="C164" s="72" t="s">
         <v>554</v>
       </c>
-      <c r="D164" s="68" t="s">
+      <c r="D164" s="72" t="s">
         <v>555</v>
       </c>
-      <c r="E164" s="74" t="s">
+      <c r="E164" s="97" t="s">
         <v>511</v>
       </c>
       <c r="F164" s="24">
@@ -8668,11 +8659,11 @@
       <c r="J164" s="35"/>
     </row>
     <row r="165" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="91"/>
-      <c r="B165" s="92"/>
-      <c r="C165" s="92"/>
-      <c r="D165" s="92"/>
-      <c r="E165" s="139"/>
+      <c r="A165" s="105"/>
+      <c r="B165" s="101"/>
+      <c r="C165" s="101"/>
+      <c r="D165" s="101"/>
+      <c r="E165" s="104"/>
       <c r="F165" s="41">
         <v>2</v>
       </c>
@@ -8686,19 +8677,19 @@
       <c r="J165" s="42"/>
     </row>
     <row r="166" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="131">
+      <c r="A166" s="108">
         <v>77</v>
       </c>
-      <c r="B166" s="130" t="s">
+      <c r="B166" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="C166" s="106" t="s">
+      <c r="C166" s="135" t="s">
         <v>557</v>
       </c>
-      <c r="D166" s="106" t="s">
+      <c r="D166" s="135" t="s">
         <v>558</v>
       </c>
-      <c r="E166" s="107" t="s">
+      <c r="E166" s="136" t="s">
         <v>559</v>
       </c>
       <c r="F166" s="24">
@@ -8714,11 +8705,11 @@
       <c r="J166" s="29"/>
     </row>
     <row r="167" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="83"/>
-      <c r="B167" s="77"/>
-      <c r="C167" s="69"/>
-      <c r="D167" s="69"/>
-      <c r="E167" s="108"/>
+      <c r="A167" s="75"/>
+      <c r="B167" s="94"/>
+      <c r="C167" s="73"/>
+      <c r="D167" s="73"/>
+      <c r="E167" s="137"/>
       <c r="F167" s="26">
         <v>2</v>
       </c>
@@ -8732,19 +8723,19 @@
       <c r="J167" s="37"/>
     </row>
     <row r="168" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="82">
+      <c r="A168" s="74">
         <v>78</v>
       </c>
-      <c r="B168" s="103" t="s">
+      <c r="B168" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="C168" s="68" t="s">
+      <c r="C168" s="72" t="s">
         <v>562</v>
       </c>
-      <c r="D168" s="68" t="s">
+      <c r="D168" s="72" t="s">
         <v>563</v>
       </c>
-      <c r="E168" s="109" t="s">
+      <c r="E168" s="138" t="s">
         <v>564</v>
       </c>
       <c r="F168" s="24">
@@ -8758,11 +8749,11 @@
       <c r="J168" s="29"/>
     </row>
     <row r="169" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="83"/>
-      <c r="B169" s="104"/>
-      <c r="C169" s="69"/>
-      <c r="D169" s="69"/>
-      <c r="E169" s="110"/>
+      <c r="A169" s="75"/>
+      <c r="B169" s="111"/>
+      <c r="C169" s="73"/>
+      <c r="D169" s="73"/>
+      <c r="E169" s="139"/>
       <c r="F169" s="26">
         <v>2</v>
       </c>
@@ -8776,19 +8767,19 @@
       <c r="J169" s="37"/>
     </row>
     <row r="170" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="82">
+      <c r="A170" s="74">
         <v>79</v>
       </c>
-      <c r="B170" s="103" t="s">
+      <c r="B170" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="C170" s="68" t="s">
+      <c r="C170" s="72" t="s">
         <v>568</v>
       </c>
-      <c r="D170" s="68" t="s">
+      <c r="D170" s="72" t="s">
         <v>569</v>
       </c>
-      <c r="E170" s="135" t="s">
+      <c r="E170" s="140" t="s">
         <v>570</v>
       </c>
       <c r="F170" s="24">
@@ -8802,11 +8793,11 @@
       <c r="J170" s="35"/>
     </row>
     <row r="171" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="83"/>
-      <c r="B171" s="104"/>
-      <c r="C171" s="69"/>
-      <c r="D171" s="69"/>
-      <c r="E171" s="136"/>
+      <c r="A171" s="75"/>
+      <c r="B171" s="111"/>
+      <c r="C171" s="73"/>
+      <c r="D171" s="73"/>
+      <c r="E171" s="141"/>
       <c r="F171" s="26">
         <v>2</v>
       </c>
@@ -8820,19 +8811,19 @@
       <c r="J171" s="37"/>
     </row>
     <row r="172" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="82">
+      <c r="A172" s="74">
         <v>80</v>
       </c>
-      <c r="B172" s="76" t="s">
+      <c r="B172" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="C172" s="68" t="s">
+      <c r="C172" s="72" t="s">
         <v>573</v>
       </c>
-      <c r="D172" s="68" t="s">
+      <c r="D172" s="72" t="s">
         <v>574</v>
       </c>
-      <c r="E172" s="137" t="s">
+      <c r="E172" s="102" t="s">
         <v>511</v>
       </c>
       <c r="F172" s="24">
@@ -8848,11 +8839,11 @@
       <c r="J172" s="29"/>
     </row>
     <row r="173" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="91"/>
-      <c r="B173" s="105"/>
-      <c r="C173" s="92"/>
-      <c r="D173" s="92"/>
-      <c r="E173" s="138"/>
+      <c r="A173" s="105"/>
+      <c r="B173" s="118"/>
+      <c r="C173" s="101"/>
+      <c r="D173" s="101"/>
+      <c r="E173" s="103"/>
       <c r="F173" s="41">
         <v>2</v>
       </c>
@@ -8866,33 +8857,33 @@
       <c r="J173" s="42"/>
     </row>
     <row r="174" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="90" t="s">
+      <c r="A174" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="B174" s="90"/>
-      <c r="C174" s="90"/>
-      <c r="D174" s="90"/>
-      <c r="E174" s="90"/>
-      <c r="F174" s="90"/>
-      <c r="G174" s="90"/>
-      <c r="H174" s="90"/>
-      <c r="I174" s="90"/>
-      <c r="J174" s="90"/>
+      <c r="B174" s="121"/>
+      <c r="C174" s="121"/>
+      <c r="D174" s="121"/>
+      <c r="E174" s="121"/>
+      <c r="F174" s="121"/>
+      <c r="G174" s="121"/>
+      <c r="H174" s="121"/>
+      <c r="I174" s="121"/>
+      <c r="J174" s="121"/>
     </row>
     <row r="175" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="94">
+      <c r="A175" s="99">
         <v>81</v>
       </c>
-      <c r="B175" s="95" t="s">
+      <c r="B175" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="C175" s="102" t="s">
+      <c r="C175" s="95" t="s">
         <v>578</v>
       </c>
-      <c r="D175" s="102" t="s">
+      <c r="D175" s="95" t="s">
         <v>579</v>
       </c>
-      <c r="E175" s="102" t="s">
+      <c r="E175" s="95" t="s">
         <v>580</v>
       </c>
       <c r="F175" s="22">
@@ -8909,10 +8900,10 @@
     </row>
     <row r="176" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="86"/>
-      <c r="B176" s="97"/>
-      <c r="C176" s="67"/>
-      <c r="D176" s="67"/>
-      <c r="E176" s="67"/>
+      <c r="B176" s="107"/>
+      <c r="C176" s="89"/>
+      <c r="D176" s="89"/>
+      <c r="E176" s="89"/>
       <c r="F176" s="24">
         <v>2</v>
       </c>
@@ -8926,19 +8917,19 @@
       <c r="J176" s="35"/>
     </row>
     <row r="177" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="93">
+      <c r="A177" s="85">
         <v>82</v>
       </c>
-      <c r="B177" s="114" t="s">
+      <c r="B177" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C177" s="65" t="s">
+      <c r="C177" s="87" t="s">
         <v>585</v>
       </c>
-      <c r="D177" s="65" t="s">
+      <c r="D177" s="87" t="s">
         <v>586</v>
       </c>
-      <c r="E177" s="65" t="s">
+      <c r="E177" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F177" s="26">
@@ -8955,10 +8946,10 @@
     </row>
     <row r="178" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="86"/>
-      <c r="B178" s="97"/>
-      <c r="C178" s="67"/>
-      <c r="D178" s="67"/>
-      <c r="E178" s="67"/>
+      <c r="B178" s="107"/>
+      <c r="C178" s="89"/>
+      <c r="D178" s="89"/>
+      <c r="E178" s="89"/>
       <c r="F178" s="24">
         <v>2</v>
       </c>
@@ -8972,19 +8963,19 @@
       <c r="J178" s="35"/>
     </row>
     <row r="179" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="93">
+      <c r="A179" s="85">
         <v>83</v>
       </c>
-      <c r="B179" s="114" t="s">
+      <c r="B179" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C179" s="65" t="s">
+      <c r="C179" s="87" t="s">
         <v>592</v>
       </c>
-      <c r="D179" s="65" t="s">
+      <c r="D179" s="87" t="s">
         <v>593</v>
       </c>
-      <c r="E179" s="65" t="s">
+      <c r="E179" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F179" s="26">
@@ -9001,10 +8992,10 @@
     </row>
     <row r="180" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="86"/>
-      <c r="B180" s="97"/>
-      <c r="C180" s="67"/>
-      <c r="D180" s="67"/>
-      <c r="E180" s="67"/>
+      <c r="B180" s="107"/>
+      <c r="C180" s="89"/>
+      <c r="D180" s="89"/>
+      <c r="E180" s="89"/>
       <c r="F180" s="24">
         <v>2</v>
       </c>
@@ -9018,19 +9009,19 @@
       <c r="J180" s="35"/>
     </row>
     <row r="181" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="93">
+      <c r="A181" s="85">
         <v>84</v>
       </c>
-      <c r="B181" s="111" t="s">
+      <c r="B181" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="C181" s="65" t="s">
+      <c r="C181" s="87" t="s">
         <v>597</v>
       </c>
-      <c r="D181" s="65" t="s">
+      <c r="D181" s="87" t="s">
         <v>598</v>
       </c>
-      <c r="E181" s="65" t="s">
+      <c r="E181" s="87" t="s">
         <v>599</v>
       </c>
       <c r="F181" s="26">
@@ -9047,10 +9038,10 @@
     </row>
     <row r="182" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="86"/>
-      <c r="B182" s="112"/>
-      <c r="C182" s="67"/>
-      <c r="D182" s="67"/>
-      <c r="E182" s="67"/>
+      <c r="B182" s="113"/>
+      <c r="C182" s="89"/>
+      <c r="D182" s="89"/>
+      <c r="E182" s="89"/>
       <c r="F182" s="24">
         <v>2</v>
       </c>
@@ -9064,19 +9055,19 @@
       <c r="J182" s="35"/>
     </row>
     <row r="183" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="93">
+      <c r="A183" s="85">
         <v>85</v>
       </c>
-      <c r="B183" s="111" t="s">
+      <c r="B183" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="C183" s="65" t="s">
+      <c r="C183" s="87" t="s">
         <v>604</v>
       </c>
-      <c r="D183" s="65" t="s">
+      <c r="D183" s="87" t="s">
         <v>605</v>
       </c>
-      <c r="E183" s="65" t="s">
+      <c r="E183" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F183" s="26">
@@ -9093,10 +9084,10 @@
     </row>
     <row r="184" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="86"/>
-      <c r="B184" s="112"/>
-      <c r="C184" s="67"/>
-      <c r="D184" s="67"/>
-      <c r="E184" s="67"/>
+      <c r="B184" s="113"/>
+      <c r="C184" s="89"/>
+      <c r="D184" s="89"/>
+      <c r="E184" s="89"/>
       <c r="F184" s="24">
         <v>2</v>
       </c>
@@ -9110,19 +9101,19 @@
       <c r="J184" s="35"/>
     </row>
     <row r="185" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="93">
+      <c r="A185" s="85">
         <v>86</v>
       </c>
-      <c r="B185" s="111" t="s">
+      <c r="B185" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="C185" s="65" t="s">
+      <c r="C185" s="87" t="s">
         <v>609</v>
       </c>
-      <c r="D185" s="65" t="s">
+      <c r="D185" s="87" t="s">
         <v>610</v>
       </c>
-      <c r="E185" s="65" t="s">
+      <c r="E185" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F185" s="26">
@@ -9139,10 +9130,10 @@
     </row>
     <row r="186" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="86"/>
-      <c r="B186" s="112"/>
-      <c r="C186" s="67"/>
-      <c r="D186" s="67"/>
-      <c r="E186" s="67"/>
+      <c r="B186" s="113"/>
+      <c r="C186" s="89"/>
+      <c r="D186" s="89"/>
+      <c r="E186" s="89"/>
       <c r="F186" s="24">
         <v>2</v>
       </c>
@@ -9156,19 +9147,19 @@
       <c r="J186" s="35"/>
     </row>
     <row r="187" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="93">
+      <c r="A187" s="85">
         <v>87</v>
       </c>
-      <c r="B187" s="111" t="s">
+      <c r="B187" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="C187" s="65" t="s">
+      <c r="C187" s="87" t="s">
         <v>614</v>
       </c>
-      <c r="D187" s="65" t="s">
+      <c r="D187" s="87" t="s">
         <v>615</v>
       </c>
-      <c r="E187" s="65" t="s">
+      <c r="E187" s="87" t="s">
         <v>616</v>
       </c>
       <c r="F187" s="26">
@@ -9185,10 +9176,10 @@
     </row>
     <row r="188" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="86"/>
-      <c r="B188" s="112"/>
-      <c r="C188" s="67"/>
-      <c r="D188" s="67"/>
-      <c r="E188" s="67"/>
+      <c r="B188" s="113"/>
+      <c r="C188" s="89"/>
+      <c r="D188" s="89"/>
+      <c r="E188" s="89"/>
       <c r="F188" s="24">
         <v>2</v>
       </c>
@@ -9202,19 +9193,19 @@
       <c r="J188" s="35"/>
     </row>
     <row r="189" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="93">
+      <c r="A189" s="85">
         <v>88</v>
       </c>
-      <c r="B189" s="111" t="s">
+      <c r="B189" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="C189" s="65" t="s">
+      <c r="C189" s="87" t="s">
         <v>621</v>
       </c>
-      <c r="D189" s="65" t="s">
+      <c r="D189" s="87" t="s">
         <v>622</v>
       </c>
-      <c r="E189" s="65" t="s">
+      <c r="E189" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F189" s="26">
@@ -9231,10 +9222,10 @@
     </row>
     <row r="190" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="86"/>
-      <c r="B190" s="112"/>
-      <c r="C190" s="67"/>
-      <c r="D190" s="67"/>
-      <c r="E190" s="67"/>
+      <c r="B190" s="113"/>
+      <c r="C190" s="89"/>
+      <c r="D190" s="89"/>
+      <c r="E190" s="89"/>
       <c r="F190" s="24">
         <v>2</v>
       </c>
@@ -9248,19 +9239,19 @@
       <c r="J190" s="35"/>
     </row>
     <row r="191" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="93">
+      <c r="A191" s="85">
         <v>89</v>
       </c>
-      <c r="B191" s="115" t="s">
+      <c r="B191" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="C191" s="65" t="s">
+      <c r="C191" s="87" t="s">
         <v>626</v>
       </c>
-      <c r="D191" s="65" t="s">
+      <c r="D191" s="87" t="s">
         <v>627</v>
       </c>
-      <c r="E191" s="65" t="s">
+      <c r="E191" s="87" t="s">
         <v>628</v>
       </c>
       <c r="F191" s="26">
@@ -9277,10 +9268,10 @@
     </row>
     <row r="192" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="86"/>
-      <c r="B192" s="116"/>
-      <c r="C192" s="67"/>
-      <c r="D192" s="67"/>
-      <c r="E192" s="67"/>
+      <c r="B192" s="134"/>
+      <c r="C192" s="89"/>
+      <c r="D192" s="89"/>
+      <c r="E192" s="89"/>
       <c r="F192" s="24">
         <v>2</v>
       </c>
@@ -9294,19 +9285,19 @@
       <c r="J192" s="35"/>
     </row>
     <row r="193" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="93">
+      <c r="A193" s="85">
         <v>90</v>
       </c>
-      <c r="B193" s="115" t="s">
+      <c r="B193" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="C193" s="65" t="s">
+      <c r="C193" s="87" t="s">
         <v>633</v>
       </c>
-      <c r="D193" s="65" t="s">
+      <c r="D193" s="87" t="s">
         <v>634</v>
       </c>
-      <c r="E193" s="65" t="s">
+      <c r="E193" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F193" s="26">
@@ -9323,10 +9314,10 @@
     </row>
     <row r="194" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="86"/>
-      <c r="B194" s="116"/>
-      <c r="C194" s="67"/>
-      <c r="D194" s="67"/>
-      <c r="E194" s="67"/>
+      <c r="B194" s="134"/>
+      <c r="C194" s="89"/>
+      <c r="D194" s="89"/>
+      <c r="E194" s="89"/>
       <c r="F194" s="24">
         <v>2</v>
       </c>
@@ -9340,19 +9331,19 @@
       <c r="J194" s="35"/>
     </row>
     <row r="195" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="93">
+      <c r="A195" s="85">
         <v>91</v>
       </c>
-      <c r="B195" s="115" t="s">
+      <c r="B195" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="C195" s="65" t="s">
+      <c r="C195" s="87" t="s">
         <v>638</v>
       </c>
-      <c r="D195" s="65" t="s">
+      <c r="D195" s="87" t="s">
         <v>553</v>
       </c>
-      <c r="E195" s="65" t="s">
+      <c r="E195" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F195" s="26">
@@ -9369,10 +9360,10 @@
     </row>
     <row r="196" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="86"/>
-      <c r="B196" s="116"/>
-      <c r="C196" s="67"/>
-      <c r="D196" s="67"/>
-      <c r="E196" s="67"/>
+      <c r="B196" s="134"/>
+      <c r="C196" s="89"/>
+      <c r="D196" s="89"/>
+      <c r="E196" s="89"/>
       <c r="F196" s="24">
         <v>2</v>
       </c>
@@ -9386,19 +9377,19 @@
       <c r="J196" s="35"/>
     </row>
     <row r="197" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="93">
+      <c r="A197" s="85">
         <v>92</v>
       </c>
-      <c r="B197" s="114" t="s">
+      <c r="B197" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C197" s="65" t="s">
+      <c r="C197" s="87" t="s">
         <v>641</v>
       </c>
-      <c r="D197" s="65" t="s">
+      <c r="D197" s="87" t="s">
         <v>642</v>
       </c>
-      <c r="E197" s="65" t="s">
+      <c r="E197" s="87" t="s">
         <v>643</v>
       </c>
       <c r="F197" s="26">
@@ -9413,10 +9404,10 @@
     </row>
     <row r="198" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="86"/>
-      <c r="B198" s="97"/>
-      <c r="C198" s="67"/>
-      <c r="D198" s="67"/>
-      <c r="E198" s="67"/>
+      <c r="B198" s="107"/>
+      <c r="C198" s="89"/>
+      <c r="D198" s="89"/>
+      <c r="E198" s="89"/>
       <c r="F198" s="24">
         <v>2</v>
       </c>
@@ -9430,19 +9421,19 @@
       <c r="J198" s="35"/>
     </row>
     <row r="199" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="93">
+      <c r="A199" s="85">
         <v>93</v>
       </c>
-      <c r="B199" s="114" t="s">
+      <c r="B199" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C199" s="65" t="s">
+      <c r="C199" s="87" t="s">
         <v>647</v>
       </c>
-      <c r="D199" s="65" t="s">
+      <c r="D199" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="E199" s="65" t="s">
+      <c r="E199" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F199" s="26">
@@ -9457,10 +9448,10 @@
     </row>
     <row r="200" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="86"/>
-      <c r="B200" s="97"/>
-      <c r="C200" s="67"/>
-      <c r="D200" s="67"/>
-      <c r="E200" s="67"/>
+      <c r="B200" s="107"/>
+      <c r="C200" s="89"/>
+      <c r="D200" s="89"/>
+      <c r="E200" s="89"/>
       <c r="F200" s="24">
         <v>2</v>
       </c>
@@ -9474,19 +9465,19 @@
       <c r="J200" s="35"/>
     </row>
     <row r="201" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="93">
+      <c r="A201" s="85">
         <v>94</v>
       </c>
-      <c r="B201" s="114" t="s">
+      <c r="B201" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C201" s="65" t="s">
+      <c r="C201" s="87" t="s">
         <v>652</v>
       </c>
-      <c r="D201" s="65" t="s">
+      <c r="D201" s="87" t="s">
         <v>653</v>
       </c>
-      <c r="E201" s="65" t="s">
+      <c r="E201" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F201" s="26">
@@ -9503,10 +9494,10 @@
     </row>
     <row r="202" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="86"/>
-      <c r="B202" s="97"/>
-      <c r="C202" s="67"/>
-      <c r="D202" s="67"/>
-      <c r="E202" s="67"/>
+      <c r="B202" s="107"/>
+      <c r="C202" s="89"/>
+      <c r="D202" s="89"/>
+      <c r="E202" s="89"/>
       <c r="F202" s="24">
         <v>2</v>
       </c>
@@ -9520,19 +9511,19 @@
       <c r="J202" s="35"/>
     </row>
     <row r="203" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="93">
+      <c r="A203" s="85">
         <v>95</v>
       </c>
-      <c r="B203" s="114" t="s">
+      <c r="B203" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="C203" s="65" t="s">
+      <c r="C203" s="87" t="s">
         <v>658</v>
       </c>
-      <c r="D203" s="65" t="s">
+      <c r="D203" s="87" t="s">
         <v>659</v>
       </c>
-      <c r="E203" s="65" t="s">
+      <c r="E203" s="87" t="s">
         <v>587</v>
       </c>
       <c r="F203" s="26">
@@ -9548,11 +9539,11 @@
       <c r="J203" s="38"/>
     </row>
     <row r="204" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="113"/>
-      <c r="B204" s="134"/>
-      <c r="C204" s="80"/>
-      <c r="D204" s="80"/>
-      <c r="E204" s="80"/>
+      <c r="A204" s="92"/>
+      <c r="B204" s="91"/>
+      <c r="C204" s="88"/>
+      <c r="D204" s="88"/>
+      <c r="E204" s="88"/>
       <c r="F204" s="31">
         <v>2</v>
       </c>
@@ -9566,33 +9557,33 @@
       <c r="J204" s="57"/>
     </row>
     <row r="205" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="81" t="s">
+      <c r="A205" s="66" t="s">
         <v>187</v>
       </c>
-      <c r="B205" s="81"/>
-      <c r="C205" s="81"/>
-      <c r="D205" s="81"/>
-      <c r="E205" s="81"/>
-      <c r="F205" s="81"/>
-      <c r="G205" s="81"/>
-      <c r="H205" s="81"/>
-      <c r="I205" s="81"/>
-      <c r="J205" s="81"/>
+      <c r="B205" s="66"/>
+      <c r="C205" s="66"/>
+      <c r="D205" s="66"/>
+      <c r="E205" s="66"/>
+      <c r="F205" s="66"/>
+      <c r="G205" s="66"/>
+      <c r="H205" s="66"/>
+      <c r="I205" s="66"/>
+      <c r="J205" s="66"/>
     </row>
     <row r="206" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="94">
+      <c r="A206" s="99">
         <v>96</v>
       </c>
-      <c r="B206" s="95" t="s">
+      <c r="B206" s="106" t="s">
         <v>162</v>
       </c>
-      <c r="C206" s="102" t="s">
+      <c r="C206" s="95" t="s">
         <v>664</v>
       </c>
-      <c r="D206" s="102" t="s">
+      <c r="D206" s="95" t="s">
         <v>665</v>
       </c>
-      <c r="E206" s="132" t="s">
+      <c r="E206" s="116" t="s">
         <v>354</v>
       </c>
       <c r="F206" s="22">
@@ -9609,10 +9600,10 @@
     </row>
     <row r="207" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="86"/>
-      <c r="B207" s="97"/>
-      <c r="C207" s="67"/>
-      <c r="D207" s="67"/>
-      <c r="E207" s="133"/>
+      <c r="B207" s="107"/>
+      <c r="C207" s="89"/>
+      <c r="D207" s="89"/>
+      <c r="E207" s="117"/>
       <c r="F207" s="24">
         <v>2</v>
       </c>
@@ -9626,19 +9617,19 @@
       <c r="J207" s="35"/>
     </row>
     <row r="208" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="93">
+      <c r="A208" s="85">
         <v>97</v>
       </c>
-      <c r="B208" s="111" t="s">
+      <c r="B208" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C208" s="65" t="s">
+      <c r="C208" s="87" t="s">
         <v>668</v>
       </c>
-      <c r="D208" s="65" t="s">
+      <c r="D208" s="87" t="s">
         <v>669</v>
       </c>
-      <c r="E208" s="117" t="s">
+      <c r="E208" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F208" s="26">
@@ -9655,10 +9646,10 @@
     </row>
     <row r="209" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="86"/>
-      <c r="B209" s="112"/>
-      <c r="C209" s="67"/>
-      <c r="D209" s="67"/>
-      <c r="E209" s="118"/>
+      <c r="B209" s="113"/>
+      <c r="C209" s="89"/>
+      <c r="D209" s="89"/>
+      <c r="E209" s="115"/>
       <c r="F209" s="24">
         <v>2</v>
       </c>
@@ -9672,19 +9663,19 @@
       <c r="J209" s="35"/>
     </row>
     <row r="210" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="93">
+      <c r="A210" s="85">
         <v>98</v>
       </c>
-      <c r="B210" s="111" t="s">
+      <c r="B210" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C210" s="65" t="s">
+      <c r="C210" s="87" t="s">
         <v>673</v>
       </c>
-      <c r="D210" s="65" t="s">
+      <c r="D210" s="87" t="s">
         <v>674</v>
       </c>
-      <c r="E210" s="117" t="s">
+      <c r="E210" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F210" s="26">
@@ -9701,10 +9692,10 @@
     </row>
     <row r="211" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="86"/>
-      <c r="B211" s="112"/>
-      <c r="C211" s="67"/>
-      <c r="D211" s="67"/>
-      <c r="E211" s="118"/>
+      <c r="B211" s="113"/>
+      <c r="C211" s="89"/>
+      <c r="D211" s="89"/>
+      <c r="E211" s="115"/>
       <c r="F211" s="24">
         <v>2</v>
       </c>
@@ -9718,19 +9709,19 @@
       <c r="J211" s="35"/>
     </row>
     <row r="212" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="93">
+      <c r="A212" s="85">
         <v>99</v>
       </c>
-      <c r="B212" s="111" t="s">
+      <c r="B212" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C212" s="65" t="s">
+      <c r="C212" s="87" t="s">
         <v>677</v>
       </c>
-      <c r="D212" s="65" t="s">
+      <c r="D212" s="87" t="s">
         <v>678</v>
       </c>
-      <c r="E212" s="117" t="s">
+      <c r="E212" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F212" s="26">
@@ -9747,10 +9738,10 @@
     </row>
     <row r="213" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="86"/>
-      <c r="B213" s="112"/>
-      <c r="C213" s="67"/>
-      <c r="D213" s="67"/>
-      <c r="E213" s="118"/>
+      <c r="B213" s="113"/>
+      <c r="C213" s="89"/>
+      <c r="D213" s="89"/>
+      <c r="E213" s="115"/>
       <c r="F213" s="24">
         <v>2</v>
       </c>
@@ -9764,19 +9755,19 @@
       <c r="J213" s="35"/>
     </row>
     <row r="214" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="93">
+      <c r="A214" s="85">
         <v>100</v>
       </c>
-      <c r="B214" s="111" t="s">
+      <c r="B214" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C214" s="65" t="s">
+      <c r="C214" s="87" t="s">
         <v>680</v>
       </c>
-      <c r="D214" s="65" t="s">
+      <c r="D214" s="87" t="s">
         <v>681</v>
       </c>
-      <c r="E214" s="117" t="s">
+      <c r="E214" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F214" s="26">
@@ -9793,10 +9784,10 @@
     </row>
     <row r="215" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="86"/>
-      <c r="B215" s="112"/>
-      <c r="C215" s="67"/>
-      <c r="D215" s="67"/>
-      <c r="E215" s="118"/>
+      <c r="B215" s="113"/>
+      <c r="C215" s="89"/>
+      <c r="D215" s="89"/>
+      <c r="E215" s="115"/>
       <c r="F215" s="24">
         <v>2</v>
       </c>
@@ -9810,19 +9801,19 @@
       <c r="J215" s="35"/>
     </row>
     <row r="216" spans="1:10" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="93">
+      <c r="A216" s="85">
         <v>101</v>
       </c>
-      <c r="B216" s="111" t="s">
+      <c r="B216" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C216" s="65" t="s">
+      <c r="C216" s="87" t="s">
         <v>683</v>
       </c>
-      <c r="D216" s="65" t="s">
+      <c r="D216" s="87" t="s">
         <v>684</v>
       </c>
-      <c r="E216" s="117" t="s">
+      <c r="E216" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F216" s="26">
@@ -9839,10 +9830,10 @@
     </row>
     <row r="217" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="86"/>
-      <c r="B217" s="112"/>
-      <c r="C217" s="67"/>
-      <c r="D217" s="67"/>
-      <c r="E217" s="118"/>
+      <c r="B217" s="113"/>
+      <c r="C217" s="89"/>
+      <c r="D217" s="89"/>
+      <c r="E217" s="115"/>
       <c r="F217" s="24">
         <v>2</v>
       </c>
@@ -9856,19 +9847,19 @@
       <c r="J217" s="35"/>
     </row>
     <row r="218" spans="1:10" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="93">
+      <c r="A218" s="85">
         <v>102</v>
       </c>
-      <c r="B218" s="111" t="s">
+      <c r="B218" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="C218" s="65" t="s">
+      <c r="C218" s="87" t="s">
         <v>686</v>
       </c>
-      <c r="D218" s="65" t="s">
+      <c r="D218" s="87" t="s">
         <v>687</v>
       </c>
-      <c r="E218" s="117" t="s">
+      <c r="E218" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F218" s="26">
@@ -9885,10 +9876,10 @@
     </row>
     <row r="219" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="86"/>
-      <c r="B219" s="112"/>
-      <c r="C219" s="67"/>
-      <c r="D219" s="67"/>
-      <c r="E219" s="118"/>
+      <c r="B219" s="113"/>
+      <c r="C219" s="89"/>
+      <c r="D219" s="89"/>
+      <c r="E219" s="115"/>
       <c r="F219" s="24">
         <v>2</v>
       </c>
@@ -9902,19 +9893,19 @@
       <c r="J219" s="35"/>
     </row>
     <row r="220" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="93">
+      <c r="A220" s="85">
         <v>103</v>
       </c>
-      <c r="B220" s="114" t="s">
+      <c r="B220" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="C220" s="65" t="s">
+      <c r="C220" s="87" t="s">
         <v>690</v>
       </c>
-      <c r="D220" s="65" t="s">
+      <c r="D220" s="87" t="s">
         <v>691</v>
       </c>
-      <c r="E220" s="117" t="s">
+      <c r="E220" s="114" t="s">
         <v>670</v>
       </c>
       <c r="F220" s="26">
@@ -9929,10 +9920,10 @@
     </row>
     <row r="221" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="86"/>
-      <c r="B221" s="97"/>
-      <c r="C221" s="67"/>
-      <c r="D221" s="67"/>
-      <c r="E221" s="118"/>
+      <c r="B221" s="107"/>
+      <c r="C221" s="89"/>
+      <c r="D221" s="89"/>
+      <c r="E221" s="115"/>
       <c r="F221" s="24">
         <v>2</v>
       </c>
@@ -9946,19 +9937,19 @@
       <c r="J221" s="35"/>
     </row>
     <row r="222" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="93">
+      <c r="A222" s="85">
         <v>104</v>
       </c>
-      <c r="B222" s="115" t="s">
+      <c r="B222" s="124" t="s">
         <v>168</v>
       </c>
-      <c r="C222" s="65" t="s">
+      <c r="C222" s="87" t="s">
         <v>694</v>
       </c>
-      <c r="D222" s="65" t="s">
+      <c r="D222" s="87" t="s">
         <v>695</v>
       </c>
-      <c r="E222" s="123" t="s">
+      <c r="E222" s="127" t="s">
         <v>696</v>
       </c>
       <c r="F222" s="26">
@@ -9972,11 +9963,11 @@
       <c r="J222" s="38"/>
     </row>
     <row r="223" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="120"/>
-      <c r="B223" s="121"/>
-      <c r="C223" s="122"/>
-      <c r="D223" s="122"/>
-      <c r="E223" s="124"/>
+      <c r="A223" s="123"/>
+      <c r="B223" s="125"/>
+      <c r="C223" s="126"/>
+      <c r="D223" s="126"/>
+      <c r="E223" s="128"/>
       <c r="F223" s="24">
         <v>2</v>
       </c>
@@ -9990,19 +9981,19 @@
       <c r="J223" s="35"/>
     </row>
     <row r="224" spans="1:10" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="119">
+      <c r="A224" s="122">
         <v>105</v>
       </c>
-      <c r="B224" s="128" t="s">
+      <c r="B224" s="132" t="s">
         <v>165</v>
       </c>
-      <c r="C224" s="127" t="s">
+      <c r="C224" s="131" t="s">
         <v>700</v>
       </c>
-      <c r="D224" s="127" t="s">
+      <c r="D224" s="131" t="s">
         <v>701</v>
       </c>
-      <c r="E224" s="125" t="s">
+      <c r="E224" s="129" t="s">
         <v>670</v>
       </c>
       <c r="F224" s="59">
@@ -10018,11 +10009,11 @@
       <c r="J224" s="61"/>
     </row>
     <row r="225" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="113"/>
-      <c r="B225" s="129"/>
-      <c r="C225" s="80"/>
-      <c r="D225" s="80"/>
-      <c r="E225" s="126"/>
+      <c r="A225" s="92"/>
+      <c r="B225" s="133"/>
+      <c r="C225" s="88"/>
+      <c r="D225" s="88"/>
+      <c r="E225" s="130"/>
       <c r="F225" s="31">
         <v>2</v>
       </c>
@@ -10036,33 +10027,33 @@
       <c r="J225" s="57"/>
     </row>
     <row r="226" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="90" t="s">
+      <c r="A226" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="B226" s="90"/>
-      <c r="C226" s="90"/>
-      <c r="D226" s="90"/>
-      <c r="E226" s="90"/>
-      <c r="F226" s="90"/>
-      <c r="G226" s="90"/>
-      <c r="H226" s="90"/>
-      <c r="I226" s="90"/>
-      <c r="J226" s="90"/>
+      <c r="B226" s="121"/>
+      <c r="C226" s="121"/>
+      <c r="D226" s="121"/>
+      <c r="E226" s="121"/>
+      <c r="F226" s="121"/>
+      <c r="G226" s="121"/>
+      <c r="H226" s="121"/>
+      <c r="I226" s="121"/>
+      <c r="J226" s="121"/>
     </row>
     <row r="227" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="94">
+      <c r="A227" s="99">
         <v>106</v>
       </c>
-      <c r="B227" s="102" t="s">
+      <c r="B227" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="C227" s="102" t="s">
+      <c r="C227" s="95" t="s">
         <v>704</v>
       </c>
-      <c r="D227" s="102" t="s">
+      <c r="D227" s="95" t="s">
         <v>705</v>
       </c>
-      <c r="E227" s="102" t="s">
+      <c r="E227" s="95" t="s">
         <v>706</v>
       </c>
       <c r="F227" s="22">
@@ -10079,10 +10070,10 @@
     </row>
     <row r="228" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="86"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="67"/>
+      <c r="B228" s="89"/>
+      <c r="C228" s="89"/>
+      <c r="D228" s="89"/>
+      <c r="E228" s="89"/>
       <c r="F228" s="24">
         <v>2</v>
       </c>
@@ -10098,19 +10089,19 @@
       <c r="J228" s="35"/>
     </row>
     <row r="229" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="93">
+      <c r="A229" s="85">
         <v>107</v>
       </c>
-      <c r="B229" s="65" t="s">
+      <c r="B229" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="C229" s="65" t="s">
+      <c r="C229" s="87" t="s">
         <v>708</v>
       </c>
-      <c r="D229" s="65" t="s">
+      <c r="D229" s="87" t="s">
         <v>709</v>
       </c>
-      <c r="E229" s="65" t="s">
+      <c r="E229" s="87" t="s">
         <v>706</v>
       </c>
       <c r="F229" s="26">
@@ -10127,10 +10118,10 @@
     </row>
     <row r="230" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="86"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="67"/>
+      <c r="B230" s="89"/>
+      <c r="C230" s="89"/>
+      <c r="D230" s="89"/>
+      <c r="E230" s="89"/>
       <c r="F230" s="24">
         <v>2</v>
       </c>
@@ -10146,19 +10137,19 @@
       <c r="J230" s="35"/>
     </row>
     <row r="231" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="93">
+      <c r="A231" s="85">
         <v>108</v>
       </c>
-      <c r="B231" s="65" t="s">
+      <c r="B231" s="87" t="s">
         <v>174</v>
       </c>
-      <c r="C231" s="65" t="s">
+      <c r="C231" s="87" t="s">
         <v>712</v>
       </c>
-      <c r="D231" s="65" t="s">
+      <c r="D231" s="87" t="s">
         <v>713</v>
       </c>
-      <c r="E231" s="65" t="s">
+      <c r="E231" s="87" t="s">
         <v>714</v>
       </c>
       <c r="F231" s="26">
@@ -10175,10 +10166,10 @@
     </row>
     <row r="232" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="86"/>
-      <c r="B232" s="67"/>
-      <c r="C232" s="67"/>
-      <c r="D232" s="67"/>
-      <c r="E232" s="67"/>
+      <c r="B232" s="89"/>
+      <c r="C232" s="89"/>
+      <c r="D232" s="89"/>
+      <c r="E232" s="89"/>
       <c r="F232" s="24">
         <v>2</v>
       </c>
@@ -10194,19 +10185,19 @@
       <c r="J232" s="35"/>
     </row>
     <row r="233" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="93">
+      <c r="A233" s="85">
         <v>109</v>
       </c>
-      <c r="B233" s="65" t="s">
+      <c r="B233" s="87" t="s">
         <v>174</v>
       </c>
-      <c r="C233" s="65" t="s">
+      <c r="C233" s="87" t="s">
         <v>717</v>
       </c>
-      <c r="D233" s="65" t="s">
+      <c r="D233" s="87" t="s">
         <v>718</v>
       </c>
-      <c r="E233" s="65" t="s">
+      <c r="E233" s="87" t="s">
         <v>714</v>
       </c>
       <c r="F233" s="26">
@@ -10222,11 +10213,11 @@
       <c r="J233" s="37"/>
     </row>
     <row r="234" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="113"/>
-      <c r="B234" s="80"/>
-      <c r="C234" s="80"/>
-      <c r="D234" s="80"/>
-      <c r="E234" s="80"/>
+      <c r="A234" s="92"/>
+      <c r="B234" s="88"/>
+      <c r="C234" s="88"/>
+      <c r="D234" s="88"/>
+      <c r="E234" s="88"/>
       <c r="F234" s="31">
         <v>2</v>
       </c>
@@ -10242,19 +10233,19 @@
       <c r="J234" s="57"/>
     </row>
     <row r="235" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="131">
+      <c r="A235" s="108">
         <v>110</v>
       </c>
-      <c r="B235" s="130" t="s">
+      <c r="B235" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="C235" s="106" t="s">
+      <c r="C235" s="135" t="s">
         <v>721</v>
       </c>
-      <c r="D235" s="106" t="s">
+      <c r="D235" s="135" t="s">
         <v>722</v>
       </c>
-      <c r="E235" s="106" t="s">
+      <c r="E235" s="135" t="s">
         <v>714</v>
       </c>
       <c r="F235" s="24">
@@ -10270,11 +10261,11 @@
       <c r="J235" s="35"/>
     </row>
     <row r="236" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="83"/>
-      <c r="B236" s="77"/>
-      <c r="C236" s="69"/>
-      <c r="D236" s="69"/>
-      <c r="E236" s="69"/>
+      <c r="A236" s="75"/>
+      <c r="B236" s="94"/>
+      <c r="C236" s="73"/>
+      <c r="D236" s="73"/>
+      <c r="E236" s="73"/>
       <c r="F236" s="26">
         <v>2</v>
       </c>
@@ -10288,19 +10279,19 @@
       <c r="J236" s="37"/>
     </row>
     <row r="237" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="82">
+      <c r="A237" s="74">
         <v>111</v>
       </c>
-      <c r="B237" s="76" t="s">
+      <c r="B237" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C237" s="68" t="s">
+      <c r="C237" s="72" t="s">
         <v>725</v>
       </c>
-      <c r="D237" s="68" t="s">
+      <c r="D237" s="72" t="s">
         <v>726</v>
       </c>
-      <c r="E237" s="68" t="s">
+      <c r="E237" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F237" s="24">
@@ -10316,11 +10307,11 @@
       <c r="J237" s="35"/>
     </row>
     <row r="238" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="83"/>
-      <c r="B238" s="77"/>
-      <c r="C238" s="69"/>
-      <c r="D238" s="69"/>
-      <c r="E238" s="69"/>
+      <c r="A238" s="75"/>
+      <c r="B238" s="94"/>
+      <c r="C238" s="73"/>
+      <c r="D238" s="73"/>
+      <c r="E238" s="73"/>
       <c r="F238" s="26">
         <v>2</v>
       </c>
@@ -10334,19 +10325,19 @@
       <c r="J238" s="37"/>
     </row>
     <row r="239" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="82">
+      <c r="A239" s="74">
         <v>112</v>
       </c>
-      <c r="B239" s="76" t="s">
+      <c r="B239" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C239" s="68" t="s">
+      <c r="C239" s="72" t="s">
         <v>729</v>
       </c>
-      <c r="D239" s="68" t="s">
+      <c r="D239" s="72" t="s">
         <v>730</v>
       </c>
-      <c r="E239" s="68" t="s">
+      <c r="E239" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F239" s="24">
@@ -10362,11 +10353,11 @@
       <c r="J239" s="35"/>
     </row>
     <row r="240" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="83"/>
-      <c r="B240" s="77"/>
-      <c r="C240" s="69"/>
-      <c r="D240" s="69"/>
-      <c r="E240" s="69"/>
+      <c r="A240" s="75"/>
+      <c r="B240" s="94"/>
+      <c r="C240" s="73"/>
+      <c r="D240" s="73"/>
+      <c r="E240" s="73"/>
       <c r="F240" s="26">
         <v>2</v>
       </c>
@@ -10380,19 +10371,19 @@
       <c r="J240" s="37"/>
     </row>
     <row r="241" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="82">
+      <c r="A241" s="74">
         <v>113</v>
       </c>
-      <c r="B241" s="76" t="s">
+      <c r="B241" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C241" s="68" t="s">
+      <c r="C241" s="72" t="s">
         <v>734</v>
       </c>
-      <c r="D241" s="68" t="s">
+      <c r="D241" s="72" t="s">
         <v>735</v>
       </c>
-      <c r="E241" s="68" t="s">
+      <c r="E241" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F241" s="24">
@@ -10408,11 +10399,11 @@
       <c r="J241" s="35"/>
     </row>
     <row r="242" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="83"/>
-      <c r="B242" s="77"/>
-      <c r="C242" s="69"/>
-      <c r="D242" s="69"/>
-      <c r="E242" s="69"/>
+      <c r="A242" s="75"/>
+      <c r="B242" s="94"/>
+      <c r="C242" s="73"/>
+      <c r="D242" s="73"/>
+      <c r="E242" s="73"/>
       <c r="F242" s="26">
         <v>2</v>
       </c>
@@ -10426,19 +10417,19 @@
       <c r="J242" s="37"/>
     </row>
     <row r="243" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="82">
+      <c r="A243" s="74">
         <v>114</v>
       </c>
-      <c r="B243" s="76" t="s">
+      <c r="B243" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C243" s="68" t="s">
+      <c r="C243" s="72" t="s">
         <v>739</v>
       </c>
-      <c r="D243" s="68" t="s">
+      <c r="D243" s="72" t="s">
         <v>740</v>
       </c>
-      <c r="E243" s="68" t="s">
+      <c r="E243" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F243" s="24">
@@ -10454,11 +10445,11 @@
       <c r="J243" s="29"/>
     </row>
     <row r="244" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="83"/>
-      <c r="B244" s="77"/>
-      <c r="C244" s="69"/>
-      <c r="D244" s="69"/>
-      <c r="E244" s="69"/>
+      <c r="A244" s="75"/>
+      <c r="B244" s="94"/>
+      <c r="C244" s="73"/>
+      <c r="D244" s="73"/>
+      <c r="E244" s="73"/>
       <c r="F244" s="26">
         <v>2</v>
       </c>
@@ -10472,19 +10463,19 @@
       <c r="J244" s="37"/>
     </row>
     <row r="245" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="82">
+      <c r="A245" s="74">
         <v>115</v>
       </c>
-      <c r="B245" s="78" t="s">
+      <c r="B245" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="C245" s="68" t="s">
+      <c r="C245" s="72" t="s">
         <v>744</v>
       </c>
-      <c r="D245" s="68" t="s">
+      <c r="D245" s="72" t="s">
         <v>745</v>
       </c>
-      <c r="E245" s="68" t="s">
+      <c r="E245" s="72" t="s">
         <v>746</v>
       </c>
       <c r="F245" s="24">
@@ -10498,11 +10489,11 @@
       <c r="J245" s="35"/>
     </row>
     <row r="246" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="83"/>
-      <c r="B246" s="79"/>
-      <c r="C246" s="69"/>
-      <c r="D246" s="69"/>
-      <c r="E246" s="69"/>
+      <c r="A246" s="75"/>
+      <c r="B246" s="77"/>
+      <c r="C246" s="73"/>
+      <c r="D246" s="73"/>
+      <c r="E246" s="73"/>
       <c r="F246" s="26">
         <v>2</v>
       </c>
@@ -10516,19 +10507,19 @@
       <c r="J246" s="37"/>
     </row>
     <row r="247" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="82">
+      <c r="A247" s="74">
         <v>116</v>
       </c>
-      <c r="B247" s="78" t="s">
+      <c r="B247" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="C247" s="68" t="s">
+      <c r="C247" s="72" t="s">
         <v>750</v>
       </c>
-      <c r="D247" s="68" t="s">
+      <c r="D247" s="72" t="s">
         <v>751</v>
       </c>
-      <c r="E247" s="68" t="s">
+      <c r="E247" s="72" t="s">
         <v>406</v>
       </c>
       <c r="F247" s="24">
@@ -10544,11 +10535,11 @@
       <c r="J247" s="35"/>
     </row>
     <row r="248" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="83"/>
-      <c r="B248" s="79"/>
-      <c r="C248" s="69"/>
-      <c r="D248" s="69"/>
-      <c r="E248" s="69"/>
+      <c r="A248" s="75"/>
+      <c r="B248" s="77"/>
+      <c r="C248" s="73"/>
+      <c r="D248" s="73"/>
+      <c r="E248" s="73"/>
       <c r="F248" s="26">
         <v>2</v>
       </c>
@@ -10562,19 +10553,19 @@
       <c r="J248" s="37"/>
     </row>
     <row r="249" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="82">
+      <c r="A249" s="74">
         <v>117</v>
       </c>
-      <c r="B249" s="76" t="s">
+      <c r="B249" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C249" s="68" t="s">
+      <c r="C249" s="72" t="s">
         <v>755</v>
       </c>
-      <c r="D249" s="68" t="s">
+      <c r="D249" s="72" t="s">
         <v>756</v>
       </c>
-      <c r="E249" s="68" t="s">
+      <c r="E249" s="72" t="s">
         <v>757</v>
       </c>
       <c r="F249" s="24">
@@ -10588,11 +10579,11 @@
       <c r="J249" s="29"/>
     </row>
     <row r="250" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="83"/>
-      <c r="B250" s="77"/>
-      <c r="C250" s="69"/>
-      <c r="D250" s="69"/>
-      <c r="E250" s="69"/>
+      <c r="A250" s="75"/>
+      <c r="B250" s="94"/>
+      <c r="C250" s="73"/>
+      <c r="D250" s="73"/>
+      <c r="E250" s="73"/>
       <c r="F250" s="26">
         <v>2</v>
       </c>
@@ -10606,19 +10597,19 @@
       <c r="J250" s="37"/>
     </row>
     <row r="251" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="82">
+      <c r="A251" s="74">
         <v>118</v>
       </c>
-      <c r="B251" s="74" t="s">
+      <c r="B251" s="97" t="s">
         <v>177</v>
       </c>
-      <c r="C251" s="68" t="s">
+      <c r="C251" s="72" t="s">
         <v>760</v>
       </c>
-      <c r="D251" s="68" t="s">
+      <c r="D251" s="72" t="s">
         <v>761</v>
       </c>
-      <c r="E251" s="68" t="s">
+      <c r="E251" s="72" t="s">
         <v>762</v>
       </c>
       <c r="F251" s="24">
@@ -10632,11 +10623,11 @@
       <c r="J251" s="35"/>
     </row>
     <row r="252" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="83"/>
-      <c r="B252" s="75"/>
-      <c r="C252" s="69"/>
-      <c r="D252" s="69"/>
-      <c r="E252" s="69"/>
+      <c r="A252" s="75"/>
+      <c r="B252" s="98"/>
+      <c r="C252" s="73"/>
+      <c r="D252" s="73"/>
+      <c r="E252" s="73"/>
       <c r="F252" s="26">
         <v>2</v>
       </c>
@@ -10650,19 +10641,19 @@
       <c r="J252" s="37"/>
     </row>
     <row r="253" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="82">
+      <c r="A253" s="74">
         <v>119</v>
       </c>
-      <c r="B253" s="76" t="s">
+      <c r="B253" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C253" s="68" t="s">
+      <c r="C253" s="72" t="s">
         <v>766</v>
       </c>
-      <c r="D253" s="68" t="s">
+      <c r="D253" s="72" t="s">
         <v>767</v>
       </c>
-      <c r="E253" s="68" t="s">
+      <c r="E253" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F253" s="24">
@@ -10678,11 +10669,11 @@
       <c r="J253" s="35"/>
     </row>
     <row r="254" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="83"/>
-      <c r="B254" s="77"/>
-      <c r="C254" s="69"/>
-      <c r="D254" s="69"/>
-      <c r="E254" s="69"/>
+      <c r="A254" s="75"/>
+      <c r="B254" s="94"/>
+      <c r="C254" s="73"/>
+      <c r="D254" s="73"/>
+      <c r="E254" s="73"/>
       <c r="F254" s="26">
         <v>2</v>
       </c>
@@ -10696,19 +10687,19 @@
       <c r="J254" s="37"/>
     </row>
     <row r="255" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="82">
+      <c r="A255" s="74">
         <v>120</v>
       </c>
-      <c r="B255" s="76" t="s">
+      <c r="B255" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="C255" s="68" t="s">
+      <c r="C255" s="72" t="s">
         <v>771</v>
       </c>
-      <c r="D255" s="68" t="s">
+      <c r="D255" s="72" t="s">
         <v>772</v>
       </c>
-      <c r="E255" s="68" t="s">
+      <c r="E255" s="72" t="s">
         <v>714</v>
       </c>
       <c r="F255" s="24">
@@ -10722,11 +10713,11 @@
       <c r="J255" s="35"/>
     </row>
     <row r="256" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="91"/>
-      <c r="B256" s="105"/>
-      <c r="C256" s="92"/>
-      <c r="D256" s="92"/>
-      <c r="E256" s="92"/>
+      <c r="A256" s="105"/>
+      <c r="B256" s="118"/>
+      <c r="C256" s="101"/>
+      <c r="D256" s="101"/>
+      <c r="E256" s="101"/>
       <c r="F256" s="41">
         <v>2</v>
       </c>
@@ -10746,104 +10737,478 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="617">
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="K45:K47"/>
-    <mergeCell ref="K48:K49"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="N56:N57"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="L12:L14"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="M12:M14"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="E105:E106"/>
-    <mergeCell ref="E103:E104"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="N30:N31"/>
-    <mergeCell ref="N32:N33"/>
-    <mergeCell ref="N34:N35"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="D127:D128"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="B95:B96"/>
+  <mergeCells count="623">
+    <mergeCell ref="N62:N63"/>
+    <mergeCell ref="N60:N61"/>
+    <mergeCell ref="N64:N65"/>
+    <mergeCell ref="N74:N77"/>
+    <mergeCell ref="N78:N81"/>
+    <mergeCell ref="N84:N85"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="D191:D192"/>
+    <mergeCell ref="E191:E192"/>
+    <mergeCell ref="E187:E188"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E148:E149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="E185:E186"/>
+    <mergeCell ref="E183:E184"/>
+    <mergeCell ref="E181:E182"/>
+    <mergeCell ref="E179:E180"/>
+    <mergeCell ref="D179:D180"/>
+    <mergeCell ref="D181:D182"/>
+    <mergeCell ref="D183:D184"/>
+    <mergeCell ref="D185:D186"/>
+    <mergeCell ref="D189:D190"/>
+    <mergeCell ref="E189:E190"/>
+    <mergeCell ref="E241:E242"/>
+    <mergeCell ref="E239:E240"/>
+    <mergeCell ref="D239:D240"/>
+    <mergeCell ref="C235:C236"/>
+    <mergeCell ref="D235:D236"/>
+    <mergeCell ref="E235:E236"/>
+    <mergeCell ref="B235:B236"/>
+    <mergeCell ref="D201:D202"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="E201:E202"/>
+    <mergeCell ref="E203:E204"/>
+    <mergeCell ref="C203:C204"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="B249:B250"/>
+    <mergeCell ref="B247:B248"/>
+    <mergeCell ref="D241:D242"/>
+    <mergeCell ref="C239:C240"/>
+    <mergeCell ref="C241:C242"/>
+    <mergeCell ref="B239:B240"/>
+    <mergeCell ref="B241:B242"/>
+    <mergeCell ref="E231:E232"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="B231:B232"/>
+    <mergeCell ref="C231:C232"/>
+    <mergeCell ref="D231:D232"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E243:E244"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="D105:D106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="E109:E110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="E107:E108"/>
+    <mergeCell ref="E111:E112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E115:E116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="E125:E126"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="D123:D124"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="E133:E135"/>
+    <mergeCell ref="D133:D135"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="C133:C135"/>
+    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="A133:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="E175:E176"/>
+    <mergeCell ref="D175:D176"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="E166:E167"/>
+    <mergeCell ref="E168:E169"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="E170:E171"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="D168:D169"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="C187:C188"/>
+    <mergeCell ref="D187:D188"/>
+    <mergeCell ref="C185:C186"/>
+    <mergeCell ref="C183:C184"/>
+    <mergeCell ref="B183:B184"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="E177:E178"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="B191:B192"/>
+    <mergeCell ref="C191:C192"/>
+    <mergeCell ref="C189:C190"/>
+    <mergeCell ref="C201:C202"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="B195:B196"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="C197:C198"/>
+    <mergeCell ref="D197:D198"/>
+    <mergeCell ref="C193:C194"/>
+    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="B193:B194"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="E208:E209"/>
+    <mergeCell ref="D208:D209"/>
+    <mergeCell ref="C208:C209"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="E216:E217"/>
+    <mergeCell ref="E214:E215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="E222:E223"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="D220:D221"/>
+    <mergeCell ref="E220:E221"/>
+    <mergeCell ref="E218:E219"/>
+    <mergeCell ref="D218:D219"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="E237:E238"/>
+    <mergeCell ref="D237:D238"/>
+    <mergeCell ref="C237:C238"/>
+    <mergeCell ref="B237:B238"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E255:E256"/>
+    <mergeCell ref="E253:E254"/>
+    <mergeCell ref="D253:D254"/>
+    <mergeCell ref="C253:C254"/>
+    <mergeCell ref="B253:B254"/>
+    <mergeCell ref="E251:E252"/>
+    <mergeCell ref="E249:E250"/>
+    <mergeCell ref="D249:D250"/>
+    <mergeCell ref="D251:D252"/>
+    <mergeCell ref="C251:C252"/>
+    <mergeCell ref="C249:C250"/>
+    <mergeCell ref="C247:C248"/>
+    <mergeCell ref="D247:D248"/>
+    <mergeCell ref="E247:E248"/>
+    <mergeCell ref="E245:E246"/>
+    <mergeCell ref="D245:D246"/>
+    <mergeCell ref="C245:C246"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="B255:B256"/>
+    <mergeCell ref="C255:C256"/>
+    <mergeCell ref="D255:D256"/>
+    <mergeCell ref="B245:B246"/>
+    <mergeCell ref="B243:B244"/>
+    <mergeCell ref="C243:C244"/>
+    <mergeCell ref="D243:D244"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A255:A256"/>
+    <mergeCell ref="A253:A254"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A249:A250"/>
+    <mergeCell ref="A247:A248"/>
+    <mergeCell ref="A245:A246"/>
+    <mergeCell ref="A243:A244"/>
+    <mergeCell ref="A241:A242"/>
+    <mergeCell ref="A239:A240"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="E210:E211"/>
+    <mergeCell ref="E206:E207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="E212:E213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="D193:D194"/>
+    <mergeCell ref="E193:E194"/>
+    <mergeCell ref="E195:E196"/>
+    <mergeCell ref="D195:D196"/>
+    <mergeCell ref="E197:E198"/>
+    <mergeCell ref="E199:E200"/>
+    <mergeCell ref="D199:D200"/>
+    <mergeCell ref="C199:C200"/>
+    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="E158:E159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="E162:E163"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E160:E161"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="E156:E157"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="E113:E114"/>
+    <mergeCell ref="A132:J132"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="E172:E173"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A142:A143"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A74:A77"/>
     <mergeCell ref="D142:D143"/>
@@ -10868,409 +11233,67 @@
     <mergeCell ref="E78:E81"/>
     <mergeCell ref="B138:B139"/>
     <mergeCell ref="B136:B137"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="E172:E173"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="E127:E128"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="N15:N17"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="N32:N33"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A82:A83"/>
     <mergeCell ref="D56:D57"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="E162:E163"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E160:E161"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="E156:E157"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="E113:E114"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C177:C178"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B179:B180"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="D193:D194"/>
-    <mergeCell ref="E193:E194"/>
-    <mergeCell ref="E195:E196"/>
-    <mergeCell ref="D195:D196"/>
-    <mergeCell ref="E197:E198"/>
-    <mergeCell ref="E199:E200"/>
-    <mergeCell ref="D199:D200"/>
-    <mergeCell ref="C199:C200"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="E210:E211"/>
-    <mergeCell ref="E206:E207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="E212:E213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="A210:A211"/>
     <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A255:A256"/>
-    <mergeCell ref="A253:A254"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A249:A250"/>
-    <mergeCell ref="A247:A248"/>
-    <mergeCell ref="A245:A246"/>
-    <mergeCell ref="A243:A244"/>
-    <mergeCell ref="A241:A242"/>
-    <mergeCell ref="A239:A240"/>
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="B255:B256"/>
-    <mergeCell ref="C255:C256"/>
-    <mergeCell ref="D255:D256"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="M12:M14"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="E105:E106"/>
+    <mergeCell ref="E103:E104"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="B245:B246"/>
-    <mergeCell ref="B243:B244"/>
-    <mergeCell ref="C243:C244"/>
-    <mergeCell ref="D243:D244"/>
     <mergeCell ref="E9:E11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="E237:E238"/>
-    <mergeCell ref="D237:D238"/>
-    <mergeCell ref="C237:C238"/>
-    <mergeCell ref="B237:B238"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E255:E256"/>
-    <mergeCell ref="E253:E254"/>
-    <mergeCell ref="D253:D254"/>
-    <mergeCell ref="C253:C254"/>
-    <mergeCell ref="B253:B254"/>
-    <mergeCell ref="E251:E252"/>
-    <mergeCell ref="E249:E250"/>
-    <mergeCell ref="D249:D250"/>
-    <mergeCell ref="D251:D252"/>
-    <mergeCell ref="C251:C252"/>
-    <mergeCell ref="C249:C250"/>
-    <mergeCell ref="C247:C248"/>
-    <mergeCell ref="D247:D248"/>
-    <mergeCell ref="E247:E248"/>
-    <mergeCell ref="E245:E246"/>
-    <mergeCell ref="D245:D246"/>
-    <mergeCell ref="C245:C246"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="E222:E223"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="D220:D221"/>
-    <mergeCell ref="E220:E221"/>
-    <mergeCell ref="E218:E219"/>
-    <mergeCell ref="D218:D219"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="E216:E217"/>
-    <mergeCell ref="E214:E215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="E208:E209"/>
-    <mergeCell ref="D208:D209"/>
-    <mergeCell ref="C208:C209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="E177:E178"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="B191:B192"/>
-    <mergeCell ref="C191:C192"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="C201:C202"/>
-    <mergeCell ref="B203:B204"/>
-    <mergeCell ref="B199:B200"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="B195:B196"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="C197:C198"/>
-    <mergeCell ref="D197:D198"/>
-    <mergeCell ref="C193:C194"/>
-    <mergeCell ref="C195:C196"/>
-    <mergeCell ref="B193:B194"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="C187:C188"/>
-    <mergeCell ref="D187:D188"/>
-    <mergeCell ref="C185:C186"/>
-    <mergeCell ref="C183:C184"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="A174:J174"/>
-    <mergeCell ref="E175:E176"/>
-    <mergeCell ref="D175:D176"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="E166:E167"/>
-    <mergeCell ref="E168:E169"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="D168:D169"/>
-    <mergeCell ref="A132:J132"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="E133:E135"/>
-    <mergeCell ref="D133:D135"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="A133:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="E127:E128"/>
-    <mergeCell ref="E125:E126"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="D125:D126"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="D123:D124"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="D117:D118"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E115:E116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="D109:D110"/>
-    <mergeCell ref="E109:E110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:D108"/>
-    <mergeCell ref="E107:E108"/>
-    <mergeCell ref="E111:E112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="D105:D106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
-    <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="A91:J91"/>
     <mergeCell ref="A89:A90"/>
@@ -11282,88 +11305,62 @@
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="A84:A85"/>
     <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="L12:L14"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="K45:K47"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D53:D54"/>
     <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="B249:B250"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="B247:B248"/>
-    <mergeCell ref="D241:D242"/>
-    <mergeCell ref="C239:C240"/>
-    <mergeCell ref="C241:C242"/>
-    <mergeCell ref="B239:B240"/>
-    <mergeCell ref="B241:B242"/>
-    <mergeCell ref="E231:E232"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="B231:B232"/>
-    <mergeCell ref="C231:C232"/>
-    <mergeCell ref="D231:D232"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E243:E244"/>
-    <mergeCell ref="E241:E242"/>
-    <mergeCell ref="E239:E240"/>
-    <mergeCell ref="D239:D240"/>
-    <mergeCell ref="C235:C236"/>
-    <mergeCell ref="D235:D236"/>
-    <mergeCell ref="E235:E236"/>
-    <mergeCell ref="B235:B236"/>
-    <mergeCell ref="D201:D202"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="E201:E202"/>
-    <mergeCell ref="E203:E204"/>
-    <mergeCell ref="C203:C204"/>
-    <mergeCell ref="E185:E186"/>
-    <mergeCell ref="E183:E184"/>
-    <mergeCell ref="E181:E182"/>
-    <mergeCell ref="E179:E180"/>
-    <mergeCell ref="D179:D180"/>
-    <mergeCell ref="D181:D182"/>
-    <mergeCell ref="D183:D184"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="D189:D190"/>
-    <mergeCell ref="E189:E190"/>
-    <mergeCell ref="D191:D192"/>
-    <mergeCell ref="E191:E192"/>
-    <mergeCell ref="E187:E188"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E148:E149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="A42:A44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11387,54 +11384,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="143" t="s">
+      <c r="B2" s="166"/>
+      <c r="C2" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="144"/>
-      <c r="E2" s="145"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="169"/>
       <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="143" t="s">
+      <c r="G2" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="146"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="170"/>
     </row>
     <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="148"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="151"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="149"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="152"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="176"/>
     </row>
     <row r="4" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="153" t="s">
@@ -11515,18 +11512,18 @@
       <c r="J9" s="163"/>
     </row>
     <row r="10" spans="1:12" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="151" t="s">
         <v>158</v>
       </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
-      <c r="J10" s="167"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
+      <c r="F10" s="152"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="152"/>
+      <c r="I10" s="152"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
@@ -11670,18 +11667,18 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="164" t="s">
+      <c r="A16" s="149" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="165"/>
-      <c r="F16" s="165"/>
-      <c r="G16" s="165"/>
-      <c r="H16" s="165"/>
-      <c r="I16" s="165"/>
-      <c r="J16" s="165"/>
+      <c r="B16" s="150"/>
+      <c r="C16" s="150"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
@@ -11823,18 +11820,18 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="164" t="s">
+      <c r="A22" s="149" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="165"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="165"/>
-      <c r="F22" s="165"/>
-      <c r="G22" s="165"/>
-      <c r="H22" s="165"/>
-      <c r="I22" s="165"/>
-      <c r="J22" s="165"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="150"/>
+      <c r="H22" s="150"/>
+      <c r="I22" s="150"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
@@ -11949,18 +11946,18 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="164" t="s">
+      <c r="A27" s="149" t="s">
         <v>183</v>
       </c>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-      <c r="F27" s="165"/>
-      <c r="G27" s="165"/>
-      <c r="H27" s="165"/>
-      <c r="I27" s="165"/>
-      <c r="J27" s="165"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
     </row>
     <row r="28" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
@@ -12075,18 +12072,18 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="164" t="s">
+      <c r="A32" s="149" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="165"/>
-      <c r="H32" s="165"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="165"/>
+      <c r="B32" s="150"/>
+      <c r="C32" s="150"/>
+      <c r="D32" s="150"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="150"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
     </row>
     <row r="33" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -12228,18 +12225,18 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="164" t="s">
+      <c r="A38" s="149" t="s">
         <v>185</v>
       </c>
-      <c r="B38" s="165"/>
-      <c r="C38" s="165"/>
-      <c r="D38" s="165"/>
-      <c r="E38" s="165"/>
-      <c r="F38" s="165"/>
-      <c r="G38" s="165"/>
-      <c r="H38" s="165"/>
-      <c r="I38" s="165"/>
-      <c r="J38" s="165"/>
+      <c r="B38" s="150"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="150"/>
+      <c r="E38" s="150"/>
+      <c r="F38" s="150"/>
+      <c r="G38" s="150"/>
+      <c r="H38" s="150"/>
+      <c r="I38" s="150"/>
+      <c r="J38" s="150"/>
     </row>
     <row r="39" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20">
@@ -12408,18 +12405,18 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="164" t="s">
+      <c r="A45" s="149" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="165"/>
-      <c r="C45" s="165"/>
-      <c r="D45" s="165"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="165"/>
-      <c r="G45" s="165"/>
-      <c r="H45" s="165"/>
-      <c r="I45" s="165"/>
-      <c r="J45" s="165"/>
+      <c r="B45" s="150"/>
+      <c r="C45" s="150"/>
+      <c r="D45" s="150"/>
+      <c r="E45" s="150"/>
+      <c r="F45" s="150"/>
+      <c r="G45" s="150"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="150"/>
+      <c r="J45" s="150"/>
     </row>
     <row r="46" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="20">
@@ -12534,18 +12531,18 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="149" t="s">
         <v>187</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="165"/>
-      <c r="D50" s="165"/>
-      <c r="E50" s="165"/>
-      <c r="F50" s="165"/>
-      <c r="G50" s="165"/>
-      <c r="H50" s="165"/>
-      <c r="I50" s="165"/>
-      <c r="J50" s="165"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="150"/>
+      <c r="D50" s="150"/>
+      <c r="E50" s="150"/>
+      <c r="F50" s="150"/>
+      <c r="G50" s="150"/>
+      <c r="H50" s="150"/>
+      <c r="I50" s="150"/>
+      <c r="J50" s="150"/>
     </row>
     <row r="51" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="20">
@@ -12660,18 +12657,18 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="164" t="s">
+      <c r="A55" s="149" t="s">
         <v>188</v>
       </c>
-      <c r="B55" s="165"/>
-      <c r="C55" s="165"/>
-      <c r="D55" s="165"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="165"/>
-      <c r="G55" s="165"/>
-      <c r="H55" s="165"/>
-      <c r="I55" s="165"/>
-      <c r="J55" s="165"/>
+      <c r="B55" s="150"/>
+      <c r="C55" s="150"/>
+      <c r="D55" s="150"/>
+      <c r="E55" s="150"/>
+      <c r="F55" s="150"/>
+      <c r="G55" s="150"/>
+      <c r="H55" s="150"/>
+      <c r="I55" s="150"/>
+      <c r="J55" s="150"/>
     </row>
     <row r="56" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20">
@@ -12760,6 +12757,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A50:J50"/>
@@ -12769,18 +12778,6 @@
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -12788,11 +12785,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0443d48f-321c-4e41-9d7a-7eb2a399c3c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12952,26 +12950,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0443d48f-321c-4e41-9d7a-7eb2a399c3c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCD443E7-F6DD-4A9A-9DCB-C1C4800B5DE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9791D7-602D-4432-8FB9-6B78B6FA939F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0443d48f-321c-4e41-9d7a-7eb2a399c3c3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12995,9 +12984,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9791D7-602D-4432-8FB9-6B78B6FA939F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCD443E7-F6DD-4A9A-9DCB-C1C4800B5DE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0443d48f-321c-4e41-9d7a-7eb2a399c3c3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/TestData/Testcase.xlsx
+++ b/TestData/Testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khoa\sqa-testing-lab\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC01B5E9-0ED3-47E2-827C-2B49E6D8E24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B6A8CF-9C5E-4C33-8449-BE1DEEC1CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{23F3E367-7927-4520-A748-866283E286BB}"/>
   </bookViews>
@@ -2479,9 +2479,6 @@
     <t>Hệ thống chặn thao tác trùng, chỉ ghi nhận 1 lệnh vay duy nhất.</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_01, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Đã có User 'khoa_it_01'</t>
   </si>
   <si>
@@ -2491,63 +2488,30 @@
     <t>Nhập Confirm Password và điền đủ các ô còn lại</t>
   </si>
   <si>
-    <t>Confirm: 456, F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_02</t>
-  </si>
-  <si>
     <t>Để trống ô 'First Name', nhập đủ các ô khác</t>
   </si>
   <si>
-    <t>F.Name: [Empty], L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_03, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Để trống ô 'SSN', nhập đủ các ô khác</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: [Empty], User: khoa_it_04, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Nhập chữ vào ô 'Zip Code', điền đủ các ô khác</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: ABCD, Phone: 0901234567, SSN: 123-456, User: khoa_it_05, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Nhập chữ vào ô 'Phone', điền đủ các ô khác</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: HELLO, SSN: 123-456, User: khoa_it_06, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: [Empty], Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_07, Pass: [Empty], Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Để trống ô 'Address', nhập đủ các ô khác</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: [Empty], City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_08, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Điền các ô khác, để trống cả 2 ô mật khẩu</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_09, Pass: [Empty], Confirm: [Empty]</t>
-  </si>
-  <si>
     <t>Điền các ô khác, nhập mật khẩu chỉ có 1 ký tự</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_10, Pass: 1, Confirm: 1</t>
-  </si>
-  <si>
     <t>Vừa nhận thông báo lỗi (từ TC_013)</t>
   </si>
   <si>
-    <t>F.Name: Khoa, L.Name: Nguyen, Address: 456 Le Loi, City: HCM, State: VN, Zip: 70000, Phone: 0909999999, SSN: 999-888, User: khoa_it_final, Pass: Khoa123!, Confirm: Khoa123!</t>
-  </si>
-  <si>
     <t>Name: Nước sạch SG, Address: 123 DBP, City: HCM, State: VN, Zip: 70000, Phone: 0901112222</t>
   </si>
   <si>
@@ -2669,6 +2633,42 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, Zip Code: 70000, Phone: 0901234567, SSN: 123-456, User: [Empty], Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 456 Le Loi, City: HCM, State: VN, ZipCode: 70000, Phone: 0909999999, SSN: 999-888, User: khoa_it_final, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_10, Pass: 1, Confirm: 1</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_09, Pass: [Empty], Confirm: [Empty]</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: [Empty], City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_08, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_07, Pass: [Empty], Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: HELLO, SSN: 123-456, User: khoa_it_06, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: ABCD, Phone: 0901234567, SSN: 123-456, User: khoa_it_05, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: [Empty], User: khoa_it_04, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>F.Name: [Empty], L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_03, Pass: Khoa123!, Confirm: Khoa123!</t>
+  </si>
+  <si>
+    <t>Confirm: 456, F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_02</t>
+  </si>
+  <si>
+    <t>F.Name: Khoa, L.Name: Nguyen, Address: 123 CMT8, City: HCM, State: VN, ZipCode: 70000, Phone: 0901234567, SSN: 123-456, User: khoa_it_01, Pass: Khoa123!, Confirm: Khoa123!</t>
   </si>
 </sst>
 </file>
@@ -3891,7 +3891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4096,13 +4096,112 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4111,84 +4210,6 @@
     <xf numFmtId="0" fontId="18" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4213,18 +4234,6 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4240,79 +4249,85 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4324,16 +4339,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4419,27 +4437,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4954,65 +4951,65 @@
         <v>20</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="139"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="139"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="139"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="140"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="142"/>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="141" t="s">
+      <c r="A8" s="143" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="142"/>
+      <c r="B8" s="143"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="143"/>
+      <c r="N8" s="144"/>
     </row>
     <row r="9" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="91">
+      <c r="A9" s="102">
         <v>1</v>
       </c>
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="99" t="s">
+      <c r="C9" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="99" t="s">
+      <c r="D9" s="97" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="99" t="s">
+      <c r="E9" s="97" t="s">
         <v>196</v>
       </c>
       <c r="F9" s="22">
@@ -5024,19 +5021,19 @@
       <c r="H9" s="21"/>
       <c r="I9" s="33"/>
       <c r="J9" s="23"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="146"/>
-      <c r="M9" s="146"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
       <c r="N9" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="82"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
+      <c r="A10" s="83"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
       <c r="F10" s="24">
         <v>2</v>
       </c>
@@ -5044,17 +5041,17 @@
         <v>241</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>774</v>
+        <v>837</v>
       </c>
       <c r="I10" s="34"/>
       <c r="J10" s="35"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139"/>
       <c r="N10" s="66"/>
     </row>
     <row r="11" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="83"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="69"/>
       <c r="C11" s="69"/>
       <c r="D11" s="69"/>
@@ -5070,26 +5067,26 @@
         <v>197</v>
       </c>
       <c r="J11" s="37"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="139"/>
+      <c r="M11" s="139"/>
       <c r="N11" s="66"/>
     </row>
     <row r="12" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="79">
+      <c r="A12" s="70">
         <v>2</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="E12" s="71" t="s">
-        <v>775</v>
+      <c r="E12" s="72" t="s">
+        <v>774</v>
       </c>
       <c r="F12" s="24">
         <v>1</v>
@@ -5100,39 +5097,39 @@
       <c r="H12" s="25"/>
       <c r="I12" s="34"/>
       <c r="J12" s="29"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
+      <c r="K12" s="140"/>
+      <c r="L12" s="139"/>
+      <c r="M12" s="139"/>
       <c r="N12" s="66"/>
     </row>
     <row r="13" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
       <c r="F13" s="26">
         <v>2</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>774</v>
+        <v>837</v>
       </c>
       <c r="I13" s="36"/>
       <c r="J13" s="37"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="146"/>
-      <c r="M13" s="146"/>
+      <c r="K13" s="140"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
       <c r="N13" s="66"/>
     </row>
     <row r="14" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="80"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="24">
         <v>3</v>
       </c>
@@ -5144,13 +5141,13 @@
         <v>200</v>
       </c>
       <c r="J14" s="35"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139"/>
       <c r="N14" s="66"/>
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="90">
+      <c r="A15" s="89">
         <v>3</v>
       </c>
       <c r="B15" s="68" t="s">
@@ -5176,35 +5173,35 @@
       </c>
       <c r="I15" s="36"/>
       <c r="J15" s="37"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
+      <c r="K15" s="140"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
       <c r="N15" s="66"/>
     </row>
     <row r="16" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="82"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
       <c r="F16" s="24">
         <v>2</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>778</v>
+        <v>836</v>
       </c>
       <c r="I16" s="34"/>
       <c r="J16" s="35"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139"/>
       <c r="N16" s="66"/>
     </row>
     <row r="17" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="83"/>
+      <c r="A17" s="84"/>
       <c r="B17" s="69"/>
       <c r="C17" s="69"/>
       <c r="D17" s="69"/>
@@ -5220,49 +5217,49 @@
         <v>204</v>
       </c>
       <c r="J17" s="37"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="146"/>
-      <c r="M17" s="146"/>
+      <c r="K17" s="140"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139"/>
       <c r="N17" s="66"/>
     </row>
     <row r="18" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="79">
+      <c r="A18" s="70">
         <v>4</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="72" t="s">
         <v>205</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F18" s="24">
         <v>1</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>780</v>
+        <v>835</v>
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="35"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="146"/>
-      <c r="M18" s="146"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
       <c r="N18" s="66"/>
     </row>
     <row r="19" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="80"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="26">
         <v>2</v>
       </c>
@@ -5274,49 +5271,49 @@
         <v>207</v>
       </c>
       <c r="J19" s="37"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="146"/>
-      <c r="M19" s="146"/>
+      <c r="K19" s="140"/>
+      <c r="L19" s="139"/>
+      <c r="M19" s="139"/>
       <c r="N19" s="66"/>
     </row>
     <row r="20" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="79">
+      <c r="A20" s="70">
         <v>5</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="72" t="s">
         <v>209</v>
       </c>
-      <c r="E20" s="71" t="s">
+      <c r="E20" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F20" s="24">
         <v>1</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>782</v>
+        <v>834</v>
       </c>
       <c r="I20" s="34"/>
       <c r="J20" s="35"/>
-      <c r="K20" s="147"/>
-      <c r="L20" s="146"/>
-      <c r="M20" s="146"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
       <c r="N20" s="66"/>
     </row>
     <row r="21" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="80"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
+      <c r="A21" s="71"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
       <c r="F21" s="26">
         <v>2</v>
       </c>
@@ -5328,49 +5325,49 @@
         <v>210</v>
       </c>
       <c r="J21" s="37"/>
-      <c r="K21" s="147"/>
-      <c r="L21" s="146"/>
-      <c r="M21" s="146"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
       <c r="N21" s="66"/>
     </row>
     <row r="22" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="79">
+      <c r="A22" s="70">
         <v>6</v>
       </c>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="72" t="s">
         <v>212</v>
       </c>
-      <c r="E22" s="71" t="s">
+      <c r="E22" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F22" s="24">
         <v>1</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>784</v>
+        <v>833</v>
       </c>
       <c r="I22" s="34"/>
       <c r="J22" s="35"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="146"/>
-      <c r="M22" s="146"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="139"/>
       <c r="N22" s="66"/>
     </row>
     <row r="23" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="80"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
+      <c r="A23" s="71"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="26">
         <v>2</v>
       </c>
@@ -5382,49 +5379,49 @@
         <v>213</v>
       </c>
       <c r="J23" s="37"/>
-      <c r="K23" s="147"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="146"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="139"/>
+      <c r="M23" s="139"/>
       <c r="N23" s="66"/>
     </row>
     <row r="24" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="79">
+      <c r="A24" s="70">
         <v>7</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="72" t="s">
         <v>248</v>
       </c>
-      <c r="E24" s="71" t="s">
+      <c r="E24" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F24" s="24">
         <v>1</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="I24" s="34"/>
       <c r="J24" s="35"/>
-      <c r="K24" s="147"/>
-      <c r="L24" s="146"/>
-      <c r="M24" s="146"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="139"/>
+      <c r="M24" s="139"/>
       <c r="N24" s="66"/>
     </row>
     <row r="25" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="80"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
+      <c r="A25" s="71"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
       <c r="F25" s="26">
         <v>2</v>
       </c>
@@ -5436,25 +5433,25 @@
         <v>215</v>
       </c>
       <c r="J25" s="37"/>
-      <c r="K25" s="147"/>
-      <c r="L25" s="146"/>
-      <c r="M25" s="146"/>
+      <c r="K25" s="140"/>
+      <c r="L25" s="139"/>
+      <c r="M25" s="139"/>
       <c r="N25" s="66"/>
     </row>
     <row r="26" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="79">
+      <c r="A26" s="70">
         <v>8</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="C26" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="E26" s="71" t="s">
+      <c r="E26" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F26" s="24">
@@ -5464,21 +5461,21 @@
         <v>249</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="I26" s="34"/>
       <c r="J26" s="35"/>
-      <c r="K26" s="147"/>
-      <c r="L26" s="146"/>
-      <c r="M26" s="146"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="139"/>
       <c r="N26" s="66"/>
     </row>
     <row r="27" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="80"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
+      <c r="A27" s="71"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="26">
         <v>2</v>
       </c>
@@ -5490,25 +5487,25 @@
         <v>218</v>
       </c>
       <c r="J27" s="37"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="146"/>
-      <c r="M27" s="146"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="139"/>
       <c r="N27" s="66"/>
     </row>
     <row r="28" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="79">
+      <c r="A28" s="70">
         <v>9</v>
       </c>
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="E28" s="71" t="s">
+      <c r="E28" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F28" s="24">
@@ -5518,21 +5515,21 @@
         <v>250</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="146"/>
-      <c r="M28" s="146"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="139"/>
       <c r="N28" s="66"/>
     </row>
     <row r="29" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="80"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
+      <c r="A29" s="71"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
       <c r="F29" s="26">
         <v>2</v>
       </c>
@@ -5544,49 +5541,49 @@
         <v>221</v>
       </c>
       <c r="J29" s="37"/>
-      <c r="K29" s="147"/>
-      <c r="L29" s="146"/>
-      <c r="M29" s="146"/>
+      <c r="K29" s="140"/>
+      <c r="L29" s="139"/>
+      <c r="M29" s="139"/>
       <c r="N29" s="66"/>
     </row>
     <row r="30" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="79">
+      <c r="A30" s="70">
         <v>10</v>
       </c>
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="71" t="s">
+      <c r="C30" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="72" t="s">
         <v>223</v>
       </c>
-      <c r="E30" s="71" t="s">
+      <c r="E30" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F30" s="24">
         <v>1</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="35"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="146"/>
-      <c r="M30" s="146"/>
+      <c r="K30" s="140"/>
+      <c r="L30" s="139"/>
+      <c r="M30" s="139"/>
       <c r="N30" s="66"/>
     </row>
     <row r="31" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="80"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
+      <c r="A31" s="71"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="26">
         <v>2</v>
       </c>
@@ -5598,25 +5595,25 @@
         <v>224</v>
       </c>
       <c r="J31" s="37"/>
-      <c r="K31" s="147"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="146"/>
+      <c r="K31" s="140"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="139"/>
       <c r="N31" s="66"/>
     </row>
     <row r="32" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="79">
+      <c r="A32" s="70">
         <v>11</v>
       </c>
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="D32" s="71" t="s">
+      <c r="D32" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="E32" s="71" t="s">
+      <c r="E32" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F32" s="24">
@@ -5628,17 +5625,17 @@
       <c r="H32" s="25"/>
       <c r="I32" s="34"/>
       <c r="J32" s="29"/>
-      <c r="K32" s="147"/>
-      <c r="L32" s="146"/>
-      <c r="M32" s="146"/>
+      <c r="K32" s="140"/>
+      <c r="L32" s="139"/>
+      <c r="M32" s="139"/>
       <c r="N32" s="66"/>
     </row>
     <row r="33" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="80"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
+      <c r="A33" s="71"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
       <c r="F33" s="26">
         <v>2</v>
       </c>
@@ -5650,49 +5647,49 @@
         <v>227</v>
       </c>
       <c r="J33" s="37"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="146"/>
-      <c r="M33" s="146"/>
+      <c r="K33" s="140"/>
+      <c r="L33" s="139"/>
+      <c r="M33" s="139"/>
       <c r="N33" s="66"/>
     </row>
     <row r="34" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="79">
+      <c r="A34" s="70">
         <v>12</v>
       </c>
-      <c r="B34" s="71" t="s">
+      <c r="B34" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="71" t="s">
+      <c r="C34" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="D34" s="71" t="s">
+      <c r="D34" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="E34" s="71" t="s">
+      <c r="E34" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="24">
         <v>1</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I34" s="34"/>
       <c r="J34" s="35"/>
-      <c r="K34" s="147"/>
-      <c r="L34" s="146"/>
-      <c r="M34" s="146"/>
+      <c r="K34" s="140"/>
+      <c r="L34" s="139"/>
+      <c r="M34" s="139"/>
       <c r="N34" s="66"/>
     </row>
     <row r="35" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="80"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
+      <c r="A35" s="71"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="26">
         <v>2</v>
       </c>
@@ -5704,49 +5701,49 @@
         <v>230</v>
       </c>
       <c r="J35" s="37"/>
-      <c r="K35" s="147"/>
-      <c r="L35" s="146"/>
-      <c r="M35" s="146"/>
+      <c r="K35" s="140"/>
+      <c r="L35" s="139"/>
+      <c r="M35" s="139"/>
       <c r="N35" s="66"/>
     </row>
     <row r="36" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="79">
+      <c r="A36" s="70">
         <v>13</v>
       </c>
-      <c r="B36" s="71" t="s">
+      <c r="B36" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="72" t="s">
         <v>231</v>
       </c>
-      <c r="D36" s="71" t="s">
+      <c r="D36" s="72" t="s">
         <v>232</v>
       </c>
-      <c r="E36" s="71" t="s">
+      <c r="E36" s="72" t="s">
         <v>203</v>
       </c>
       <c r="F36" s="24">
         <v>1</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="I36" s="34"/>
       <c r="J36" s="35"/>
-      <c r="K36" s="147"/>
-      <c r="L36" s="146"/>
-      <c r="M36" s="146"/>
+      <c r="K36" s="140"/>
+      <c r="L36" s="139"/>
+      <c r="M36" s="139"/>
       <c r="N36" s="66"/>
     </row>
     <row r="37" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="80"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
+      <c r="A37" s="71"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="26">
         <v>2</v>
       </c>
@@ -5758,9 +5755,9 @@
         <v>233</v>
       </c>
       <c r="J37" s="37"/>
-      <c r="K37" s="147"/>
-      <c r="L37" s="146"/>
-      <c r="M37" s="146"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="139"/>
+      <c r="M37" s="139"/>
       <c r="N37" s="66"/>
     </row>
     <row r="38" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
@@ -5777,7 +5774,7 @@
         <v>235</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="F38" s="24">
         <v>1</v>
@@ -5792,7 +5789,7 @@
       <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="90">
+      <c r="A39" s="89">
         <v>15</v>
       </c>
       <c r="B39" s="68" t="s">
@@ -5814,21 +5811,21 @@
         <v>254</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>796</v>
+        <v>827</v>
       </c>
       <c r="I39" s="36"/>
       <c r="J39" s="37"/>
-      <c r="K39" s="147"/>
-      <c r="L39" s="146"/>
-      <c r="M39" s="146"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="139"/>
+      <c r="M39" s="139"/>
       <c r="N39" s="66"/>
     </row>
     <row r="40" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
+      <c r="A40" s="116"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
       <c r="F40" s="31">
         <v>2</v>
       </c>
@@ -5840,43 +5837,43 @@
         <v>239</v>
       </c>
       <c r="J40" s="57"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="146"/>
-      <c r="M40" s="146"/>
+      <c r="K40" s="140"/>
+      <c r="L40" s="139"/>
+      <c r="M40" s="139"/>
       <c r="N40" s="66"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="143" t="s">
+      <c r="A41" s="148" t="s">
         <v>158</v>
       </c>
-      <c r="B41" s="144"/>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="144"/>
-      <c r="J41" s="144"/>
-      <c r="K41" s="144"/>
-      <c r="L41" s="144"/>
-      <c r="M41" s="144"/>
-      <c r="N41" s="145"/>
+      <c r="B41" s="149"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="149"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
+      <c r="I41" s="149"/>
+      <c r="J41" s="149"/>
+      <c r="K41" s="149"/>
+      <c r="L41" s="149"/>
+      <c r="M41" s="149"/>
+      <c r="N41" s="150"/>
     </row>
     <row r="42" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="81">
+      <c r="A42" s="82">
         <v>16</v>
       </c>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="D42" s="87" t="s">
+      <c r="D42" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="E42" s="87" t="s">
+      <c r="E42" s="85" t="s">
         <v>255</v>
       </c>
       <c r="F42" s="44">
@@ -5890,19 +5887,19 @@
       </c>
       <c r="I42" s="45"/>
       <c r="J42" s="46"/>
-      <c r="K42" s="149"/>
-      <c r="L42" s="184"/>
-      <c r="M42" s="184"/>
-      <c r="N42" s="148" t="s">
-        <v>837</v>
+      <c r="K42" s="147"/>
+      <c r="L42" s="151"/>
+      <c r="M42" s="151"/>
+      <c r="N42" s="146" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="82"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
+      <c r="A43" s="83"/>
+      <c r="B43" s="86"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
       <c r="F43" s="24">
         <v>2</v>
       </c>
@@ -5914,13 +5911,13 @@
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="35"/>
-      <c r="K43" s="147"/>
-      <c r="L43" s="146"/>
-      <c r="M43" s="146"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="139"/>
+      <c r="M43" s="139"/>
       <c r="N43" s="66"/>
     </row>
     <row r="44" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="83"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="69"/>
       <c r="C44" s="69"/>
       <c r="D44" s="69"/>
@@ -5936,25 +5933,25 @@
         <v>261</v>
       </c>
       <c r="J44" s="37"/>
-      <c r="K44" s="147"/>
-      <c r="L44" s="146"/>
-      <c r="M44" s="146"/>
+      <c r="K44" s="140"/>
+      <c r="L44" s="139"/>
+      <c r="M44" s="139"/>
       <c r="N44" s="66"/>
     </row>
     <row r="45" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79">
+      <c r="A45" s="70">
         <v>17</v>
       </c>
-      <c r="B45" s="71" t="s">
+      <c r="B45" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="71" t="s">
+      <c r="C45" s="72" t="s">
         <v>262</v>
       </c>
-      <c r="D45" s="71" t="s">
+      <c r="D45" s="72" t="s">
         <v>263</v>
       </c>
-      <c r="E45" s="71" t="s">
+      <c r="E45" s="72" t="s">
         <v>255</v>
       </c>
       <c r="F45" s="24">
@@ -5968,15 +5965,15 @@
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="29"/>
-      <c r="K45" s="147"/>
-      <c r="N45" s="148"/>
+      <c r="K45" s="140"/>
+      <c r="N45" s="146"/>
     </row>
     <row r="46" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="88"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
+      <c r="A46" s="87"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="88"/>
+      <c r="D46" s="88"/>
+      <c r="E46" s="88"/>
       <c r="F46" s="26">
         <v>2</v>
       </c>
@@ -5988,15 +5985,15 @@
       </c>
       <c r="I46" s="36"/>
       <c r="J46" s="37"/>
-      <c r="K46" s="147"/>
+      <c r="K46" s="140"/>
       <c r="N46" s="66"/>
     </row>
     <row r="47" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
       <c r="F47" s="24">
         <v>3</v>
       </c>
@@ -6008,11 +6005,11 @@
         <v>267</v>
       </c>
       <c r="J47" s="35"/>
-      <c r="K47" s="147"/>
+      <c r="K47" s="140"/>
       <c r="N47" s="66"/>
     </row>
     <row r="48" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="90">
+      <c r="A48" s="89">
         <v>18</v>
       </c>
       <c r="B48" s="68" t="s">
@@ -6038,11 +6035,11 @@
       </c>
       <c r="I48" s="36"/>
       <c r="J48" s="37"/>
-      <c r="K48" s="147"/>
+      <c r="K48" s="140"/>
       <c r="N48" s="66"/>
     </row>
     <row r="49" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="83"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="69"/>
       <c r="C49" s="69"/>
       <c r="D49" s="69"/>
@@ -6058,7 +6055,7 @@
         <v>267</v>
       </c>
       <c r="J49" s="35"/>
-      <c r="K49" s="147"/>
+      <c r="K49" s="140"/>
       <c r="N49" s="66"/>
     </row>
     <row r="50" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -6119,7 +6116,7 @@
       </c>
       <c r="J51" s="35"/>
       <c r="N51" s="65" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -6151,19 +6148,19 @@
       <c r="J52" s="38"/>
     </row>
     <row r="53" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="79">
+      <c r="A53" s="70">
         <v>22</v>
       </c>
-      <c r="B53" s="71" t="s">
+      <c r="B53" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="71" t="s">
+      <c r="C53" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="D53" s="71" t="s">
+      <c r="D53" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="E53" s="71" t="s">
+      <c r="E53" s="72" t="s">
         <v>291</v>
       </c>
       <c r="F53" s="24">
@@ -6175,15 +6172,15 @@
       <c r="H53" s="25"/>
       <c r="I53" s="34"/>
       <c r="J53" s="35"/>
-      <c r="K53" s="147"/>
+      <c r="K53" s="140"/>
       <c r="N53" s="66"/>
     </row>
     <row r="54" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
       <c r="F54" s="26">
         <v>2</v>
       </c>
@@ -6195,7 +6192,7 @@
         <v>294</v>
       </c>
       <c r="J54" s="37"/>
-      <c r="K54" s="147"/>
+      <c r="K54" s="140"/>
       <c r="N54" s="66"/>
     </row>
     <row r="55" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -6227,7 +6224,7 @@
       <c r="J55" s="29"/>
     </row>
     <row r="56" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="90">
+      <c r="A56" s="89">
         <v>24</v>
       </c>
       <c r="B56" s="68" t="s">
@@ -6253,11 +6250,11 @@
       </c>
       <c r="I56" s="36"/>
       <c r="J56" s="37"/>
-      <c r="K56" s="147"/>
+      <c r="K56" s="140"/>
       <c r="N56" s="66"/>
     </row>
     <row r="57" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="69"/>
       <c r="C57" s="69"/>
       <c r="D57" s="69"/>
@@ -6273,7 +6270,7 @@
         <v>305</v>
       </c>
       <c r="J57" s="35"/>
-      <c r="K57" s="147"/>
+      <c r="K57" s="140"/>
       <c r="N57" s="66"/>
     </row>
     <row r="58" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -6305,37 +6302,37 @@
       <c r="J58" s="42"/>
     </row>
     <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="118" t="s">
+      <c r="A59" s="145" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="118"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="118"/>
-      <c r="H59" s="118"/>
-      <c r="I59" s="118"/>
-      <c r="J59" s="118"/>
-      <c r="K59" s="118"/>
-      <c r="L59" s="118"/>
-      <c r="M59" s="118"/>
-      <c r="N59" s="118"/>
+      <c r="B59" s="145"/>
+      <c r="C59" s="145"/>
+      <c r="D59" s="145"/>
+      <c r="E59" s="145"/>
+      <c r="F59" s="145"/>
+      <c r="G59" s="145"/>
+      <c r="H59" s="145"/>
+      <c r="I59" s="145"/>
+      <c r="J59" s="145"/>
+      <c r="K59" s="145"/>
+      <c r="L59" s="145"/>
+      <c r="M59" s="145"/>
+      <c r="N59" s="145"/>
     </row>
     <row r="60" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="91">
+      <c r="A60" s="102">
         <v>26</v>
       </c>
-      <c r="B60" s="99" t="s">
+      <c r="B60" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="99" t="s">
+      <c r="C60" s="97" t="s">
         <v>311</v>
       </c>
-      <c r="D60" s="99" t="s">
+      <c r="D60" s="97" t="s">
         <v>312</v>
       </c>
-      <c r="E60" s="99" t="s">
+      <c r="E60" s="97" t="s">
         <v>313</v>
       </c>
       <c r="F60" s="22">
@@ -6347,15 +6344,15 @@
       <c r="H60" s="47"/>
       <c r="I60" s="33"/>
       <c r="J60" s="23"/>
-      <c r="K60" s="147"/>
-      <c r="L60" s="146"/>
-      <c r="M60" s="146"/>
+      <c r="K60" s="140"/>
+      <c r="L60" s="139"/>
+      <c r="M60" s="139"/>
       <c r="N60" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="84"/>
       <c r="B61" s="69"/>
       <c r="C61" s="69"/>
       <c r="D61" s="69"/>
@@ -6371,13 +6368,13 @@
         <v>316</v>
       </c>
       <c r="J61" s="35"/>
-      <c r="K61" s="147"/>
-      <c r="L61" s="146"/>
-      <c r="M61" s="146"/>
+      <c r="K61" s="140"/>
+      <c r="L61" s="139"/>
+      <c r="M61" s="139"/>
       <c r="N61" s="66"/>
     </row>
     <row r="62" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="90">
+      <c r="A62" s="89">
         <v>27</v>
       </c>
       <c r="B62" s="68" t="s">
@@ -6401,15 +6398,15 @@
       <c r="H62" s="49"/>
       <c r="I62" s="36"/>
       <c r="J62" s="37"/>
-      <c r="K62" s="147"/>
-      <c r="L62" s="146"/>
-      <c r="M62" s="146"/>
+      <c r="K62" s="140"/>
+      <c r="L62" s="139"/>
+      <c r="M62" s="139"/>
       <c r="N62" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="84"/>
       <c r="B63" s="69"/>
       <c r="C63" s="69"/>
       <c r="D63" s="69"/>
@@ -6425,13 +6422,13 @@
         <v>322</v>
       </c>
       <c r="J63" s="35"/>
-      <c r="K63" s="147"/>
-      <c r="L63" s="146"/>
-      <c r="M63" s="146"/>
+      <c r="K63" s="140"/>
+      <c r="L63" s="139"/>
+      <c r="M63" s="139"/>
       <c r="N63" s="66"/>
     </row>
     <row r="64" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="90">
+      <c r="A64" s="89">
         <v>28</v>
       </c>
       <c r="B64" s="68" t="s">
@@ -6457,15 +6454,15 @@
       </c>
       <c r="I64" s="36"/>
       <c r="J64" s="37"/>
-      <c r="K64" s="147"/>
-      <c r="L64" s="146"/>
-      <c r="M64" s="146"/>
+      <c r="K64" s="140"/>
+      <c r="L64" s="139"/>
+      <c r="M64" s="139"/>
       <c r="N64" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="83"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="69"/>
       <c r="C65" s="69"/>
       <c r="D65" s="69"/>
@@ -6481,9 +6478,9 @@
         <v>329</v>
       </c>
       <c r="J65" s="35"/>
-      <c r="K65" s="147"/>
-      <c r="L65" s="146"/>
-      <c r="M65" s="146"/>
+      <c r="K65" s="140"/>
+      <c r="L65" s="139"/>
+      <c r="M65" s="139"/>
       <c r="N65" s="66"/>
     </row>
     <row r="66" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
@@ -6515,19 +6512,19 @@
       <c r="J66" s="38"/>
     </row>
     <row r="67" spans="1:14" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="79">
+      <c r="A67" s="70">
         <v>30</v>
       </c>
-      <c r="B67" s="71" t="s">
+      <c r="B67" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="71" t="s">
+      <c r="C67" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="D67" s="71" t="s">
+      <c r="D67" s="72" t="s">
         <v>334</v>
       </c>
-      <c r="E67" s="71" t="s">
+      <c r="E67" s="72" t="s">
         <v>335</v>
       </c>
       <c r="F67" s="24">
@@ -6541,11 +6538,11 @@
       <c r="J67" s="35"/>
     </row>
     <row r="68" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="80"/>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
+      <c r="A68" s="71"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
       <c r="F68" s="26">
         <v>2</v>
       </c>
@@ -6559,19 +6556,19 @@
       <c r="J68" s="37"/>
     </row>
     <row r="69" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="79">
+      <c r="A69" s="70">
         <v>31</v>
       </c>
-      <c r="B69" s="71" t="s">
+      <c r="B69" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="71" t="s">
+      <c r="C69" s="72" t="s">
         <v>338</v>
       </c>
-      <c r="D69" s="71" t="s">
+      <c r="D69" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="E69" s="71" t="s">
+      <c r="E69" s="72" t="s">
         <v>325</v>
       </c>
       <c r="F69" s="24">
@@ -6585,11 +6582,11 @@
       <c r="J69" s="35"/>
     </row>
     <row r="70" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="80"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="72"/>
-      <c r="E70" s="72"/>
+      <c r="A70" s="71"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
       <c r="F70" s="26">
         <v>2</v>
       </c>
@@ -6658,7 +6655,7 @@
       </c>
       <c r="J72" s="52"/>
       <c r="N72" s="65" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6680,19 +6677,19 @@
       <c r="N73" s="67"/>
     </row>
     <row r="74" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="91">
+      <c r="A74" s="102">
         <v>34</v>
       </c>
-      <c r="B74" s="99" t="s">
+      <c r="B74" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="C74" s="99" t="s">
+      <c r="C74" s="97" t="s">
         <v>194</v>
       </c>
-      <c r="D74" s="99" t="s">
+      <c r="D74" s="97" t="s">
         <v>352</v>
       </c>
-      <c r="E74" s="99" t="s">
+      <c r="E74" s="97" t="s">
         <v>353</v>
       </c>
       <c r="F74" s="22">
@@ -6704,19 +6701,19 @@
       <c r="H74" s="47"/>
       <c r="I74" s="33"/>
       <c r="J74" s="23"/>
-      <c r="K74" s="147"/>
-      <c r="L74" s="146"/>
-      <c r="M74" s="146"/>
+      <c r="K74" s="140"/>
+      <c r="L74" s="139"/>
+      <c r="M74" s="139"/>
       <c r="N74" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="82"/>
-      <c r="B75" s="70"/>
-      <c r="C75" s="70"/>
-      <c r="D75" s="70"/>
-      <c r="E75" s="70"/>
+      <c r="A75" s="83"/>
+      <c r="B75" s="86"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="86"/>
       <c r="F75" s="24">
         <v>2</v>
       </c>
@@ -6728,17 +6725,17 @@
       </c>
       <c r="I75" s="34"/>
       <c r="J75" s="35"/>
-      <c r="K75" s="147"/>
-      <c r="L75" s="146"/>
-      <c r="M75" s="146"/>
+      <c r="K75" s="140"/>
+      <c r="L75" s="139"/>
+      <c r="M75" s="139"/>
       <c r="N75" s="66"/>
     </row>
     <row r="76" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="82"/>
-      <c r="B76" s="70"/>
-      <c r="C76" s="70"/>
-      <c r="D76" s="70"/>
-      <c r="E76" s="70"/>
+      <c r="A76" s="83"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="86"/>
+      <c r="D76" s="86"/>
+      <c r="E76" s="86"/>
       <c r="F76" s="26">
         <v>3</v>
       </c>
@@ -6748,13 +6745,13 @@
       <c r="H76" s="49"/>
       <c r="I76" s="36"/>
       <c r="J76" s="37"/>
-      <c r="K76" s="147"/>
-      <c r="L76" s="146"/>
-      <c r="M76" s="146"/>
+      <c r="K76" s="140"/>
+      <c r="L76" s="139"/>
+      <c r="M76" s="139"/>
       <c r="N76" s="66"/>
     </row>
     <row r="77" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="83"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="69"/>
       <c r="C77" s="69"/>
       <c r="D77" s="69"/>
@@ -6770,13 +6767,13 @@
         <v>359</v>
       </c>
       <c r="J77" s="35"/>
-      <c r="K77" s="147"/>
-      <c r="L77" s="146"/>
-      <c r="M77" s="146"/>
+      <c r="K77" s="140"/>
+      <c r="L77" s="139"/>
+      <c r="M77" s="139"/>
       <c r="N77" s="66"/>
     </row>
     <row r="78" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="90">
+      <c r="A78" s="89">
         <v>35</v>
       </c>
       <c r="B78" s="68" t="s">
@@ -6800,19 +6797,19 @@
       <c r="H78" s="49"/>
       <c r="I78" s="36"/>
       <c r="J78" s="38"/>
-      <c r="K78" s="147"/>
-      <c r="L78" s="146"/>
-      <c r="M78" s="146"/>
+      <c r="K78" s="140"/>
+      <c r="L78" s="139"/>
+      <c r="M78" s="139"/>
       <c r="N78" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="82"/>
-      <c r="B79" s="70"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
+      <c r="A79" s="83"/>
+      <c r="B79" s="86"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="86"/>
+      <c r="E79" s="86"/>
       <c r="F79" s="24">
         <v>2</v>
       </c>
@@ -6824,17 +6821,17 @@
       </c>
       <c r="I79" s="34"/>
       <c r="J79" s="35"/>
-      <c r="K79" s="147"/>
-      <c r="L79" s="146"/>
-      <c r="M79" s="146"/>
+      <c r="K79" s="140"/>
+      <c r="L79" s="139"/>
+      <c r="M79" s="139"/>
       <c r="N79" s="66"/>
     </row>
     <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="82"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
+      <c r="A80" s="83"/>
+      <c r="B80" s="86"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="86"/>
+      <c r="E80" s="86"/>
       <c r="F80" s="26">
         <v>3</v>
       </c>
@@ -6844,13 +6841,13 @@
       <c r="H80" s="49"/>
       <c r="I80" s="36"/>
       <c r="J80" s="37"/>
-      <c r="K80" s="147"/>
-      <c r="L80" s="146"/>
-      <c r="M80" s="146"/>
+      <c r="K80" s="140"/>
+      <c r="L80" s="139"/>
+      <c r="M80" s="139"/>
       <c r="N80" s="66"/>
     </row>
     <row r="81" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="83"/>
+      <c r="A81" s="84"/>
       <c r="B81" s="69"/>
       <c r="C81" s="69"/>
       <c r="D81" s="69"/>
@@ -6866,13 +6863,13 @@
         <v>365</v>
       </c>
       <c r="J81" s="35"/>
-      <c r="K81" s="147"/>
-      <c r="L81" s="146"/>
-      <c r="M81" s="146"/>
+      <c r="K81" s="140"/>
+      <c r="L81" s="139"/>
+      <c r="M81" s="139"/>
       <c r="N81" s="66"/>
     </row>
     <row r="82" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="90">
+      <c r="A82" s="89">
         <v>36</v>
       </c>
       <c r="B82" s="68" t="s">
@@ -6900,7 +6897,7 @@
       <c r="J82" s="37"/>
     </row>
     <row r="83" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="83"/>
+      <c r="A83" s="84"/>
       <c r="B83" s="69"/>
       <c r="C83" s="69"/>
       <c r="D83" s="69"/>
@@ -6918,7 +6915,7 @@
       <c r="J83" s="35"/>
     </row>
     <row r="84" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="90">
+      <c r="A84" s="89">
         <v>37</v>
       </c>
       <c r="B84" s="68" t="s">
@@ -6942,15 +6939,15 @@
       <c r="H84" s="49"/>
       <c r="I84" s="36"/>
       <c r="J84" s="38"/>
-      <c r="K84" s="147"/>
-      <c r="L84" s="146"/>
-      <c r="M84" s="146"/>
+      <c r="K84" s="140"/>
+      <c r="L84" s="139"/>
+      <c r="M84" s="139"/>
       <c r="N84" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="83"/>
+      <c r="A85" s="84"/>
       <c r="B85" s="69"/>
       <c r="C85" s="69"/>
       <c r="D85" s="69"/>
@@ -6966,13 +6963,13 @@
         <v>376</v>
       </c>
       <c r="J85" s="35"/>
-      <c r="K85" s="147"/>
-      <c r="L85" s="146"/>
-      <c r="M85" s="146"/>
+      <c r="K85" s="140"/>
+      <c r="L85" s="139"/>
+      <c r="M85" s="139"/>
       <c r="N85" s="66"/>
     </row>
     <row r="86" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="90">
+      <c r="A86" s="89">
         <v>38</v>
       </c>
       <c r="B86" s="68" t="s">
@@ -7000,7 +6997,7 @@
       <c r="J86" s="37"/>
     </row>
     <row r="87" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="83"/>
+      <c r="A87" s="84"/>
       <c r="B87" s="69"/>
       <c r="C87" s="69"/>
       <c r="D87" s="69"/>
@@ -7046,19 +7043,19 @@
       <c r="J88" s="38"/>
     </row>
     <row r="89" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="79">
+      <c r="A89" s="70">
         <v>40</v>
       </c>
-      <c r="B89" s="71" t="s">
+      <c r="B89" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="C89" s="71" t="s">
+      <c r="C89" s="72" t="s">
         <v>389</v>
       </c>
-      <c r="D89" s="71" t="s">
+      <c r="D89" s="72" t="s">
         <v>390</v>
       </c>
-      <c r="E89" s="71" t="s">
+      <c r="E89" s="72" t="s">
         <v>391</v>
       </c>
       <c r="F89" s="24">
@@ -7073,10 +7070,10 @@
     </row>
     <row r="90" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="133"/>
-      <c r="B90" s="108"/>
-      <c r="C90" s="108"/>
-      <c r="D90" s="108"/>
-      <c r="E90" s="108"/>
+      <c r="B90" s="115"/>
+      <c r="C90" s="115"/>
+      <c r="D90" s="115"/>
+      <c r="E90" s="115"/>
       <c r="F90" s="41">
         <v>2</v>
       </c>
@@ -7108,19 +7105,19 @@
       <c r="N91" s="100"/>
     </row>
     <row r="92" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="91">
+      <c r="A92" s="102">
         <v>41</v>
       </c>
-      <c r="B92" s="92" t="s">
+      <c r="B92" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="C92" s="99" t="s">
+      <c r="C92" s="97" t="s">
         <v>395</v>
       </c>
-      <c r="D92" s="99" t="s">
+      <c r="D92" s="97" t="s">
         <v>396</v>
       </c>
-      <c r="E92" s="99" t="s">
+      <c r="E92" s="97" t="s">
         <v>397</v>
       </c>
       <c r="F92" s="22">
@@ -7134,19 +7131,19 @@
       </c>
       <c r="I92" s="33"/>
       <c r="J92" s="23"/>
-      <c r="K92" s="180"/>
-      <c r="L92" s="179"/>
-      <c r="M92" s="179"/>
-      <c r="N92" s="178" t="s">
-        <v>837</v>
+      <c r="K92" s="155"/>
+      <c r="L92" s="154"/>
+      <c r="M92" s="154"/>
+      <c r="N92" s="101" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="82"/>
-      <c r="B93" s="93"/>
-      <c r="C93" s="70"/>
-      <c r="D93" s="70"/>
-      <c r="E93" s="70"/>
+      <c r="A93" s="83"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="86"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="86"/>
       <c r="F93" s="24">
         <v>2</v>
       </c>
@@ -7156,14 +7153,14 @@
       <c r="H93" s="25"/>
       <c r="I93" s="34"/>
       <c r="J93" s="35"/>
-      <c r="K93" s="147"/>
-      <c r="L93" s="146"/>
-      <c r="M93" s="183"/>
+      <c r="K93" s="140"/>
+      <c r="L93" s="139"/>
+      <c r="M93" s="139"/>
       <c r="N93" s="66"/>
     </row>
     <row r="94" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="83"/>
-      <c r="B94" s="94"/>
+      <c r="A94" s="84"/>
+      <c r="B94" s="96"/>
       <c r="C94" s="69"/>
       <c r="D94" s="69"/>
       <c r="E94" s="69"/>
@@ -7178,25 +7175,25 @@
         <v>402</v>
       </c>
       <c r="J94" s="37"/>
-      <c r="K94" s="147"/>
-      <c r="L94" s="146"/>
-      <c r="M94" s="183"/>
+      <c r="K94" s="140"/>
+      <c r="L94" s="139"/>
+      <c r="M94" s="139"/>
       <c r="N94" s="66"/>
     </row>
     <row r="95" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="79">
+      <c r="A95" s="70">
         <v>42</v>
       </c>
-      <c r="B95" s="73" t="s">
+      <c r="B95" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="C95" s="71" t="s">
+      <c r="C95" s="72" t="s">
         <v>403</v>
       </c>
-      <c r="D95" s="71" t="s">
+      <c r="D95" s="72" t="s">
         <v>404</v>
       </c>
-      <c r="E95" s="71" t="s">
+      <c r="E95" s="72" t="s">
         <v>405</v>
       </c>
       <c r="F95" s="24">
@@ -7210,19 +7207,19 @@
       </c>
       <c r="I95" s="34"/>
       <c r="J95" s="29"/>
-      <c r="K95" s="147"/>
-      <c r="L95" s="146"/>
-      <c r="M95" s="146"/>
+      <c r="K95" s="140"/>
+      <c r="L95" s="139"/>
+      <c r="M95" s="139"/>
       <c r="N95" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
-      <c r="B96" s="74"/>
-      <c r="C96" s="72"/>
-      <c r="D96" s="72"/>
-      <c r="E96" s="72"/>
+      <c r="A96" s="71"/>
+      <c r="B96" s="107"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="73"/>
       <c r="F96" s="26">
         <v>2</v>
       </c>
@@ -7234,25 +7231,25 @@
         <v>408</v>
       </c>
       <c r="J96" s="37"/>
-      <c r="K96" s="147"/>
-      <c r="L96" s="146"/>
-      <c r="M96" s="146"/>
+      <c r="K96" s="140"/>
+      <c r="L96" s="139"/>
+      <c r="M96" s="139"/>
       <c r="N96" s="66"/>
     </row>
     <row r="97" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="79">
+      <c r="A97" s="70">
         <v>43</v>
       </c>
-      <c r="B97" s="77" t="s">
+      <c r="B97" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C97" s="71" t="s">
+      <c r="C97" s="72" t="s">
         <v>409</v>
       </c>
-      <c r="D97" s="71" t="s">
+      <c r="D97" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="E97" s="71" t="s">
+      <c r="E97" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F97" s="24">
@@ -7266,19 +7263,19 @@
       </c>
       <c r="I97" s="34"/>
       <c r="J97" s="29"/>
-      <c r="K97" s="147"/>
-      <c r="L97" s="146"/>
-      <c r="M97" s="146"/>
+      <c r="K97" s="140"/>
+      <c r="L97" s="139"/>
+      <c r="M97" s="139"/>
       <c r="N97" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="80"/>
-      <c r="B98" s="78"/>
-      <c r="C98" s="72"/>
-      <c r="D98" s="72"/>
-      <c r="E98" s="72"/>
+      <c r="A98" s="71"/>
+      <c r="B98" s="75"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="73"/>
+      <c r="E98" s="73"/>
       <c r="F98" s="26">
         <v>2</v>
       </c>
@@ -7290,25 +7287,25 @@
         <v>413</v>
       </c>
       <c r="J98" s="37"/>
-      <c r="K98" s="147"/>
-      <c r="L98" s="146"/>
-      <c r="M98" s="146"/>
+      <c r="K98" s="140"/>
+      <c r="L98" s="139"/>
+      <c r="M98" s="139"/>
       <c r="N98" s="66"/>
     </row>
     <row r="99" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="79">
+      <c r="A99" s="70">
         <v>44</v>
       </c>
-      <c r="B99" s="77" t="s">
+      <c r="B99" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C99" s="71" t="s">
+      <c r="C99" s="72" t="s">
         <v>414</v>
       </c>
-      <c r="D99" s="71" t="s">
+      <c r="D99" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="E99" s="71" t="s">
+      <c r="E99" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F99" s="24">
@@ -7322,19 +7319,19 @@
       </c>
       <c r="I99" s="34"/>
       <c r="J99" s="29"/>
-      <c r="K99" s="147"/>
-      <c r="L99" s="146"/>
-      <c r="M99" s="146"/>
+      <c r="K99" s="140"/>
+      <c r="L99" s="139"/>
+      <c r="M99" s="139"/>
       <c r="N99" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="80"/>
-      <c r="B100" s="78"/>
-      <c r="C100" s="72"/>
-      <c r="D100" s="72"/>
-      <c r="E100" s="72"/>
+      <c r="A100" s="71"/>
+      <c r="B100" s="75"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="73"/>
       <c r="F100" s="26">
         <v>2</v>
       </c>
@@ -7346,25 +7343,25 @@
         <v>418</v>
       </c>
       <c r="J100" s="37"/>
-      <c r="K100" s="147"/>
-      <c r="L100" s="146"/>
-      <c r="M100" s="146"/>
+      <c r="K100" s="140"/>
+      <c r="L100" s="139"/>
+      <c r="M100" s="139"/>
       <c r="N100" s="66"/>
     </row>
     <row r="101" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="79">
+      <c r="A101" s="70">
         <v>45</v>
       </c>
-      <c r="B101" s="77" t="s">
+      <c r="B101" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C101" s="71" t="s">
+      <c r="C101" s="72" t="s">
         <v>419</v>
       </c>
-      <c r="D101" s="71" t="s">
+      <c r="D101" s="72" t="s">
         <v>420</v>
       </c>
-      <c r="E101" s="71" t="s">
+      <c r="E101" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F101" s="24">
@@ -7378,19 +7375,19 @@
       </c>
       <c r="I101" s="34"/>
       <c r="J101" s="35"/>
-      <c r="K101" s="147"/>
-      <c r="L101" s="146"/>
-      <c r="M101" s="146"/>
+      <c r="K101" s="140"/>
+      <c r="L101" s="139"/>
+      <c r="M101" s="139"/>
       <c r="N101" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="80"/>
-      <c r="B102" s="78"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
+      <c r="A102" s="71"/>
+      <c r="B102" s="75"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
       <c r="F102" s="26">
         <v>2</v>
       </c>
@@ -7402,25 +7399,25 @@
         <v>423</v>
       </c>
       <c r="J102" s="37"/>
-      <c r="K102" s="147"/>
-      <c r="L102" s="146"/>
-      <c r="M102" s="146"/>
+      <c r="K102" s="140"/>
+      <c r="L102" s="139"/>
+      <c r="M102" s="139"/>
       <c r="N102" s="66"/>
     </row>
     <row r="103" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="79">
+      <c r="A103" s="70">
         <v>46</v>
       </c>
-      <c r="B103" s="95" t="s">
+      <c r="B103" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="C103" s="71" t="s">
+      <c r="C103" s="72" t="s">
         <v>424</v>
       </c>
-      <c r="D103" s="71" t="s">
+      <c r="D103" s="72" t="s">
         <v>425</v>
       </c>
-      <c r="E103" s="71" t="s">
+      <c r="E103" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F103" s="24">
@@ -7434,19 +7431,19 @@
       </c>
       <c r="I103" s="34"/>
       <c r="J103" s="35"/>
-      <c r="K103" s="147"/>
-      <c r="L103" s="146"/>
-      <c r="M103" s="146"/>
+      <c r="K103" s="140"/>
+      <c r="L103" s="139"/>
+      <c r="M103" s="139"/>
       <c r="N103" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="80"/>
-      <c r="B104" s="96"/>
-      <c r="C104" s="72"/>
-      <c r="D104" s="72"/>
-      <c r="E104" s="72"/>
+      <c r="A104" s="71"/>
+      <c r="B104" s="81"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="73"/>
       <c r="F104" s="26">
         <v>2</v>
       </c>
@@ -7458,25 +7455,25 @@
         <v>428</v>
       </c>
       <c r="J104" s="37"/>
-      <c r="K104" s="147"/>
-      <c r="L104" s="146"/>
-      <c r="M104" s="146"/>
+      <c r="K104" s="140"/>
+      <c r="L104" s="139"/>
+      <c r="M104" s="139"/>
       <c r="N104" s="66"/>
     </row>
     <row r="105" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="79">
+      <c r="A105" s="70">
         <v>47</v>
       </c>
-      <c r="B105" s="75" t="s">
+      <c r="B105" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C105" s="71" t="s">
+      <c r="C105" s="72" t="s">
         <v>429</v>
       </c>
-      <c r="D105" s="71" t="s">
+      <c r="D105" s="72" t="s">
         <v>430</v>
       </c>
-      <c r="E105" s="71" t="s">
+      <c r="E105" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F105" s="24">
@@ -7490,19 +7487,19 @@
       </c>
       <c r="I105" s="34"/>
       <c r="J105" s="35"/>
-      <c r="K105" s="147"/>
-      <c r="L105" s="146"/>
-      <c r="M105" s="146"/>
+      <c r="K105" s="140"/>
+      <c r="L105" s="139"/>
+      <c r="M105" s="139"/>
       <c r="N105" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="80"/>
-      <c r="B106" s="76"/>
-      <c r="C106" s="72"/>
-      <c r="D106" s="72"/>
-      <c r="E106" s="72"/>
+      <c r="A106" s="71"/>
+      <c r="B106" s="79"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="73"/>
+      <c r="E106" s="73"/>
       <c r="F106" s="26">
         <v>2</v>
       </c>
@@ -7514,25 +7511,25 @@
         <v>433</v>
       </c>
       <c r="J106" s="37"/>
-      <c r="K106" s="147"/>
-      <c r="L106" s="146"/>
-      <c r="M106" s="146"/>
+      <c r="K106" s="140"/>
+      <c r="L106" s="139"/>
+      <c r="M106" s="139"/>
       <c r="N106" s="66"/>
     </row>
     <row r="107" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="79">
+      <c r="A107" s="70">
         <v>48</v>
       </c>
-      <c r="B107" s="75" t="s">
+      <c r="B107" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="71" t="s">
+      <c r="C107" s="72" t="s">
         <v>434</v>
       </c>
-      <c r="D107" s="71" t="s">
+      <c r="D107" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="E107" s="71" t="s">
+      <c r="E107" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F107" s="24">
@@ -7548,11 +7545,11 @@
       <c r="J107" s="35"/>
     </row>
     <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="80"/>
-      <c r="B108" s="76"/>
-      <c r="C108" s="72"/>
-      <c r="D108" s="72"/>
-      <c r="E108" s="72"/>
+      <c r="A108" s="71"/>
+      <c r="B108" s="79"/>
+      <c r="C108" s="73"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="73"/>
       <c r="F108" s="26">
         <v>2</v>
       </c>
@@ -7566,19 +7563,19 @@
       <c r="J108" s="37"/>
     </row>
     <row r="109" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="79">
+      <c r="A109" s="70">
         <v>49</v>
       </c>
-      <c r="B109" s="97" t="s">
+      <c r="B109" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C109" s="71" t="s">
+      <c r="C109" s="72" t="s">
         <v>439</v>
       </c>
-      <c r="D109" s="71" t="s">
+      <c r="D109" s="72" t="s">
         <v>440</v>
       </c>
-      <c r="E109" s="71" t="s">
+      <c r="E109" s="72" t="s">
         <v>441</v>
       </c>
       <c r="F109" s="24">
@@ -7592,19 +7589,19 @@
       </c>
       <c r="I109" s="34"/>
       <c r="J109" s="29"/>
-      <c r="K109" s="147"/>
-      <c r="L109" s="146"/>
-      <c r="M109" s="146"/>
+      <c r="K109" s="140"/>
+      <c r="L109" s="139"/>
+      <c r="M109" s="139"/>
       <c r="N109" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="80"/>
-      <c r="B110" s="98"/>
-      <c r="C110" s="72"/>
-      <c r="D110" s="72"/>
-      <c r="E110" s="72"/>
+      <c r="A110" s="71"/>
+      <c r="B110" s="77"/>
+      <c r="C110" s="73"/>
+      <c r="D110" s="73"/>
+      <c r="E110" s="73"/>
       <c r="F110" s="26">
         <v>2</v>
       </c>
@@ -7616,25 +7613,25 @@
         <v>445</v>
       </c>
       <c r="J110" s="37"/>
-      <c r="K110" s="147"/>
-      <c r="L110" s="146"/>
-      <c r="M110" s="146"/>
+      <c r="K110" s="140"/>
+      <c r="L110" s="139"/>
+      <c r="M110" s="139"/>
       <c r="N110" s="66"/>
     </row>
     <row r="111" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="79">
+      <c r="A111" s="70">
         <v>50</v>
       </c>
-      <c r="B111" s="97" t="s">
+      <c r="B111" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C111" s="71" t="s">
+      <c r="C111" s="72" t="s">
         <v>446</v>
       </c>
-      <c r="D111" s="71" t="s">
+      <c r="D111" s="72" t="s">
         <v>447</v>
       </c>
-      <c r="E111" s="71" t="s">
+      <c r="E111" s="72" t="s">
         <v>441</v>
       </c>
       <c r="F111" s="24">
@@ -7648,19 +7645,19 @@
       </c>
       <c r="I111" s="34"/>
       <c r="J111" s="29"/>
-      <c r="K111" s="147"/>
-      <c r="L111" s="146"/>
-      <c r="M111" s="146"/>
+      <c r="K111" s="140"/>
+      <c r="L111" s="139"/>
+      <c r="M111" s="139"/>
       <c r="N111" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="80"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="72"/>
-      <c r="D112" s="72"/>
-      <c r="E112" s="72"/>
+      <c r="A112" s="71"/>
+      <c r="B112" s="77"/>
+      <c r="C112" s="73"/>
+      <c r="D112" s="73"/>
+      <c r="E112" s="73"/>
       <c r="F112" s="26">
         <v>2</v>
       </c>
@@ -7672,25 +7669,25 @@
         <v>448</v>
       </c>
       <c r="J112" s="37"/>
-      <c r="K112" s="147"/>
-      <c r="L112" s="146"/>
-      <c r="M112" s="146"/>
+      <c r="K112" s="140"/>
+      <c r="L112" s="139"/>
+      <c r="M112" s="139"/>
       <c r="N112" s="66"/>
     </row>
     <row r="113" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="79">
+      <c r="A113" s="70">
         <v>51</v>
       </c>
-      <c r="B113" s="75" t="s">
+      <c r="B113" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="71" t="s">
+      <c r="C113" s="72" t="s">
         <v>449</v>
       </c>
-      <c r="D113" s="71" t="s">
+      <c r="D113" s="72" t="s">
         <v>450</v>
       </c>
-      <c r="E113" s="71" t="s">
+      <c r="E113" s="72" t="s">
         <v>451</v>
       </c>
       <c r="F113" s="24">
@@ -7706,11 +7703,11 @@
       <c r="J113" s="29"/>
     </row>
     <row r="114" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="80"/>
-      <c r="B114" s="76"/>
-      <c r="C114" s="72"/>
-      <c r="D114" s="72"/>
-      <c r="E114" s="72"/>
+      <c r="A114" s="71"/>
+      <c r="B114" s="79"/>
+      <c r="C114" s="73"/>
+      <c r="D114" s="73"/>
+      <c r="E114" s="73"/>
       <c r="F114" s="26">
         <v>2</v>
       </c>
@@ -7724,19 +7721,19 @@
       <c r="J114" s="37"/>
     </row>
     <row r="115" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="79">
+      <c r="A115" s="70">
         <v>52</v>
       </c>
-      <c r="B115" s="75" t="s">
+      <c r="B115" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C115" s="71" t="s">
+      <c r="C115" s="72" t="s">
         <v>455</v>
       </c>
-      <c r="D115" s="71" t="s">
+      <c r="D115" s="72" t="s">
         <v>456</v>
       </c>
-      <c r="E115" s="71" t="s">
+      <c r="E115" s="72" t="s">
         <v>457</v>
       </c>
       <c r="F115" s="24">
@@ -7750,11 +7747,11 @@
       <c r="J115" s="35"/>
     </row>
     <row r="116" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="80"/>
-      <c r="B116" s="76"/>
-      <c r="C116" s="72"/>
-      <c r="D116" s="72"/>
-      <c r="E116" s="72"/>
+      <c r="A116" s="71"/>
+      <c r="B116" s="79"/>
+      <c r="C116" s="73"/>
+      <c r="D116" s="73"/>
+      <c r="E116" s="73"/>
       <c r="F116" s="26">
         <v>2</v>
       </c>
@@ -7768,19 +7765,19 @@
       <c r="J116" s="37"/>
     </row>
     <row r="117" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="79">
+      <c r="A117" s="70">
         <v>53</v>
       </c>
-      <c r="B117" s="75" t="s">
+      <c r="B117" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C117" s="71" t="s">
+      <c r="C117" s="72" t="s">
         <v>461</v>
       </c>
-      <c r="D117" s="71" t="s">
+      <c r="D117" s="72" t="s">
         <v>462</v>
       </c>
-      <c r="E117" s="71" t="s">
+      <c r="E117" s="72" t="s">
         <v>457</v>
       </c>
       <c r="F117" s="24">
@@ -7794,11 +7791,11 @@
       <c r="J117" s="35"/>
     </row>
     <row r="118" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="80"/>
-      <c r="B118" s="76"/>
-      <c r="C118" s="72"/>
-      <c r="D118" s="72"/>
-      <c r="E118" s="72"/>
+      <c r="A118" s="71"/>
+      <c r="B118" s="79"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="73"/>
+      <c r="E118" s="73"/>
       <c r="F118" s="26">
         <v>2</v>
       </c>
@@ -7812,19 +7809,19 @@
       <c r="J118" s="37"/>
     </row>
     <row r="119" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="79">
+      <c r="A119" s="70">
         <v>54</v>
       </c>
-      <c r="B119" s="75" t="s">
+      <c r="B119" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C119" s="71" t="s">
+      <c r="C119" s="72" t="s">
         <v>465</v>
       </c>
-      <c r="D119" s="71" t="s">
+      <c r="D119" s="72" t="s">
         <v>466</v>
       </c>
-      <c r="E119" s="71" t="s">
+      <c r="E119" s="72" t="s">
         <v>467</v>
       </c>
       <c r="F119" s="24">
@@ -7838,11 +7835,11 @@
       <c r="J119" s="35"/>
     </row>
     <row r="120" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="80"/>
-      <c r="B120" s="76"/>
-      <c r="C120" s="72"/>
-      <c r="D120" s="72"/>
-      <c r="E120" s="72"/>
+      <c r="A120" s="71"/>
+      <c r="B120" s="79"/>
+      <c r="C120" s="73"/>
+      <c r="D120" s="73"/>
+      <c r="E120" s="73"/>
       <c r="F120" s="26">
         <v>2</v>
       </c>
@@ -7856,19 +7853,19 @@
       <c r="J120" s="37"/>
     </row>
     <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="79">
+      <c r="A121" s="70">
         <v>55</v>
       </c>
-      <c r="B121" s="77" t="s">
+      <c r="B121" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C121" s="71" t="s">
+      <c r="C121" s="72" t="s">
         <v>471</v>
       </c>
-      <c r="D121" s="71" t="s">
+      <c r="D121" s="72" t="s">
         <v>472</v>
       </c>
-      <c r="E121" s="71" t="s">
+      <c r="E121" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F121" s="24">
@@ -7884,11 +7881,11 @@
       <c r="J121" s="35"/>
     </row>
     <row r="122" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="80"/>
-      <c r="B122" s="78"/>
-      <c r="C122" s="72"/>
-      <c r="D122" s="72"/>
-      <c r="E122" s="72"/>
+      <c r="A122" s="71"/>
+      <c r="B122" s="75"/>
+      <c r="C122" s="73"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="73"/>
       <c r="F122" s="26">
         <v>2</v>
       </c>
@@ -7902,19 +7899,19 @@
       <c r="J122" s="37"/>
     </row>
     <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="79">
+      <c r="A123" s="70">
         <v>56</v>
       </c>
-      <c r="B123" s="75" t="s">
+      <c r="B123" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C123" s="71" t="s">
+      <c r="C123" s="72" t="s">
         <v>476</v>
       </c>
-      <c r="D123" s="71" t="s">
+      <c r="D123" s="72" t="s">
         <v>477</v>
       </c>
-      <c r="E123" s="71" t="s">
+      <c r="E123" s="72" t="s">
         <v>441</v>
       </c>
       <c r="F123" s="24">
@@ -7928,11 +7925,11 @@
       <c r="J123" s="29"/>
     </row>
     <row r="124" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="80"/>
-      <c r="B124" s="76"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
+      <c r="A124" s="71"/>
+      <c r="B124" s="79"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
       <c r="F124" s="26">
         <v>2</v>
       </c>
@@ -7946,19 +7943,19 @@
       <c r="J124" s="37"/>
     </row>
     <row r="125" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="79">
+      <c r="A125" s="70">
         <v>57</v>
       </c>
-      <c r="B125" s="75" t="s">
+      <c r="B125" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C125" s="71" t="s">
+      <c r="C125" s="72" t="s">
         <v>481</v>
       </c>
-      <c r="D125" s="71" t="s">
+      <c r="D125" s="72" t="s">
         <v>482</v>
       </c>
-      <c r="E125" s="71" t="s">
+      <c r="E125" s="72" t="s">
         <v>483</v>
       </c>
       <c r="F125" s="24">
@@ -7972,11 +7969,11 @@
       <c r="J125" s="29"/>
     </row>
     <row r="126" spans="1:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="80"/>
-      <c r="B126" s="76"/>
-      <c r="C126" s="72"/>
-      <c r="D126" s="72"/>
-      <c r="E126" s="72"/>
+      <c r="A126" s="71"/>
+      <c r="B126" s="79"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="73"/>
+      <c r="E126" s="73"/>
       <c r="F126" s="26">
         <v>2</v>
       </c>
@@ -7990,19 +7987,19 @@
       <c r="J126" s="37"/>
     </row>
     <row r="127" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="79">
+      <c r="A127" s="70">
         <v>58</v>
       </c>
-      <c r="B127" s="75" t="s">
+      <c r="B127" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="C127" s="71" t="s">
+      <c r="C127" s="72" t="s">
         <v>487</v>
       </c>
-      <c r="D127" s="71" t="s">
+      <c r="D127" s="72" t="s">
         <v>488</v>
       </c>
-      <c r="E127" s="71" t="s">
+      <c r="E127" s="72" t="s">
         <v>353</v>
       </c>
       <c r="F127" s="24">
@@ -8018,11 +8015,11 @@
       <c r="J127" s="29"/>
     </row>
     <row r="128" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="80"/>
-      <c r="B128" s="76"/>
-      <c r="C128" s="72"/>
-      <c r="D128" s="72"/>
-      <c r="E128" s="72"/>
+      <c r="A128" s="71"/>
+      <c r="B128" s="79"/>
+      <c r="C128" s="73"/>
+      <c r="D128" s="73"/>
+      <c r="E128" s="73"/>
       <c r="F128" s="26">
         <v>2</v>
       </c>
@@ -8064,10 +8061,10 @@
       <c r="J129" s="29"/>
     </row>
     <row r="130" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="90">
+      <c r="A130" s="89">
         <v>60</v>
       </c>
-      <c r="B130" s="114" t="s">
+      <c r="B130" s="117" t="s">
         <v>112</v>
       </c>
       <c r="C130" s="68" t="s">
@@ -8090,19 +8087,19 @@
       </c>
       <c r="I130" s="36"/>
       <c r="J130" s="38"/>
-      <c r="K130" s="147"/>
-      <c r="L130" s="146"/>
-      <c r="M130" s="146"/>
+      <c r="K130" s="140"/>
+      <c r="L130" s="139"/>
+      <c r="M130" s="139"/>
       <c r="N130" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="131" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="113"/>
-      <c r="B131" s="117"/>
-      <c r="C131" s="86"/>
-      <c r="D131" s="86"/>
-      <c r="E131" s="86"/>
+      <c r="A131" s="116"/>
+      <c r="B131" s="120"/>
+      <c r="C131" s="90"/>
+      <c r="D131" s="90"/>
+      <c r="E131" s="90"/>
       <c r="F131" s="31">
         <v>2</v>
       </c>
@@ -8114,43 +8111,43 @@
         <v>501</v>
       </c>
       <c r="J131" s="57"/>
-      <c r="K131" s="182"/>
-      <c r="L131" s="181"/>
-      <c r="M131" s="181"/>
+      <c r="K131" s="153"/>
+      <c r="L131" s="152"/>
+      <c r="M131" s="152"/>
       <c r="N131" s="66"/>
     </row>
     <row r="132" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="118" t="s">
+      <c r="A132" s="145" t="s">
         <v>184</v>
       </c>
-      <c r="B132" s="118"/>
-      <c r="C132" s="118"/>
-      <c r="D132" s="118"/>
-      <c r="E132" s="118"/>
-      <c r="F132" s="118"/>
-      <c r="G132" s="118"/>
-      <c r="H132" s="118"/>
-      <c r="I132" s="118"/>
-      <c r="J132" s="118"/>
-      <c r="K132" s="118"/>
-      <c r="L132" s="118"/>
-      <c r="M132" s="118"/>
-      <c r="N132" s="118"/>
+      <c r="B132" s="145"/>
+      <c r="C132" s="145"/>
+      <c r="D132" s="145"/>
+      <c r="E132" s="145"/>
+      <c r="F132" s="145"/>
+      <c r="G132" s="145"/>
+      <c r="H132" s="145"/>
+      <c r="I132" s="145"/>
+      <c r="J132" s="145"/>
+      <c r="K132" s="145"/>
+      <c r="L132" s="145"/>
+      <c r="M132" s="145"/>
+      <c r="N132" s="145"/>
     </row>
     <row r="133" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="91">
+      <c r="A133" s="102">
         <v>61</v>
       </c>
-      <c r="B133" s="99" t="s">
+      <c r="B133" s="97" t="s">
         <v>127</v>
       </c>
-      <c r="C133" s="99" t="s">
+      <c r="C133" s="97" t="s">
         <v>502</v>
       </c>
-      <c r="D133" s="99" t="s">
+      <c r="D133" s="97" t="s">
         <v>503</v>
       </c>
-      <c r="E133" s="92" t="s">
+      <c r="E133" s="95" t="s">
         <v>504</v>
       </c>
       <c r="F133" s="22">
@@ -8160,23 +8157,23 @@
         <v>505</v>
       </c>
       <c r="H133" s="21" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="I133" s="33"/>
       <c r="J133" s="23"/>
-      <c r="K133" s="147"/>
-      <c r="L133" s="146"/>
-      <c r="M133" s="146"/>
+      <c r="K133" s="140"/>
+      <c r="L133" s="139"/>
+      <c r="M133" s="139"/>
       <c r="N133" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="134" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="82"/>
-      <c r="B134" s="70"/>
-      <c r="C134" s="70"/>
-      <c r="D134" s="70"/>
-      <c r="E134" s="93"/>
+      <c r="A134" s="83"/>
+      <c r="B134" s="86"/>
+      <c r="C134" s="86"/>
+      <c r="D134" s="86"/>
+      <c r="E134" s="103"/>
       <c r="F134" s="24">
         <v>2</v>
       </c>
@@ -8184,21 +8181,21 @@
         <v>506</v>
       </c>
       <c r="H134" s="25" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="I134" s="34"/>
       <c r="J134" s="35"/>
-      <c r="K134" s="147"/>
-      <c r="L134" s="146"/>
-      <c r="M134" s="146"/>
+      <c r="K134" s="140"/>
+      <c r="L134" s="139"/>
+      <c r="M134" s="139"/>
       <c r="N134" s="66"/>
     </row>
     <row r="135" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="83"/>
+      <c r="A135" s="84"/>
       <c r="B135" s="69"/>
       <c r="C135" s="69"/>
       <c r="D135" s="69"/>
-      <c r="E135" s="94"/>
+      <c r="E135" s="96"/>
       <c r="F135" s="26">
         <v>3</v>
       </c>
@@ -8207,28 +8204,28 @@
       </c>
       <c r="H135" s="27"/>
       <c r="I135" s="27" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="J135" s="37"/>
-      <c r="K135" s="147"/>
-      <c r="L135" s="146"/>
-      <c r="M135" s="146"/>
+      <c r="K135" s="140"/>
+      <c r="L135" s="139"/>
+      <c r="M135" s="139"/>
       <c r="N135" s="66"/>
     </row>
     <row r="136" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="79">
+      <c r="A136" s="70">
         <v>62</v>
       </c>
-      <c r="B136" s="71" t="s">
+      <c r="B136" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C136" s="71" t="s">
+      <c r="C136" s="72" t="s">
         <v>508</v>
       </c>
-      <c r="D136" s="71" t="s">
+      <c r="D136" s="72" t="s">
         <v>509</v>
       </c>
-      <c r="E136" s="73" t="s">
+      <c r="E136" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F136" s="24">
@@ -8238,53 +8235,53 @@
         <v>511</v>
       </c>
       <c r="H136" s="25" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="I136" s="34"/>
       <c r="J136" s="29"/>
-      <c r="K136" s="147"/>
-      <c r="L136" s="146"/>
-      <c r="M136" s="146"/>
+      <c r="K136" s="140"/>
+      <c r="L136" s="139"/>
+      <c r="M136" s="139"/>
       <c r="N136" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="137" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="80"/>
-      <c r="B137" s="72"/>
-      <c r="C137" s="72"/>
-      <c r="D137" s="72"/>
-      <c r="E137" s="74"/>
+      <c r="A137" s="71"/>
+      <c r="B137" s="73"/>
+      <c r="C137" s="73"/>
+      <c r="D137" s="73"/>
+      <c r="E137" s="107"/>
       <c r="F137" s="26">
         <v>2</v>
       </c>
       <c r="G137" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H137" s="27"/>
       <c r="I137" s="27" t="s">
         <v>513</v>
       </c>
       <c r="J137" s="37"/>
-      <c r="K137" s="147"/>
-      <c r="L137" s="146"/>
-      <c r="M137" s="146"/>
+      <c r="K137" s="140"/>
+      <c r="L137" s="139"/>
+      <c r="M137" s="139"/>
       <c r="N137" s="66"/>
     </row>
     <row r="138" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="79">
+      <c r="A138" s="70">
         <v>63</v>
       </c>
-      <c r="B138" s="71" t="s">
+      <c r="B138" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C138" s="71" t="s">
+      <c r="C138" s="72" t="s">
         <v>514</v>
       </c>
-      <c r="D138" s="71" t="s">
+      <c r="D138" s="72" t="s">
         <v>515</v>
       </c>
-      <c r="E138" s="73" t="s">
+      <c r="E138" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F138" s="24">
@@ -8294,22 +8291,22 @@
         <v>515</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="I138" s="34"/>
       <c r="J138" s="35"/>
     </row>
     <row r="139" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="80"/>
-      <c r="B139" s="72"/>
-      <c r="C139" s="72"/>
-      <c r="D139" s="72"/>
-      <c r="E139" s="74"/>
+      <c r="A139" s="71"/>
+      <c r="B139" s="73"/>
+      <c r="C139" s="73"/>
+      <c r="D139" s="73"/>
+      <c r="E139" s="107"/>
       <c r="F139" s="26">
         <v>2</v>
       </c>
       <c r="G139" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H139" s="27"/>
       <c r="I139" s="27" t="s">
@@ -8318,19 +8315,19 @@
       <c r="J139" s="37"/>
     </row>
     <row r="140" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="79">
+      <c r="A140" s="70">
         <v>64</v>
       </c>
-      <c r="B140" s="71" t="s">
+      <c r="B140" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C140" s="71" t="s">
+      <c r="C140" s="72" t="s">
         <v>517</v>
       </c>
-      <c r="D140" s="71" t="s">
+      <c r="D140" s="72" t="s">
         <v>518</v>
       </c>
-      <c r="E140" s="73" t="s">
+      <c r="E140" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F140" s="24">
@@ -8340,22 +8337,22 @@
         <v>518</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="I140" s="34"/>
       <c r="J140" s="35"/>
     </row>
     <row r="141" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="80"/>
-      <c r="B141" s="72"/>
-      <c r="C141" s="72"/>
-      <c r="D141" s="72"/>
-      <c r="E141" s="74"/>
+      <c r="A141" s="71"/>
+      <c r="B141" s="73"/>
+      <c r="C141" s="73"/>
+      <c r="D141" s="73"/>
+      <c r="E141" s="107"/>
       <c r="F141" s="26">
         <v>2</v>
       </c>
       <c r="G141" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H141" s="27"/>
       <c r="I141" s="27" t="s">
@@ -8364,19 +8361,19 @@
       <c r="J141" s="37"/>
     </row>
     <row r="142" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="79">
+      <c r="A142" s="70">
         <v>65</v>
       </c>
-      <c r="B142" s="71" t="s">
+      <c r="B142" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C142" s="71" t="s">
+      <c r="C142" s="72" t="s">
         <v>520</v>
       </c>
-      <c r="D142" s="71" t="s">
+      <c r="D142" s="72" t="s">
         <v>521</v>
       </c>
-      <c r="E142" s="73" t="s">
+      <c r="E142" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F142" s="24">
@@ -8386,22 +8383,22 @@
         <v>521</v>
       </c>
       <c r="H142" s="25" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="I142" s="34"/>
       <c r="J142" s="35"/>
     </row>
     <row r="143" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="80"/>
-      <c r="B143" s="72"/>
-      <c r="C143" s="72"/>
-      <c r="D143" s="72"/>
-      <c r="E143" s="74"/>
+      <c r="A143" s="71"/>
+      <c r="B143" s="73"/>
+      <c r="C143" s="73"/>
+      <c r="D143" s="73"/>
+      <c r="E143" s="107"/>
       <c r="F143" s="26">
         <v>2</v>
       </c>
       <c r="G143" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H143" s="27"/>
       <c r="I143" s="27" t="s">
@@ -8410,19 +8407,19 @@
       <c r="J143" s="37"/>
     </row>
     <row r="144" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="79">
+      <c r="A144" s="70">
         <v>66</v>
       </c>
-      <c r="B144" s="71" t="s">
+      <c r="B144" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C144" s="71" t="s">
+      <c r="C144" s="72" t="s">
         <v>523</v>
       </c>
-      <c r="D144" s="71" t="s">
+      <c r="D144" s="72" t="s">
         <v>524</v>
       </c>
-      <c r="E144" s="73" t="s">
+      <c r="E144" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F144" s="24">
@@ -8432,22 +8429,22 @@
         <v>524</v>
       </c>
       <c r="H144" s="25" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="I144" s="34"/>
       <c r="J144" s="35"/>
     </row>
     <row r="145" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="80"/>
-      <c r="B145" s="72"/>
-      <c r="C145" s="72"/>
-      <c r="D145" s="72"/>
-      <c r="E145" s="74"/>
+      <c r="A145" s="71"/>
+      <c r="B145" s="73"/>
+      <c r="C145" s="73"/>
+      <c r="D145" s="73"/>
+      <c r="E145" s="107"/>
       <c r="F145" s="26">
         <v>2</v>
       </c>
       <c r="G145" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H145" s="27"/>
       <c r="I145" s="27" t="s">
@@ -8456,19 +8453,19 @@
       <c r="J145" s="37"/>
     </row>
     <row r="146" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="79">
+      <c r="A146" s="70">
         <v>67</v>
       </c>
-      <c r="B146" s="71" t="s">
+      <c r="B146" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="C146" s="71" t="s">
+      <c r="C146" s="72" t="s">
         <v>526</v>
       </c>
-      <c r="D146" s="71" t="s">
+      <c r="D146" s="72" t="s">
         <v>527</v>
       </c>
-      <c r="E146" s="73" t="s">
+      <c r="E146" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F146" s="24">
@@ -8478,22 +8475,22 @@
         <v>528</v>
       </c>
       <c r="H146" s="25" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="I146" s="34"/>
       <c r="J146" s="35"/>
     </row>
     <row r="147" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="80"/>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="74"/>
+      <c r="A147" s="71"/>
+      <c r="B147" s="73"/>
+      <c r="C147" s="73"/>
+      <c r="D147" s="73"/>
+      <c r="E147" s="107"/>
       <c r="F147" s="26">
         <v>2</v>
       </c>
       <c r="G147" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H147" s="27"/>
       <c r="I147" s="27" t="s">
@@ -8502,19 +8499,19 @@
       <c r="J147" s="37"/>
     </row>
     <row r="148" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="79">
+      <c r="A148" s="70">
         <v>68</v>
       </c>
-      <c r="B148" s="71" t="s">
+      <c r="B148" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C148" s="71" t="s">
+      <c r="C148" s="72" t="s">
         <v>529</v>
       </c>
-      <c r="D148" s="71" t="s">
+      <c r="D148" s="72" t="s">
         <v>530</v>
       </c>
-      <c r="E148" s="73" t="s">
+      <c r="E148" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F148" s="24">
@@ -8524,22 +8521,22 @@
         <v>530</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="I148" s="34"/>
       <c r="J148" s="35"/>
     </row>
-    <row r="149" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="80"/>
-      <c r="B149" s="72"/>
-      <c r="C149" s="72"/>
-      <c r="D149" s="72"/>
-      <c r="E149" s="74"/>
+    <row r="149" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="71"/>
+      <c r="B149" s="73"/>
+      <c r="C149" s="73"/>
+      <c r="D149" s="73"/>
+      <c r="E149" s="107"/>
       <c r="F149" s="26">
         <v>2</v>
       </c>
       <c r="G149" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H149" s="27"/>
       <c r="I149" s="27" t="s">
@@ -8548,19 +8545,19 @@
       <c r="J149" s="37"/>
     </row>
     <row r="150" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="79">
+      <c r="A150" s="70">
         <v>69</v>
       </c>
-      <c r="B150" s="71" t="s">
+      <c r="B150" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="C150" s="71" t="s">
+      <c r="C150" s="72" t="s">
         <v>532</v>
       </c>
-      <c r="D150" s="71" t="s">
+      <c r="D150" s="72" t="s">
         <v>533</v>
       </c>
-      <c r="E150" s="73" t="s">
+      <c r="E150" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F150" s="24">
@@ -8570,22 +8567,22 @@
         <v>534</v>
       </c>
       <c r="H150" s="25" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="I150" s="34"/>
       <c r="J150" s="35"/>
     </row>
     <row r="151" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="80"/>
-      <c r="B151" s="72"/>
-      <c r="C151" s="72"/>
-      <c r="D151" s="72"/>
-      <c r="E151" s="74"/>
+      <c r="A151" s="71"/>
+      <c r="B151" s="73"/>
+      <c r="C151" s="73"/>
+      <c r="D151" s="73"/>
+      <c r="E151" s="107"/>
       <c r="F151" s="26">
         <v>2</v>
       </c>
       <c r="G151" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H151" s="27"/>
       <c r="I151" s="27" t="s">
@@ -8594,19 +8591,19 @@
       <c r="J151" s="37"/>
     </row>
     <row r="152" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="79">
+      <c r="A152" s="70">
         <v>70</v>
       </c>
-      <c r="B152" s="71" t="s">
+      <c r="B152" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C152" s="71" t="s">
+      <c r="C152" s="72" t="s">
         <v>536</v>
       </c>
-      <c r="D152" s="71" t="s">
+      <c r="D152" s="72" t="s">
         <v>537</v>
       </c>
-      <c r="E152" s="73" t="s">
+      <c r="E152" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F152" s="24">
@@ -8616,22 +8613,22 @@
         <v>537</v>
       </c>
       <c r="H152" s="25" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="I152" s="34"/>
       <c r="J152" s="35"/>
     </row>
     <row r="153" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="80"/>
-      <c r="B153" s="72"/>
-      <c r="C153" s="72"/>
-      <c r="D153" s="72"/>
-      <c r="E153" s="74"/>
+      <c r="A153" s="71"/>
+      <c r="B153" s="73"/>
+      <c r="C153" s="73"/>
+      <c r="D153" s="73"/>
+      <c r="E153" s="107"/>
       <c r="F153" s="26">
         <v>2</v>
       </c>
       <c r="G153" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H153" s="27"/>
       <c r="I153" s="27" t="s">
@@ -8640,75 +8637,75 @@
       <c r="J153" s="37"/>
     </row>
     <row r="154" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="79">
+      <c r="A154" s="70">
         <v>71</v>
       </c>
-      <c r="B154" s="71" t="s">
+      <c r="B154" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="C154" s="71" t="s">
+      <c r="C154" s="72" t="s">
         <v>539</v>
       </c>
-      <c r="D154" s="71" t="s">
+      <c r="D154" s="72" t="s">
         <v>540</v>
       </c>
-      <c r="E154" s="73" t="s">
+      <c r="E154" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F154" s="24">
         <v>1</v>
       </c>
       <c r="G154" s="25" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="H154" s="25" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="I154" s="34"/>
       <c r="J154" s="35"/>
-      <c r="K154" s="147"/>
-      <c r="L154" s="146"/>
-      <c r="M154" s="146"/>
+      <c r="K154" s="140"/>
+      <c r="L154" s="139"/>
+      <c r="M154" s="139"/>
       <c r="N154" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="155" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="80"/>
-      <c r="B155" s="72"/>
-      <c r="C155" s="72"/>
-      <c r="D155" s="72"/>
-      <c r="E155" s="74"/>
+      <c r="A155" s="71"/>
+      <c r="B155" s="73"/>
+      <c r="C155" s="73"/>
+      <c r="D155" s="73"/>
+      <c r="E155" s="107"/>
       <c r="F155" s="26">
         <v>2</v>
       </c>
       <c r="G155" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H155" s="27"/>
       <c r="I155" s="27" t="s">
         <v>541</v>
       </c>
       <c r="J155" s="37"/>
-      <c r="K155" s="147"/>
-      <c r="L155" s="146"/>
-      <c r="M155" s="146"/>
+      <c r="K155" s="140"/>
+      <c r="L155" s="139"/>
+      <c r="M155" s="139"/>
       <c r="N155" s="66"/>
     </row>
     <row r="156" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="79">
+      <c r="A156" s="70">
         <v>72</v>
       </c>
-      <c r="B156" s="71" t="s">
+      <c r="B156" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C156" s="71" t="s">
+      <c r="C156" s="72" t="s">
         <v>542</v>
       </c>
-      <c r="D156" s="71" t="s">
+      <c r="D156" s="72" t="s">
         <v>543</v>
       </c>
-      <c r="E156" s="73" t="s">
+      <c r="E156" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F156" s="24">
@@ -8718,22 +8715,22 @@
         <v>543</v>
       </c>
       <c r="H156" s="25" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="I156" s="34"/>
       <c r="J156" s="35"/>
     </row>
     <row r="157" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="80"/>
-      <c r="B157" s="72"/>
-      <c r="C157" s="72"/>
-      <c r="D157" s="72"/>
-      <c r="E157" s="74"/>
+      <c r="A157" s="71"/>
+      <c r="B157" s="73"/>
+      <c r="C157" s="73"/>
+      <c r="D157" s="73"/>
+      <c r="E157" s="107"/>
       <c r="F157" s="26">
         <v>2</v>
       </c>
       <c r="G157" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H157" s="27"/>
       <c r="I157" s="27" t="s">
@@ -8742,19 +8739,19 @@
       <c r="J157" s="37"/>
     </row>
     <row r="158" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="79">
+      <c r="A158" s="70">
         <v>73</v>
       </c>
-      <c r="B158" s="71" t="s">
+      <c r="B158" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="C158" s="71" t="s">
+      <c r="C158" s="72" t="s">
         <v>545</v>
       </c>
-      <c r="D158" s="71" t="s">
+      <c r="D158" s="72" t="s">
         <v>546</v>
       </c>
-      <c r="E158" s="73" t="s">
+      <c r="E158" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F158" s="24">
@@ -8764,53 +8761,53 @@
         <v>546</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="I158" s="34"/>
       <c r="J158" s="35"/>
-      <c r="K158" s="147"/>
-      <c r="L158" s="146"/>
-      <c r="M158" s="146"/>
+      <c r="K158" s="140"/>
+      <c r="L158" s="139"/>
+      <c r="M158" s="139"/>
       <c r="N158" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="159" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="80"/>
-      <c r="B159" s="72"/>
-      <c r="C159" s="72"/>
-      <c r="D159" s="72"/>
-      <c r="E159" s="74"/>
+      <c r="A159" s="71"/>
+      <c r="B159" s="73"/>
+      <c r="C159" s="73"/>
+      <c r="D159" s="73"/>
+      <c r="E159" s="107"/>
       <c r="F159" s="26">
         <v>2</v>
       </c>
       <c r="G159" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H159" s="27"/>
       <c r="I159" s="27" t="s">
         <v>547</v>
       </c>
       <c r="J159" s="37"/>
-      <c r="K159" s="147"/>
-      <c r="L159" s="146"/>
-      <c r="M159" s="146"/>
+      <c r="K159" s="140"/>
+      <c r="L159" s="139"/>
+      <c r="M159" s="139"/>
       <c r="N159" s="66"/>
     </row>
     <row r="160" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="79">
+      <c r="A160" s="70">
         <v>74</v>
       </c>
-      <c r="B160" s="71" t="s">
+      <c r="B160" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="C160" s="71" t="s">
+      <c r="C160" s="72" t="s">
         <v>548</v>
       </c>
-      <c r="D160" s="71" t="s">
+      <c r="D160" s="72" t="s">
         <v>549</v>
       </c>
-      <c r="E160" s="73" t="s">
+      <c r="E160" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F160" s="24">
@@ -8820,22 +8817,22 @@
         <v>411</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="I160" s="34"/>
       <c r="J160" s="35"/>
     </row>
     <row r="161" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="80"/>
-      <c r="B161" s="72"/>
-      <c r="C161" s="72"/>
-      <c r="D161" s="72"/>
-      <c r="E161" s="74"/>
+      <c r="A161" s="71"/>
+      <c r="B161" s="73"/>
+      <c r="C161" s="73"/>
+      <c r="D161" s="73"/>
+      <c r="E161" s="107"/>
       <c r="F161" s="26">
         <v>2</v>
       </c>
       <c r="G161" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H161" s="27"/>
       <c r="I161" s="27" t="s">
@@ -8844,19 +8841,19 @@
       <c r="J161" s="37"/>
     </row>
     <row r="162" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="79">
+      <c r="A162" s="70">
         <v>75</v>
       </c>
-      <c r="B162" s="71" t="s">
+      <c r="B162" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="C162" s="71" t="s">
+      <c r="C162" s="72" t="s">
         <v>551</v>
       </c>
-      <c r="D162" s="71" t="s">
+      <c r="D162" s="72" t="s">
         <v>552</v>
       </c>
-      <c r="E162" s="73" t="s">
+      <c r="E162" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F162" s="24">
@@ -8866,22 +8863,22 @@
         <v>416</v>
       </c>
       <c r="H162" s="25" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="I162" s="34"/>
       <c r="J162" s="35"/>
     </row>
     <row r="163" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="80"/>
-      <c r="B163" s="72"/>
-      <c r="C163" s="72"/>
-      <c r="D163" s="72"/>
-      <c r="E163" s="74"/>
+      <c r="A163" s="71"/>
+      <c r="B163" s="73"/>
+      <c r="C163" s="73"/>
+      <c r="D163" s="73"/>
+      <c r="E163" s="107"/>
       <c r="F163" s="26">
         <v>2</v>
       </c>
       <c r="G163" s="27" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H163" s="27"/>
       <c r="I163" s="27" t="s">
@@ -8890,19 +8887,19 @@
       <c r="J163" s="37"/>
     </row>
     <row r="164" spans="1:14" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="79">
+      <c r="A164" s="70">
         <v>76</v>
       </c>
-      <c r="B164" s="71" t="s">
+      <c r="B164" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="C164" s="71" t="s">
+      <c r="C164" s="72" t="s">
         <v>553</v>
       </c>
-      <c r="D164" s="71" t="s">
+      <c r="D164" s="72" t="s">
         <v>554</v>
       </c>
-      <c r="E164" s="73" t="s">
+      <c r="E164" s="106" t="s">
         <v>510</v>
       </c>
       <c r="F164" s="24">
@@ -8912,22 +8909,22 @@
         <v>420</v>
       </c>
       <c r="H164" s="25" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="I164" s="34"/>
       <c r="J164" s="35"/>
     </row>
     <row r="165" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="133"/>
-      <c r="B165" s="108"/>
-      <c r="C165" s="108"/>
-      <c r="D165" s="108"/>
+      <c r="B165" s="115"/>
+      <c r="C165" s="115"/>
+      <c r="D165" s="115"/>
       <c r="E165" s="138"/>
       <c r="F165" s="41">
         <v>2</v>
       </c>
       <c r="G165" s="40" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H165" s="40"/>
       <c r="I165" s="40" t="s">
@@ -8939,16 +8936,16 @@
       <c r="A166" s="132">
         <v>77</v>
       </c>
-      <c r="B166" s="85" t="s">
+      <c r="B166" s="99" t="s">
         <v>127</v>
       </c>
-      <c r="C166" s="84" t="s">
+      <c r="C166" s="98" t="s">
         <v>556</v>
       </c>
-      <c r="D166" s="84" t="s">
+      <c r="D166" s="98" t="s">
         <v>557</v>
       </c>
-      <c r="E166" s="104" t="s">
+      <c r="E166" s="111" t="s">
         <v>558</v>
       </c>
       <c r="F166" s="24">
@@ -8962,19 +8959,19 @@
       </c>
       <c r="I166" s="34"/>
       <c r="J166" s="29"/>
-      <c r="K166" s="147"/>
-      <c r="L166" s="146"/>
-      <c r="M166" s="146"/>
+      <c r="K166" s="140"/>
+      <c r="L166" s="139"/>
+      <c r="M166" s="139"/>
       <c r="N166" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="167" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="80"/>
-      <c r="B167" s="76"/>
-      <c r="C167" s="72"/>
-      <c r="D167" s="72"/>
-      <c r="E167" s="105"/>
+      <c r="A167" s="71"/>
+      <c r="B167" s="79"/>
+      <c r="C167" s="73"/>
+      <c r="D167" s="73"/>
+      <c r="E167" s="112"/>
       <c r="F167" s="26">
         <v>2</v>
       </c>
@@ -8986,25 +8983,25 @@
         <v>560</v>
       </c>
       <c r="J167" s="37"/>
-      <c r="K167" s="147"/>
-      <c r="L167" s="146"/>
-      <c r="M167" s="146"/>
+      <c r="K167" s="140"/>
+      <c r="L167" s="139"/>
+      <c r="M167" s="139"/>
       <c r="N167" s="66"/>
     </row>
     <row r="168" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="79">
+      <c r="A168" s="70">
         <v>78</v>
       </c>
-      <c r="B168" s="101" t="s">
+      <c r="B168" s="108" t="s">
         <v>142</v>
       </c>
-      <c r="C168" s="71" t="s">
+      <c r="C168" s="72" t="s">
         <v>561</v>
       </c>
-      <c r="D168" s="71" t="s">
+      <c r="D168" s="72" t="s">
         <v>562</v>
       </c>
-      <c r="E168" s="106" t="s">
+      <c r="E168" s="113" t="s">
         <v>563</v>
       </c>
       <c r="F168" s="24">
@@ -9016,19 +9013,19 @@
       <c r="H168" s="25"/>
       <c r="I168" s="34"/>
       <c r="J168" s="29"/>
-      <c r="K168" s="147"/>
-      <c r="L168" s="146"/>
-      <c r="M168" s="146"/>
+      <c r="K168" s="140"/>
+      <c r="L168" s="139"/>
+      <c r="M168" s="139"/>
       <c r="N168" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="169" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="80"/>
-      <c r="B169" s="102"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="107"/>
+      <c r="A169" s="71"/>
+      <c r="B169" s="109"/>
+      <c r="C169" s="73"/>
+      <c r="D169" s="73"/>
+      <c r="E169" s="114"/>
       <c r="F169" s="26">
         <v>2</v>
       </c>
@@ -9040,25 +9037,25 @@
         <v>566</v>
       </c>
       <c r="J169" s="37"/>
-      <c r="K169" s="147"/>
-      <c r="L169" s="146"/>
-      <c r="M169" s="146"/>
+      <c r="K169" s="140"/>
+      <c r="L169" s="139"/>
+      <c r="M169" s="139"/>
       <c r="N169" s="66"/>
     </row>
     <row r="170" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="79">
+      <c r="A170" s="70">
         <v>79</v>
       </c>
-      <c r="B170" s="101" t="s">
+      <c r="B170" s="108" t="s">
         <v>142</v>
       </c>
-      <c r="C170" s="71" t="s">
+      <c r="C170" s="72" t="s">
         <v>567</v>
       </c>
-      <c r="D170" s="71" t="s">
+      <c r="D170" s="72" t="s">
         <v>568</v>
       </c>
-      <c r="E170" s="109" t="s">
+      <c r="E170" s="104" t="s">
         <v>569</v>
       </c>
       <c r="F170" s="24">
@@ -9072,11 +9069,11 @@
       <c r="J170" s="35"/>
     </row>
     <row r="171" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="80"/>
-      <c r="B171" s="102"/>
-      <c r="C171" s="72"/>
-      <c r="D171" s="72"/>
-      <c r="E171" s="110"/>
+      <c r="A171" s="71"/>
+      <c r="B171" s="109"/>
+      <c r="C171" s="73"/>
+      <c r="D171" s="73"/>
+      <c r="E171" s="105"/>
       <c r="F171" s="26">
         <v>2</v>
       </c>
@@ -9090,16 +9087,16 @@
       <c r="J171" s="37"/>
     </row>
     <row r="172" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="79">
+      <c r="A172" s="70">
         <v>80</v>
       </c>
-      <c r="B172" s="75" t="s">
+      <c r="B172" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C172" s="71" t="s">
+      <c r="C172" s="72" t="s">
         <v>572</v>
       </c>
-      <c r="D172" s="71" t="s">
+      <c r="D172" s="72" t="s">
         <v>573</v>
       </c>
       <c r="E172" s="136" t="s">
@@ -9119,9 +9116,9 @@
     </row>
     <row r="173" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="133"/>
-      <c r="B173" s="103"/>
-      <c r="C173" s="108"/>
-      <c r="D173" s="108"/>
+      <c r="B173" s="110"/>
+      <c r="C173" s="115"/>
+      <c r="D173" s="115"/>
       <c r="E173" s="137"/>
       <c r="F173" s="41">
         <v>2</v>
@@ -9154,19 +9151,19 @@
       <c r="N174" s="100"/>
     </row>
     <row r="175" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="91">
+      <c r="A175" s="102">
         <v>81</v>
       </c>
-      <c r="B175" s="92" t="s">
+      <c r="B175" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="C175" s="99" t="s">
+      <c r="C175" s="97" t="s">
         <v>577</v>
       </c>
-      <c r="D175" s="99" t="s">
+      <c r="D175" s="97" t="s">
         <v>578</v>
       </c>
-      <c r="E175" s="99" t="s">
+      <c r="E175" s="97" t="s">
         <v>579</v>
       </c>
       <c r="F175" s="22">
@@ -9180,16 +9177,16 @@
       </c>
       <c r="I175" s="33"/>
       <c r="J175" s="23"/>
-      <c r="K175" s="180"/>
-      <c r="L175" s="179"/>
-      <c r="M175" s="179"/>
-      <c r="N175" s="178" t="s">
-        <v>837</v>
+      <c r="K175" s="155"/>
+      <c r="L175" s="154"/>
+      <c r="M175" s="154"/>
+      <c r="N175" s="101" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="176" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="83"/>
-      <c r="B176" s="94"/>
+      <c r="A176" s="84"/>
+      <c r="B176" s="96"/>
       <c r="C176" s="69"/>
       <c r="D176" s="69"/>
       <c r="E176" s="69"/>
@@ -9204,16 +9201,16 @@
         <v>583</v>
       </c>
       <c r="J176" s="35"/>
-      <c r="K176" s="147"/>
-      <c r="L176" s="146"/>
-      <c r="M176" s="146"/>
+      <c r="K176" s="140"/>
+      <c r="L176" s="139"/>
+      <c r="M176" s="139"/>
       <c r="N176" s="66"/>
     </row>
     <row r="177" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="90">
+      <c r="A177" s="89">
         <v>82</v>
       </c>
-      <c r="B177" s="114" t="s">
+      <c r="B177" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C177" s="68" t="s">
@@ -9236,16 +9233,16 @@
       </c>
       <c r="I177" s="36"/>
       <c r="J177" s="38"/>
-      <c r="K177" s="147"/>
-      <c r="L177" s="146"/>
-      <c r="M177" s="146"/>
+      <c r="K177" s="140"/>
+      <c r="L177" s="139"/>
+      <c r="M177" s="139"/>
       <c r="N177" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="178" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="83"/>
-      <c r="B178" s="94"/>
+      <c r="A178" s="84"/>
+      <c r="B178" s="96"/>
       <c r="C178" s="69"/>
       <c r="D178" s="69"/>
       <c r="E178" s="69"/>
@@ -9260,16 +9257,16 @@
         <v>590</v>
       </c>
       <c r="J178" s="35"/>
-      <c r="K178" s="147"/>
-      <c r="L178" s="146"/>
-      <c r="M178" s="146"/>
+      <c r="K178" s="140"/>
+      <c r="L178" s="139"/>
+      <c r="M178" s="139"/>
       <c r="N178" s="66"/>
     </row>
     <row r="179" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="90">
+      <c r="A179" s="89">
         <v>83</v>
       </c>
-      <c r="B179" s="114" t="s">
+      <c r="B179" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C179" s="68" t="s">
@@ -9294,8 +9291,8 @@
       <c r="J179" s="37"/>
     </row>
     <row r="180" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="83"/>
-      <c r="B180" s="94"/>
+      <c r="A180" s="84"/>
+      <c r="B180" s="96"/>
       <c r="C180" s="69"/>
       <c r="D180" s="69"/>
       <c r="E180" s="69"/>
@@ -9312,10 +9309,10 @@
       <c r="J180" s="35"/>
     </row>
     <row r="181" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="90">
+      <c r="A181" s="89">
         <v>84</v>
       </c>
-      <c r="B181" s="111" t="s">
+      <c r="B181" s="93" t="s">
         <v>148</v>
       </c>
       <c r="C181" s="68" t="s">
@@ -9338,16 +9335,16 @@
       </c>
       <c r="I181" s="36"/>
       <c r="J181" s="37"/>
-      <c r="K181" s="147"/>
-      <c r="L181" s="146"/>
-      <c r="M181" s="146"/>
+      <c r="K181" s="140"/>
+      <c r="L181" s="139"/>
+      <c r="M181" s="139"/>
       <c r="N181" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="182" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="83"/>
-      <c r="B182" s="112"/>
+      <c r="A182" s="84"/>
+      <c r="B182" s="94"/>
       <c r="C182" s="69"/>
       <c r="D182" s="69"/>
       <c r="E182" s="69"/>
@@ -9362,16 +9359,16 @@
         <v>602</v>
       </c>
       <c r="J182" s="35"/>
-      <c r="K182" s="147"/>
-      <c r="L182" s="146"/>
-      <c r="M182" s="146"/>
+      <c r="K182" s="140"/>
+      <c r="L182" s="139"/>
+      <c r="M182" s="139"/>
       <c r="N182" s="66"/>
     </row>
     <row r="183" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="90">
+      <c r="A183" s="89">
         <v>85</v>
       </c>
-      <c r="B183" s="111" t="s">
+      <c r="B183" s="93" t="s">
         <v>148</v>
       </c>
       <c r="C183" s="68" t="s">
@@ -9396,8 +9393,8 @@
       <c r="J183" s="37"/>
     </row>
     <row r="184" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="83"/>
-      <c r="B184" s="112"/>
+      <c r="A184" s="84"/>
+      <c r="B184" s="94"/>
       <c r="C184" s="69"/>
       <c r="D184" s="69"/>
       <c r="E184" s="69"/>
@@ -9414,10 +9411,10 @@
       <c r="J184" s="35"/>
     </row>
     <row r="185" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="90">
+      <c r="A185" s="89">
         <v>86</v>
       </c>
-      <c r="B185" s="111" t="s">
+      <c r="B185" s="93" t="s">
         <v>148</v>
       </c>
       <c r="C185" s="68" t="s">
@@ -9442,8 +9439,8 @@
       <c r="J185" s="37"/>
     </row>
     <row r="186" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="83"/>
-      <c r="B186" s="112"/>
+      <c r="A186" s="84"/>
+      <c r="B186" s="94"/>
       <c r="C186" s="69"/>
       <c r="D186" s="69"/>
       <c r="E186" s="69"/>
@@ -9460,10 +9457,10 @@
       <c r="J186" s="35"/>
     </row>
     <row r="187" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="90">
+      <c r="A187" s="89">
         <v>87</v>
       </c>
-      <c r="B187" s="111" t="s">
+      <c r="B187" s="93" t="s">
         <v>148</v>
       </c>
       <c r="C187" s="68" t="s">
@@ -9486,16 +9483,16 @@
       </c>
       <c r="I187" s="36"/>
       <c r="J187" s="37"/>
-      <c r="K187" s="147"/>
-      <c r="L187" s="146"/>
-      <c r="M187" s="146"/>
+      <c r="K187" s="140"/>
+      <c r="L187" s="139"/>
+      <c r="M187" s="139"/>
       <c r="N187" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="188" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="83"/>
-      <c r="B188" s="112"/>
+      <c r="A188" s="84"/>
+      <c r="B188" s="94"/>
       <c r="C188" s="69"/>
       <c r="D188" s="69"/>
       <c r="E188" s="69"/>
@@ -9510,16 +9507,16 @@
         <v>619</v>
       </c>
       <c r="J188" s="35"/>
-      <c r="K188" s="147"/>
-      <c r="L188" s="146"/>
-      <c r="M188" s="146"/>
+      <c r="K188" s="140"/>
+      <c r="L188" s="139"/>
+      <c r="M188" s="139"/>
       <c r="N188" s="66"/>
     </row>
     <row r="189" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="90">
+      <c r="A189" s="89">
         <v>88</v>
       </c>
-      <c r="B189" s="111" t="s">
+      <c r="B189" s="93" t="s">
         <v>148</v>
       </c>
       <c r="C189" s="68" t="s">
@@ -9544,8 +9541,8 @@
       <c r="J189" s="38"/>
     </row>
     <row r="190" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="83"/>
-      <c r="B190" s="112"/>
+      <c r="A190" s="84"/>
+      <c r="B190" s="94"/>
       <c r="C190" s="69"/>
       <c r="D190" s="69"/>
       <c r="E190" s="69"/>
@@ -9562,10 +9559,10 @@
       <c r="J190" s="35"/>
     </row>
     <row r="191" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="90">
+      <c r="A191" s="89">
         <v>89</v>
       </c>
-      <c r="B191" s="115" t="s">
+      <c r="B191" s="118" t="s">
         <v>151</v>
       </c>
       <c r="C191" s="68" t="s">
@@ -9588,16 +9585,16 @@
       </c>
       <c r="I191" s="36"/>
       <c r="J191" s="37"/>
-      <c r="K191" s="147"/>
-      <c r="L191" s="146"/>
-      <c r="M191" s="146"/>
+      <c r="K191" s="140"/>
+      <c r="L191" s="139"/>
+      <c r="M191" s="139"/>
       <c r="N191" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="192" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="83"/>
-      <c r="B192" s="116"/>
+      <c r="A192" s="84"/>
+      <c r="B192" s="119"/>
       <c r="C192" s="69"/>
       <c r="D192" s="69"/>
       <c r="E192" s="69"/>
@@ -9612,16 +9609,16 @@
         <v>631</v>
       </c>
       <c r="J192" s="35"/>
-      <c r="K192" s="147"/>
-      <c r="L192" s="146"/>
-      <c r="M192" s="146"/>
+      <c r="K192" s="140"/>
+      <c r="L192" s="139"/>
+      <c r="M192" s="139"/>
       <c r="N192" s="66"/>
     </row>
     <row r="193" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="90">
+      <c r="A193" s="89">
         <v>90</v>
       </c>
-      <c r="B193" s="115" t="s">
+      <c r="B193" s="118" t="s">
         <v>151</v>
       </c>
       <c r="C193" s="68" t="s">
@@ -9646,8 +9643,8 @@
       <c r="J193" s="37"/>
     </row>
     <row r="194" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="83"/>
-      <c r="B194" s="116"/>
+      <c r="A194" s="84"/>
+      <c r="B194" s="119"/>
       <c r="C194" s="69"/>
       <c r="D194" s="69"/>
       <c r="E194" s="69"/>
@@ -9664,10 +9661,10 @@
       <c r="J194" s="35"/>
     </row>
     <row r="195" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="90">
+      <c r="A195" s="89">
         <v>91</v>
       </c>
-      <c r="B195" s="115" t="s">
+      <c r="B195" s="118" t="s">
         <v>151</v>
       </c>
       <c r="C195" s="68" t="s">
@@ -9692,8 +9689,8 @@
       <c r="J195" s="37"/>
     </row>
     <row r="196" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="83"/>
-      <c r="B196" s="116"/>
+      <c r="A196" s="84"/>
+      <c r="B196" s="119"/>
       <c r="C196" s="69"/>
       <c r="D196" s="69"/>
       <c r="E196" s="69"/>
@@ -9710,10 +9707,10 @@
       <c r="J196" s="35"/>
     </row>
     <row r="197" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="90">
+      <c r="A197" s="89">
         <v>92</v>
       </c>
-      <c r="B197" s="114" t="s">
+      <c r="B197" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C197" s="68" t="s">
@@ -9736,8 +9733,8 @@
       <c r="J197" s="37"/>
     </row>
     <row r="198" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="83"/>
-      <c r="B198" s="94"/>
+      <c r="A198" s="84"/>
+      <c r="B198" s="96"/>
       <c r="C198" s="69"/>
       <c r="D198" s="69"/>
       <c r="E198" s="69"/>
@@ -9754,10 +9751,10 @@
       <c r="J198" s="35"/>
     </row>
     <row r="199" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="90">
+      <c r="A199" s="89">
         <v>93</v>
       </c>
-      <c r="B199" s="114" t="s">
+      <c r="B199" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C199" s="68" t="s">
@@ -9780,8 +9777,8 @@
       <c r="J199" s="37"/>
     </row>
     <row r="200" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="83"/>
-      <c r="B200" s="94"/>
+      <c r="A200" s="84"/>
+      <c r="B200" s="96"/>
       <c r="C200" s="69"/>
       <c r="D200" s="69"/>
       <c r="E200" s="69"/>
@@ -9798,10 +9795,10 @@
       <c r="J200" s="35"/>
     </row>
     <row r="201" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="90">
+      <c r="A201" s="89">
         <v>94</v>
       </c>
-      <c r="B201" s="114" t="s">
+      <c r="B201" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C201" s="68" t="s">
@@ -9826,8 +9823,8 @@
       <c r="J201" s="38"/>
     </row>
     <row r="202" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="83"/>
-      <c r="B202" s="94"/>
+      <c r="A202" s="84"/>
+      <c r="B202" s="96"/>
       <c r="C202" s="69"/>
       <c r="D202" s="69"/>
       <c r="E202" s="69"/>
@@ -9844,10 +9841,10 @@
       <c r="J202" s="35"/>
     </row>
     <row r="203" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="90">
+      <c r="A203" s="89">
         <v>95</v>
       </c>
-      <c r="B203" s="114" t="s">
+      <c r="B203" s="117" t="s">
         <v>145</v>
       </c>
       <c r="C203" s="68" t="s">
@@ -9872,11 +9869,11 @@
       <c r="J203" s="38"/>
     </row>
     <row r="204" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="113"/>
-      <c r="B204" s="117"/>
-      <c r="C204" s="86"/>
-      <c r="D204" s="86"/>
-      <c r="E204" s="86"/>
+      <c r="A204" s="116"/>
+      <c r="B204" s="120"/>
+      <c r="C204" s="90"/>
+      <c r="D204" s="90"/>
+      <c r="E204" s="90"/>
       <c r="F204" s="31">
         <v>2</v>
       </c>
@@ -9890,34 +9887,34 @@
       <c r="J204" s="57"/>
     </row>
     <row r="205" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="118" t="s">
+      <c r="A205" s="145" t="s">
         <v>186</v>
       </c>
-      <c r="B205" s="118"/>
-      <c r="C205" s="118"/>
-      <c r="D205" s="118"/>
-      <c r="E205" s="118"/>
-      <c r="F205" s="118"/>
-      <c r="G205" s="118"/>
-      <c r="H205" s="118"/>
-      <c r="I205" s="118"/>
-      <c r="J205" s="118"/>
-      <c r="K205" s="118"/>
-      <c r="L205" s="118"/>
-      <c r="M205" s="118"/>
-      <c r="N205" s="118"/>
+      <c r="B205" s="145"/>
+      <c r="C205" s="145"/>
+      <c r="D205" s="145"/>
+      <c r="E205" s="145"/>
+      <c r="F205" s="145"/>
+      <c r="G205" s="145"/>
+      <c r="H205" s="145"/>
+      <c r="I205" s="145"/>
+      <c r="J205" s="145"/>
+      <c r="K205" s="145"/>
+      <c r="L205" s="145"/>
+      <c r="M205" s="145"/>
+      <c r="N205" s="145"/>
     </row>
     <row r="206" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="91">
+      <c r="A206" s="102">
         <v>96</v>
       </c>
-      <c r="B206" s="92" t="s">
+      <c r="B206" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="C206" s="99" t="s">
+      <c r="C206" s="97" t="s">
         <v>663</v>
       </c>
-      <c r="D206" s="99" t="s">
+      <c r="D206" s="97" t="s">
         <v>664</v>
       </c>
       <c r="E206" s="134" t="s">
@@ -9927,23 +9924,23 @@
         <v>1</v>
       </c>
       <c r="G206" s="21" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="H206" s="21" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="I206" s="33"/>
       <c r="J206" s="23"/>
-      <c r="K206" s="147"/>
-      <c r="L206" s="146"/>
-      <c r="M206" s="146"/>
+      <c r="K206" s="140"/>
+      <c r="L206" s="139"/>
+      <c r="M206" s="139"/>
       <c r="N206" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="207" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="83"/>
-      <c r="B207" s="94"/>
+      <c r="A207" s="84"/>
+      <c r="B207" s="96"/>
       <c r="C207" s="69"/>
       <c r="D207" s="69"/>
       <c r="E207" s="135"/>
@@ -9958,16 +9955,16 @@
         <v>666</v>
       </c>
       <c r="J207" s="35"/>
-      <c r="K207" s="147"/>
-      <c r="L207" s="146"/>
-      <c r="M207" s="146"/>
+      <c r="K207" s="140"/>
+      <c r="L207" s="139"/>
+      <c r="M207" s="139"/>
       <c r="N207" s="66"/>
     </row>
     <row r="208" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="90">
+      <c r="A208" s="89">
         <v>97</v>
       </c>
-      <c r="B208" s="111" t="s">
+      <c r="B208" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C208" s="68" t="s">
@@ -9976,7 +9973,7 @@
       <c r="D208" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="E208" s="119" t="s">
+      <c r="E208" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F208" s="26">
@@ -9986,23 +9983,23 @@
         <v>670</v>
       </c>
       <c r="H208" s="27" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="I208" s="36"/>
       <c r="J208" s="38"/>
-      <c r="K208" s="147"/>
-      <c r="L208" s="146"/>
-      <c r="M208" s="146"/>
+      <c r="K208" s="140"/>
+      <c r="L208" s="139"/>
+      <c r="M208" s="139"/>
       <c r="N208" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="209" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="83"/>
-      <c r="B209" s="112"/>
+      <c r="A209" s="84"/>
+      <c r="B209" s="94"/>
       <c r="C209" s="69"/>
       <c r="D209" s="69"/>
-      <c r="E209" s="120"/>
+      <c r="E209" s="92"/>
       <c r="F209" s="24">
         <v>2</v>
       </c>
@@ -10014,16 +10011,16 @@
         <v>671</v>
       </c>
       <c r="J209" s="35"/>
-      <c r="K209" s="147"/>
-      <c r="L209" s="146"/>
-      <c r="M209" s="146"/>
+      <c r="K209" s="140"/>
+      <c r="L209" s="139"/>
+      <c r="M209" s="139"/>
       <c r="N209" s="66"/>
     </row>
     <row r="210" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="90">
+      <c r="A210" s="89">
         <v>98</v>
       </c>
-      <c r="B210" s="111" t="s">
+      <c r="B210" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C210" s="68" t="s">
@@ -10032,7 +10029,7 @@
       <c r="D210" s="68" t="s">
         <v>673</v>
       </c>
-      <c r="E210" s="119" t="s">
+      <c r="E210" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F210" s="26">
@@ -10042,17 +10039,17 @@
         <v>674</v>
       </c>
       <c r="H210" s="27" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="I210" s="36"/>
       <c r="J210" s="37"/>
     </row>
     <row r="211" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="83"/>
-      <c r="B211" s="112"/>
+      <c r="A211" s="84"/>
+      <c r="B211" s="94"/>
       <c r="C211" s="69"/>
       <c r="D211" s="69"/>
-      <c r="E211" s="120"/>
+      <c r="E211" s="92"/>
       <c r="F211" s="24">
         <v>2</v>
       </c>
@@ -10066,10 +10063,10 @@
       <c r="J211" s="35"/>
     </row>
     <row r="212" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="90">
+      <c r="A212" s="89">
         <v>99</v>
       </c>
-      <c r="B212" s="111" t="s">
+      <c r="B212" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C212" s="68" t="s">
@@ -10078,7 +10075,7 @@
       <c r="D212" s="68" t="s">
         <v>677</v>
       </c>
-      <c r="E212" s="119" t="s">
+      <c r="E212" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F212" s="26">
@@ -10088,17 +10085,17 @@
         <v>678</v>
       </c>
       <c r="H212" s="27" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="I212" s="36"/>
       <c r="J212" s="37"/>
     </row>
     <row r="213" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="83"/>
-      <c r="B213" s="112"/>
+      <c r="A213" s="84"/>
+      <c r="B213" s="94"/>
       <c r="C213" s="69"/>
       <c r="D213" s="69"/>
-      <c r="E213" s="120"/>
+      <c r="E213" s="92"/>
       <c r="F213" s="24">
         <v>2</v>
       </c>
@@ -10112,10 +10109,10 @@
       <c r="J213" s="35"/>
     </row>
     <row r="214" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="90">
+      <c r="A214" s="89">
         <v>100</v>
       </c>
-      <c r="B214" s="111" t="s">
+      <c r="B214" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C214" s="68" t="s">
@@ -10124,7 +10121,7 @@
       <c r="D214" s="68" t="s">
         <v>680</v>
       </c>
-      <c r="E214" s="119" t="s">
+      <c r="E214" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F214" s="26">
@@ -10134,17 +10131,17 @@
         <v>681</v>
       </c>
       <c r="H214" s="27" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="I214" s="36"/>
       <c r="J214" s="37"/>
     </row>
     <row r="215" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="83"/>
-      <c r="B215" s="112"/>
+      <c r="A215" s="84"/>
+      <c r="B215" s="94"/>
       <c r="C215" s="69"/>
       <c r="D215" s="69"/>
-      <c r="E215" s="120"/>
+      <c r="E215" s="92"/>
       <c r="F215" s="24">
         <v>2</v>
       </c>
@@ -10158,10 +10155,10 @@
       <c r="J215" s="35"/>
     </row>
     <row r="216" spans="1:14" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="90">
+      <c r="A216" s="89">
         <v>101</v>
       </c>
-      <c r="B216" s="111" t="s">
+      <c r="B216" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C216" s="68" t="s">
@@ -10170,7 +10167,7 @@
       <c r="D216" s="68" t="s">
         <v>683</v>
       </c>
-      <c r="E216" s="119" t="s">
+      <c r="E216" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F216" s="26">
@@ -10180,17 +10177,17 @@
         <v>684</v>
       </c>
       <c r="H216" s="27" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="I216" s="36"/>
       <c r="J216" s="37"/>
     </row>
     <row r="217" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="83"/>
-      <c r="B217" s="112"/>
+      <c r="A217" s="84"/>
+      <c r="B217" s="94"/>
       <c r="C217" s="69"/>
       <c r="D217" s="69"/>
-      <c r="E217" s="120"/>
+      <c r="E217" s="92"/>
       <c r="F217" s="24">
         <v>2</v>
       </c>
@@ -10204,10 +10201,10 @@
       <c r="J217" s="35"/>
     </row>
     <row r="218" spans="1:14" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="90">
+      <c r="A218" s="89">
         <v>102</v>
       </c>
-      <c r="B218" s="111" t="s">
+      <c r="B218" s="93" t="s">
         <v>164</v>
       </c>
       <c r="C218" s="68" t="s">
@@ -10216,7 +10213,7 @@
       <c r="D218" s="68" t="s">
         <v>686</v>
       </c>
-      <c r="E218" s="119" t="s">
+      <c r="E218" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F218" s="26">
@@ -10226,23 +10223,23 @@
         <v>687</v>
       </c>
       <c r="H218" s="27" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="I218" s="36"/>
       <c r="J218" s="37"/>
-      <c r="K218" s="147"/>
-      <c r="L218" s="146"/>
-      <c r="M218" s="146"/>
+      <c r="K218" s="140"/>
+      <c r="L218" s="139"/>
+      <c r="M218" s="139"/>
       <c r="N218" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="219" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="83"/>
-      <c r="B219" s="112"/>
+      <c r="A219" s="84"/>
+      <c r="B219" s="94"/>
       <c r="C219" s="69"/>
       <c r="D219" s="69"/>
-      <c r="E219" s="120"/>
+      <c r="E219" s="92"/>
       <c r="F219" s="24">
         <v>2</v>
       </c>
@@ -10254,16 +10251,16 @@
         <v>688</v>
       </c>
       <c r="J219" s="35"/>
-      <c r="K219" s="147"/>
-      <c r="L219" s="146"/>
-      <c r="M219" s="146"/>
+      <c r="K219" s="140"/>
+      <c r="L219" s="139"/>
+      <c r="M219" s="139"/>
       <c r="N219" s="66"/>
     </row>
     <row r="220" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="90">
+      <c r="A220" s="89">
         <v>103</v>
       </c>
-      <c r="B220" s="114" t="s">
+      <c r="B220" s="117" t="s">
         <v>161</v>
       </c>
       <c r="C220" s="68" t="s">
@@ -10272,7 +10269,7 @@
       <c r="D220" s="68" t="s">
         <v>690</v>
       </c>
-      <c r="E220" s="119" t="s">
+      <c r="E220" s="91" t="s">
         <v>669</v>
       </c>
       <c r="F220" s="26">
@@ -10286,11 +10283,11 @@
       <c r="J220" s="37"/>
     </row>
     <row r="221" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="83"/>
-      <c r="B221" s="94"/>
+      <c r="A221" s="84"/>
+      <c r="B221" s="96"/>
       <c r="C221" s="69"/>
       <c r="D221" s="69"/>
-      <c r="E221" s="120"/>
+      <c r="E221" s="92"/>
       <c r="F221" s="24">
         <v>2</v>
       </c>
@@ -10304,10 +10301,10 @@
       <c r="J221" s="35"/>
     </row>
     <row r="222" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="90">
+      <c r="A222" s="89">
         <v>104</v>
       </c>
-      <c r="B222" s="115" t="s">
+      <c r="B222" s="118" t="s">
         <v>167</v>
       </c>
       <c r="C222" s="68" t="s">
@@ -10328,11 +10325,11 @@
       <c r="H222" s="27"/>
       <c r="I222" s="36"/>
       <c r="J222" s="38"/>
-      <c r="K222" s="147"/>
-      <c r="L222" s="146"/>
-      <c r="M222" s="146"/>
+      <c r="K222" s="140"/>
+      <c r="L222" s="139"/>
+      <c r="M222" s="139"/>
       <c r="N222" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="223" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -10352,9 +10349,9 @@
         <v>698</v>
       </c>
       <c r="J223" s="35"/>
-      <c r="K223" s="147"/>
-      <c r="L223" s="146"/>
-      <c r="M223" s="146"/>
+      <c r="K223" s="140"/>
+      <c r="L223" s="139"/>
+      <c r="M223" s="139"/>
       <c r="N223" s="66"/>
     </row>
     <row r="224" spans="1:14" ht="93" thickBot="1" x14ac:dyDescent="0.35">
@@ -10380,16 +10377,16 @@
         <v>701</v>
       </c>
       <c r="H224" s="58" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="I224" s="60"/>
       <c r="J224" s="61"/>
     </row>
     <row r="225" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="113"/>
+      <c r="A225" s="116"/>
       <c r="B225" s="131"/>
-      <c r="C225" s="86"/>
-      <c r="D225" s="86"/>
+      <c r="C225" s="90"/>
+      <c r="D225" s="90"/>
       <c r="E225" s="128"/>
       <c r="F225" s="31">
         <v>2</v>
@@ -10422,41 +10419,41 @@
       <c r="N226" s="100"/>
     </row>
     <row r="227" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="91">
+      <c r="A227" s="102">
         <v>106</v>
       </c>
-      <c r="B227" s="99" t="s">
+      <c r="B227" s="97" t="s">
         <v>173</v>
       </c>
-      <c r="C227" s="99" t="s">
+      <c r="C227" s="97" t="s">
         <v>703</v>
       </c>
-      <c r="D227" s="99" t="s">
+      <c r="D227" s="97" t="s">
         <v>704</v>
       </c>
-      <c r="E227" s="99" t="s">
+      <c r="E227" s="97" t="s">
         <v>705</v>
       </c>
       <c r="F227" s="22">
         <v>1</v>
       </c>
       <c r="G227" s="21" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="H227" s="21" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="I227" s="33"/>
       <c r="J227" s="23"/>
-      <c r="K227" s="180"/>
-      <c r="L227" s="179"/>
-      <c r="M227" s="179"/>
-      <c r="N227" s="178" t="s">
-        <v>837</v>
+      <c r="K227" s="155"/>
+      <c r="L227" s="154"/>
+      <c r="M227" s="154"/>
+      <c r="N227" s="101" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="228" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="83"/>
+      <c r="A228" s="84"/>
       <c r="B228" s="69"/>
       <c r="C228" s="69"/>
       <c r="D228" s="69"/>
@@ -10465,22 +10462,22 @@
         <v>2</v>
       </c>
       <c r="G228" s="25" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="H228" s="25" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="I228" s="25" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="J228" s="35"/>
-      <c r="K228" s="147"/>
-      <c r="L228" s="146"/>
-      <c r="M228" s="146"/>
+      <c r="K228" s="140"/>
+      <c r="L228" s="139"/>
+      <c r="M228" s="139"/>
       <c r="N228" s="66"/>
     </row>
     <row r="229" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="90">
+      <c r="A229" s="89">
         <v>107</v>
       </c>
       <c r="B229" s="68" t="s">
@@ -10502,19 +10499,19 @@
         <v>709</v>
       </c>
       <c r="H229" s="27" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="I229" s="36"/>
       <c r="J229" s="38"/>
-      <c r="K229" s="147"/>
-      <c r="L229" s="146"/>
-      <c r="M229" s="146"/>
+      <c r="K229" s="140"/>
+      <c r="L229" s="139"/>
+      <c r="M229" s="139"/>
       <c r="N229" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="230" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="83"/>
+      <c r="A230" s="84"/>
       <c r="B230" s="69"/>
       <c r="C230" s="69"/>
       <c r="D230" s="69"/>
@@ -10523,22 +10520,22 @@
         <v>2</v>
       </c>
       <c r="G230" s="25" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="H230" s="25" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="I230" s="25" t="s">
         <v>710</v>
       </c>
       <c r="J230" s="35"/>
-      <c r="K230" s="147"/>
-      <c r="L230" s="146"/>
-      <c r="M230" s="146"/>
+      <c r="K230" s="140"/>
+      <c r="L230" s="139"/>
+      <c r="M230" s="139"/>
       <c r="N230" s="66"/>
     </row>
     <row r="231" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="90">
+      <c r="A231" s="89">
         <v>108</v>
       </c>
       <c r="B231" s="68" t="s">
@@ -10560,19 +10557,19 @@
         <v>714</v>
       </c>
       <c r="H231" s="27" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="I231" s="36"/>
       <c r="J231" s="37"/>
-      <c r="K231" s="147"/>
-      <c r="L231" s="146"/>
-      <c r="M231" s="146"/>
+      <c r="K231" s="140"/>
+      <c r="L231" s="139"/>
+      <c r="M231" s="139"/>
       <c r="N231" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="232" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="83"/>
+      <c r="A232" s="84"/>
       <c r="B232" s="69"/>
       <c r="C232" s="69"/>
       <c r="D232" s="69"/>
@@ -10584,19 +10581,19 @@
         <v>706</v>
       </c>
       <c r="H232" s="25" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="I232" s="25" t="s">
         <v>715</v>
       </c>
       <c r="J232" s="35"/>
-      <c r="K232" s="147"/>
-      <c r="L232" s="146"/>
-      <c r="M232" s="146"/>
+      <c r="K232" s="140"/>
+      <c r="L232" s="139"/>
+      <c r="M232" s="139"/>
       <c r="N232" s="66"/>
     </row>
     <row r="233" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="90">
+      <c r="A233" s="89">
         <v>109</v>
       </c>
       <c r="B233" s="68" t="s">
@@ -10618,17 +10615,17 @@
         <v>718</v>
       </c>
       <c r="H233" s="27" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="I233" s="36"/>
       <c r="J233" s="37"/>
     </row>
     <row r="234" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="113"/>
-      <c r="B234" s="86"/>
-      <c r="C234" s="86"/>
-      <c r="D234" s="86"/>
-      <c r="E234" s="86"/>
+      <c r="A234" s="116"/>
+      <c r="B234" s="90"/>
+      <c r="C234" s="90"/>
+      <c r="D234" s="90"/>
+      <c r="E234" s="90"/>
       <c r="F234" s="31">
         <v>2</v>
       </c>
@@ -10636,7 +10633,7 @@
         <v>706</v>
       </c>
       <c r="H234" s="32" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="I234" s="32" t="s">
         <v>719</v>
@@ -10647,16 +10644,16 @@
       <c r="A235" s="132">
         <v>110</v>
       </c>
-      <c r="B235" s="85" t="s">
+      <c r="B235" s="99" t="s">
         <v>173</v>
       </c>
-      <c r="C235" s="84" t="s">
+      <c r="C235" s="98" t="s">
         <v>720</v>
       </c>
-      <c r="D235" s="84" t="s">
+      <c r="D235" s="98" t="s">
         <v>721</v>
       </c>
-      <c r="E235" s="84" t="s">
+      <c r="E235" s="98" t="s">
         <v>713</v>
       </c>
       <c r="F235" s="24">
@@ -10672,11 +10669,11 @@
       <c r="J235" s="35"/>
     </row>
     <row r="236" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="80"/>
-      <c r="B236" s="76"/>
-      <c r="C236" s="72"/>
-      <c r="D236" s="72"/>
-      <c r="E236" s="72"/>
+      <c r="A236" s="71"/>
+      <c r="B236" s="79"/>
+      <c r="C236" s="73"/>
+      <c r="D236" s="73"/>
+      <c r="E236" s="73"/>
       <c r="F236" s="26">
         <v>2</v>
       </c>
@@ -10690,19 +10687,19 @@
       <c r="J236" s="37"/>
     </row>
     <row r="237" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="79">
+      <c r="A237" s="70">
         <v>111</v>
       </c>
-      <c r="B237" s="75" t="s">
+      <c r="B237" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C237" s="71" t="s">
+      <c r="C237" s="72" t="s">
         <v>724</v>
       </c>
-      <c r="D237" s="71" t="s">
+      <c r="D237" s="72" t="s">
         <v>725</v>
       </c>
-      <c r="E237" s="71" t="s">
+      <c r="E237" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F237" s="24">
@@ -10718,11 +10715,11 @@
       <c r="J237" s="35"/>
     </row>
     <row r="238" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="80"/>
-      <c r="B238" s="76"/>
-      <c r="C238" s="72"/>
-      <c r="D238" s="72"/>
-      <c r="E238" s="72"/>
+      <c r="A238" s="71"/>
+      <c r="B238" s="79"/>
+      <c r="C238" s="73"/>
+      <c r="D238" s="73"/>
+      <c r="E238" s="73"/>
       <c r="F238" s="26">
         <v>2</v>
       </c>
@@ -10736,19 +10733,19 @@
       <c r="J238" s="37"/>
     </row>
     <row r="239" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="79">
+      <c r="A239" s="70">
         <v>112</v>
       </c>
-      <c r="B239" s="75" t="s">
+      <c r="B239" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C239" s="71" t="s">
+      <c r="C239" s="72" t="s">
         <v>728</v>
       </c>
-      <c r="D239" s="71" t="s">
+      <c r="D239" s="72" t="s">
         <v>729</v>
       </c>
-      <c r="E239" s="71" t="s">
+      <c r="E239" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F239" s="24">
@@ -10764,11 +10761,11 @@
       <c r="J239" s="35"/>
     </row>
     <row r="240" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="80"/>
-      <c r="B240" s="76"/>
-      <c r="C240" s="72"/>
-      <c r="D240" s="72"/>
-      <c r="E240" s="72"/>
+      <c r="A240" s="71"/>
+      <c r="B240" s="79"/>
+      <c r="C240" s="73"/>
+      <c r="D240" s="73"/>
+      <c r="E240" s="73"/>
       <c r="F240" s="26">
         <v>2</v>
       </c>
@@ -10782,19 +10779,19 @@
       <c r="J240" s="37"/>
     </row>
     <row r="241" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="79">
+      <c r="A241" s="70">
         <v>113</v>
       </c>
-      <c r="B241" s="75" t="s">
+      <c r="B241" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C241" s="71" t="s">
+      <c r="C241" s="72" t="s">
         <v>733</v>
       </c>
-      <c r="D241" s="71" t="s">
+      <c r="D241" s="72" t="s">
         <v>734</v>
       </c>
-      <c r="E241" s="71" t="s">
+      <c r="E241" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F241" s="24">
@@ -10810,11 +10807,11 @@
       <c r="J241" s="35"/>
     </row>
     <row r="242" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="80"/>
-      <c r="B242" s="76"/>
-      <c r="C242" s="72"/>
-      <c r="D242" s="72"/>
-      <c r="E242" s="72"/>
+      <c r="A242" s="71"/>
+      <c r="B242" s="79"/>
+      <c r="C242" s="73"/>
+      <c r="D242" s="73"/>
+      <c r="E242" s="73"/>
       <c r="F242" s="26">
         <v>2</v>
       </c>
@@ -10828,19 +10825,19 @@
       <c r="J242" s="37"/>
     </row>
     <row r="243" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="79">
+      <c r="A243" s="70">
         <v>114</v>
       </c>
-      <c r="B243" s="75" t="s">
+      <c r="B243" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C243" s="71" t="s">
+      <c r="C243" s="72" t="s">
         <v>738</v>
       </c>
-      <c r="D243" s="71" t="s">
+      <c r="D243" s="72" t="s">
         <v>739</v>
       </c>
-      <c r="E243" s="71" t="s">
+      <c r="E243" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F243" s="24">
@@ -10854,19 +10851,19 @@
       </c>
       <c r="I243" s="34"/>
       <c r="J243" s="29"/>
-      <c r="K243" s="147"/>
-      <c r="L243" s="146"/>
-      <c r="M243" s="146"/>
+      <c r="K243" s="140"/>
+      <c r="L243" s="139"/>
+      <c r="M243" s="139"/>
       <c r="N243" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="244" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="80"/>
-      <c r="B244" s="76"/>
-      <c r="C244" s="72"/>
-      <c r="D244" s="72"/>
-      <c r="E244" s="72"/>
+      <c r="A244" s="71"/>
+      <c r="B244" s="79"/>
+      <c r="C244" s="73"/>
+      <c r="D244" s="73"/>
+      <c r="E244" s="73"/>
       <c r="F244" s="26">
         <v>2</v>
       </c>
@@ -10878,25 +10875,25 @@
         <v>742</v>
       </c>
       <c r="J244" s="37"/>
-      <c r="K244" s="147"/>
-      <c r="L244" s="146"/>
-      <c r="M244" s="146"/>
+      <c r="K244" s="140"/>
+      <c r="L244" s="139"/>
+      <c r="M244" s="139"/>
       <c r="N244" s="66"/>
     </row>
     <row r="245" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="79">
+      <c r="A245" s="70">
         <v>115</v>
       </c>
-      <c r="B245" s="77" t="s">
+      <c r="B245" s="74" t="s">
         <v>179</v>
       </c>
-      <c r="C245" s="71" t="s">
+      <c r="C245" s="72" t="s">
         <v>743</v>
       </c>
-      <c r="D245" s="71" t="s">
+      <c r="D245" s="72" t="s">
         <v>744</v>
       </c>
-      <c r="E245" s="71" t="s">
+      <c r="E245" s="72" t="s">
         <v>745</v>
       </c>
       <c r="F245" s="24">
@@ -10910,11 +10907,11 @@
       <c r="J245" s="35"/>
     </row>
     <row r="246" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="80"/>
-      <c r="B246" s="78"/>
-      <c r="C246" s="72"/>
-      <c r="D246" s="72"/>
-      <c r="E246" s="72"/>
+      <c r="A246" s="71"/>
+      <c r="B246" s="75"/>
+      <c r="C246" s="73"/>
+      <c r="D246" s="73"/>
+      <c r="E246" s="73"/>
       <c r="F246" s="26">
         <v>2</v>
       </c>
@@ -10928,19 +10925,19 @@
       <c r="J246" s="37"/>
     </row>
     <row r="247" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="79">
+      <c r="A247" s="70">
         <v>116</v>
       </c>
-      <c r="B247" s="77" t="s">
+      <c r="B247" s="74" t="s">
         <v>179</v>
       </c>
-      <c r="C247" s="71" t="s">
+      <c r="C247" s="72" t="s">
         <v>749</v>
       </c>
-      <c r="D247" s="71" t="s">
+      <c r="D247" s="72" t="s">
         <v>750</v>
       </c>
-      <c r="E247" s="71" t="s">
+      <c r="E247" s="72" t="s">
         <v>405</v>
       </c>
       <c r="F247" s="24">
@@ -10954,19 +10951,19 @@
       </c>
       <c r="I247" s="34"/>
       <c r="J247" s="35"/>
-      <c r="K247" s="147"/>
-      <c r="L247" s="146"/>
-      <c r="M247" s="146"/>
+      <c r="K247" s="140"/>
+      <c r="L247" s="139"/>
+      <c r="M247" s="139"/>
       <c r="N247" s="66" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="248" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="80"/>
-      <c r="B248" s="78"/>
-      <c r="C248" s="72"/>
-      <c r="D248" s="72"/>
-      <c r="E248" s="72"/>
+      <c r="A248" s="71"/>
+      <c r="B248" s="75"/>
+      <c r="C248" s="73"/>
+      <c r="D248" s="73"/>
+      <c r="E248" s="73"/>
       <c r="F248" s="26">
         <v>2</v>
       </c>
@@ -10978,25 +10975,25 @@
         <v>753</v>
       </c>
       <c r="J248" s="37"/>
-      <c r="K248" s="147"/>
-      <c r="L248" s="146"/>
-      <c r="M248" s="146"/>
+      <c r="K248" s="140"/>
+      <c r="L248" s="139"/>
+      <c r="M248" s="139"/>
       <c r="N248" s="66"/>
     </row>
     <row r="249" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="79">
+      <c r="A249" s="70">
         <v>117</v>
       </c>
-      <c r="B249" s="75" t="s">
+      <c r="B249" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C249" s="71" t="s">
+      <c r="C249" s="72" t="s">
         <v>754</v>
       </c>
-      <c r="D249" s="71" t="s">
+      <c r="D249" s="72" t="s">
         <v>755</v>
       </c>
-      <c r="E249" s="71" t="s">
+      <c r="E249" s="72" t="s">
         <v>756</v>
       </c>
       <c r="F249" s="24">
@@ -11010,11 +11007,11 @@
       <c r="J249" s="29"/>
     </row>
     <row r="250" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="80"/>
-      <c r="B250" s="76"/>
-      <c r="C250" s="72"/>
-      <c r="D250" s="72"/>
-      <c r="E250" s="72"/>
+      <c r="A250" s="71"/>
+      <c r="B250" s="79"/>
+      <c r="C250" s="73"/>
+      <c r="D250" s="73"/>
+      <c r="E250" s="73"/>
       <c r="F250" s="26">
         <v>2</v>
       </c>
@@ -11028,19 +11025,19 @@
       <c r="J250" s="37"/>
     </row>
     <row r="251" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="79">
+      <c r="A251" s="70">
         <v>118</v>
       </c>
-      <c r="B251" s="73" t="s">
+      <c r="B251" s="106" t="s">
         <v>176</v>
       </c>
-      <c r="C251" s="71" t="s">
+      <c r="C251" s="72" t="s">
         <v>759</v>
       </c>
-      <c r="D251" s="71" t="s">
+      <c r="D251" s="72" t="s">
         <v>760</v>
       </c>
-      <c r="E251" s="71" t="s">
+      <c r="E251" s="72" t="s">
         <v>761</v>
       </c>
       <c r="F251" s="24">
@@ -11054,11 +11051,11 @@
       <c r="J251" s="35"/>
     </row>
     <row r="252" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="80"/>
-      <c r="B252" s="74"/>
-      <c r="C252" s="72"/>
-      <c r="D252" s="72"/>
-      <c r="E252" s="72"/>
+      <c r="A252" s="71"/>
+      <c r="B252" s="107"/>
+      <c r="C252" s="73"/>
+      <c r="D252" s="73"/>
+      <c r="E252" s="73"/>
       <c r="F252" s="26">
         <v>2</v>
       </c>
@@ -11072,19 +11069,19 @@
       <c r="J252" s="37"/>
     </row>
     <row r="253" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="79">
+      <c r="A253" s="70">
         <v>119</v>
       </c>
-      <c r="B253" s="75" t="s">
+      <c r="B253" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C253" s="71" t="s">
+      <c r="C253" s="72" t="s">
         <v>765</v>
       </c>
-      <c r="D253" s="71" t="s">
+      <c r="D253" s="72" t="s">
         <v>766</v>
       </c>
-      <c r="E253" s="71" t="s">
+      <c r="E253" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F253" s="24">
@@ -11100,11 +11097,11 @@
       <c r="J253" s="35"/>
     </row>
     <row r="254" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="80"/>
-      <c r="B254" s="76"/>
-      <c r="C254" s="72"/>
-      <c r="D254" s="72"/>
-      <c r="E254" s="72"/>
+      <c r="A254" s="71"/>
+      <c r="B254" s="79"/>
+      <c r="C254" s="73"/>
+      <c r="D254" s="73"/>
+      <c r="E254" s="73"/>
       <c r="F254" s="26">
         <v>2</v>
       </c>
@@ -11118,19 +11115,19 @@
       <c r="J254" s="37"/>
     </row>
     <row r="255" spans="1:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="79">
+      <c r="A255" s="70">
         <v>120</v>
       </c>
-      <c r="B255" s="75" t="s">
+      <c r="B255" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="C255" s="71" t="s">
+      <c r="C255" s="72" t="s">
         <v>770</v>
       </c>
-      <c r="D255" s="71" t="s">
+      <c r="D255" s="72" t="s">
         <v>771</v>
       </c>
-      <c r="E255" s="71" t="s">
+      <c r="E255" s="72" t="s">
         <v>713</v>
       </c>
       <c r="F255" s="24">
@@ -11145,10 +11142,10 @@
     </row>
     <row r="256" spans="1:14" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="133"/>
-      <c r="B256" s="103"/>
-      <c r="C256" s="108"/>
-      <c r="D256" s="108"/>
-      <c r="E256" s="108"/>
+      <c r="B256" s="110"/>
+      <c r="C256" s="115"/>
+      <c r="D256" s="115"/>
+      <c r="E256" s="115"/>
       <c r="F256" s="41">
         <v>2</v>
       </c>
@@ -11325,6 +11322,7 @@
     <mergeCell ref="M34:M35"/>
     <mergeCell ref="L34:L35"/>
     <mergeCell ref="K34:K35"/>
+    <mergeCell ref="E56:E57"/>
     <mergeCell ref="K32:K33"/>
     <mergeCell ref="K30:K31"/>
     <mergeCell ref="L30:L31"/>
@@ -11334,6 +11332,21 @@
     <mergeCell ref="E103:E104"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E39:E40"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="E53:E54"/>
@@ -11358,11 +11371,6 @@
     <mergeCell ref="N34:N35"/>
     <mergeCell ref="N36:N37"/>
     <mergeCell ref="N39:N40"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="E18:E19"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="N18:N20"/>
     <mergeCell ref="N21:N23"/>
@@ -11372,6 +11380,11 @@
     <mergeCell ref="L18:L20"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="M24:M25"/>
     <mergeCell ref="M26:M27"/>
     <mergeCell ref="M39:M40"/>
@@ -11420,16 +11433,6 @@
     <mergeCell ref="C127:C128"/>
     <mergeCell ref="D127:D128"/>
     <mergeCell ref="A119:A120"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="E144:E145"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="C74:C77"/>
     <mergeCell ref="D146:D147"/>
     <mergeCell ref="C146:C147"/>
     <mergeCell ref="D74:D77"/>
@@ -11446,16 +11449,6 @@
     <mergeCell ref="E127:E128"/>
     <mergeCell ref="E101:E102"/>
     <mergeCell ref="D101:D102"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="E105:E106"/>
-    <mergeCell ref="E152:E153"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A150:A151"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="E150:E151"/>
     <mergeCell ref="B67:B68"/>
@@ -11472,10 +11465,14 @@
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A74:A77"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="E172:E173"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="E144:E145"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="C74:C77"/>
     <mergeCell ref="E164:E165"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="D164:D165"/>
@@ -11496,7 +11493,10 @@
     <mergeCell ref="C62:C63"/>
     <mergeCell ref="D162:D163"/>
     <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="E105:E106"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="D152:D153"/>
     <mergeCell ref="D160:D161"/>
     <mergeCell ref="E62:E63"/>
     <mergeCell ref="C160:C161"/>
@@ -11518,13 +11518,9 @@
     <mergeCell ref="C140:C141"/>
     <mergeCell ref="D113:D114"/>
     <mergeCell ref="E113:E114"/>
-    <mergeCell ref="B156:B157"/>
     <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C177:C178"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="C156:C157"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A166:A167"/>
     <mergeCell ref="B53:B54"/>
@@ -11543,7 +11539,20 @@
     <mergeCell ref="A158:A159"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="E210:E211"/>
+    <mergeCell ref="E206:E207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="E212:E213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A206:A207"/>
     <mergeCell ref="A193:A194"/>
     <mergeCell ref="D193:D194"/>
     <mergeCell ref="E193:E194"/>
@@ -11553,32 +11562,6 @@
     <mergeCell ref="E199:E200"/>
     <mergeCell ref="D199:D200"/>
     <mergeCell ref="C199:C200"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="E210:E211"/>
-    <mergeCell ref="E206:E207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="E212:E213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="B255:B256"/>
-    <mergeCell ref="C255:C256"/>
-    <mergeCell ref="D255:D256"/>
-    <mergeCell ref="B245:B246"/>
-    <mergeCell ref="B243:B244"/>
-    <mergeCell ref="C243:C244"/>
-    <mergeCell ref="D243:D244"/>
-    <mergeCell ref="B251:B252"/>
     <mergeCell ref="A255:A256"/>
     <mergeCell ref="A253:A254"/>
     <mergeCell ref="A251:A252"/>
@@ -11588,14 +11571,6 @@
     <mergeCell ref="A243:A244"/>
     <mergeCell ref="A241:A242"/>
     <mergeCell ref="A239:A240"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D32:D33"/>
@@ -11603,8 +11578,23 @@
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B179:B180"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="C18:C19"/>
@@ -11614,6 +11604,13 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E18:E19"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B32:B33"/>
@@ -11638,6 +11635,9 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="E216:E217"/>
     <mergeCell ref="E255:E256"/>
     <mergeCell ref="E253:E254"/>
     <mergeCell ref="D253:D254"/>
@@ -11649,7 +11649,18 @@
     <mergeCell ref="D251:D252"/>
     <mergeCell ref="C251:C252"/>
     <mergeCell ref="C249:C250"/>
+    <mergeCell ref="B255:B256"/>
+    <mergeCell ref="C255:C256"/>
+    <mergeCell ref="D255:D256"/>
+    <mergeCell ref="B245:B246"/>
+    <mergeCell ref="B243:B244"/>
+    <mergeCell ref="C243:C244"/>
+    <mergeCell ref="D243:D244"/>
+    <mergeCell ref="B251:B252"/>
     <mergeCell ref="C247:C248"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
     <mergeCell ref="D247:D248"/>
     <mergeCell ref="E247:E248"/>
     <mergeCell ref="E245:E246"/>
@@ -11671,9 +11682,10 @@
     <mergeCell ref="C229:C230"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="B216:B217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="E216:E217"/>
+    <mergeCell ref="D197:D198"/>
+    <mergeCell ref="C193:C194"/>
+    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="B193:B194"/>
     <mergeCell ref="E214:E215"/>
     <mergeCell ref="D214:D215"/>
     <mergeCell ref="C214:C215"/>
@@ -11694,8 +11706,6 @@
     <mergeCell ref="B224:B225"/>
     <mergeCell ref="C220:C221"/>
     <mergeCell ref="D220:D221"/>
-    <mergeCell ref="E177:E178"/>
-    <mergeCell ref="D177:D178"/>
     <mergeCell ref="A203:A204"/>
     <mergeCell ref="A201:A202"/>
     <mergeCell ref="B201:B202"/>
@@ -11714,14 +11724,6 @@
     <mergeCell ref="B195:B196"/>
     <mergeCell ref="B197:B198"/>
     <mergeCell ref="C197:C198"/>
-    <mergeCell ref="D197:D198"/>
-    <mergeCell ref="C193:C194"/>
-    <mergeCell ref="C195:C196"/>
-    <mergeCell ref="B193:B194"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A185:A186"/>
     <mergeCell ref="A187:A188"/>
     <mergeCell ref="B187:B188"/>
     <mergeCell ref="C187:C188"/>
@@ -11732,16 +11734,21 @@
     <mergeCell ref="B185:B186"/>
     <mergeCell ref="B181:B182"/>
     <mergeCell ref="C181:C182"/>
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="E175:E176"/>
-    <mergeCell ref="D175:D176"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B172:B173"/>
     <mergeCell ref="C166:C167"/>
     <mergeCell ref="D166:D167"/>
     <mergeCell ref="E166:E167"/>
     <mergeCell ref="E168:E169"/>
     <mergeCell ref="C172:C173"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="E177:E178"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="E172:E173"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="E170:E171"/>
     <mergeCell ref="D170:D171"/>
@@ -11757,6 +11764,15 @@
     <mergeCell ref="A133:A135"/>
     <mergeCell ref="A136:A137"/>
     <mergeCell ref="A138:A139"/>
+    <mergeCell ref="E148:E149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="E175:E176"/>
+    <mergeCell ref="D175:D176"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="B172:B173"/>
     <mergeCell ref="E125:E126"/>
     <mergeCell ref="A125:A126"/>
     <mergeCell ref="B125:B126"/>
@@ -11778,6 +11794,21 @@
     <mergeCell ref="C115:C116"/>
     <mergeCell ref="B115:B116"/>
     <mergeCell ref="A115:A116"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="E95:E96"/>
     <mergeCell ref="B111:B112"/>
     <mergeCell ref="C111:C112"/>
     <mergeCell ref="A107:A108"/>
@@ -11787,22 +11818,6 @@
     <mergeCell ref="E107:E108"/>
     <mergeCell ref="E111:E112"/>
     <mergeCell ref="D111:D112"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="E56:E57"/>
     <mergeCell ref="D64:D65"/>
     <mergeCell ref="A78:A81"/>
     <mergeCell ref="A95:A96"/>
@@ -11847,13 +11862,8 @@
     <mergeCell ref="D208:D209"/>
     <mergeCell ref="C208:C209"/>
     <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A206:A207"/>
     <mergeCell ref="B206:B207"/>
     <mergeCell ref="C206:C207"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="E185:E186"/>
     <mergeCell ref="E183:E184"/>
@@ -11878,21 +11888,6 @@
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
     <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E148:E149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="B121:B122"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="C69:C70"/>
     <mergeCell ref="D69:D70"/>
@@ -11902,6 +11897,8 @@
     <mergeCell ref="C103:C104"/>
     <mergeCell ref="B105:B106"/>
     <mergeCell ref="B103:B104"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="E99:E100"/>
     <mergeCell ref="N62:N63"/>
     <mergeCell ref="N60:N61"/>
     <mergeCell ref="N64:N65"/>
@@ -11949,86 +11946,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="153" t="s">
+      <c r="B2" s="158"/>
+      <c r="C2" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="161"/>
       <c r="F2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="159" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="156"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="162"/>
     </row>
     <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="167"/>
       <c r="F3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="159"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="162"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="168"/>
     </row>
     <row r="4" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="164"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="167"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="173"/>
       <c r="F4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-      <c r="J4" s="169"/>
+      <c r="H4" s="172"/>
+      <c r="I4" s="172"/>
+      <c r="J4" s="175"/>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="170" t="s">
+      <c r="A7" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="170"/>
+      <c r="B7" s="176"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -12063,32 +12060,32 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="171" t="s">
+      <c r="A9" s="177" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="172"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
-      <c r="I9" s="172"/>
-      <c r="J9" s="173"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="178"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="178"/>
+      <c r="G9" s="178"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="179"/>
     </row>
     <row r="10" spans="1:12" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="176" t="s">
+      <c r="A10" s="182" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="177"/>
-      <c r="C10" s="177"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="177"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="177"/>
-      <c r="H10" s="177"/>
-      <c r="I10" s="177"/>
-      <c r="J10" s="177"/>
+      <c r="B10" s="183"/>
+      <c r="C10" s="183"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="183"/>
+      <c r="F10" s="183"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="183"/>
+      <c r="J10" s="183"/>
     </row>
     <row r="11" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
@@ -12232,18 +12229,18 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="174" t="s">
+      <c r="A16" s="180" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="175"/>
-      <c r="C16" s="175"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="175"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="175"/>
+      <c r="B16" s="181"/>
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="181"/>
+      <c r="H16" s="181"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="181"/>
     </row>
     <row r="17" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
@@ -12385,18 +12382,18 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="174" t="s">
+      <c r="A22" s="180" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="175"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="175"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="175"/>
-      <c r="I22" s="175"/>
-      <c r="J22" s="175"/>
+      <c r="B22" s="181"/>
+      <c r="C22" s="181"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="181"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="181"/>
     </row>
     <row r="23" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
@@ -12511,18 +12508,18 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="174" t="s">
+      <c r="A27" s="180" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="175"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="175"/>
-      <c r="I27" s="175"/>
-      <c r="J27" s="175"/>
+      <c r="B27" s="181"/>
+      <c r="C27" s="181"/>
+      <c r="D27" s="181"/>
+      <c r="E27" s="181"/>
+      <c r="F27" s="181"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="181"/>
     </row>
     <row r="28" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
@@ -12637,18 +12634,18 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="174" t="s">
+      <c r="A32" s="180" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="175"/>
-      <c r="C32" s="175"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="175"/>
-      <c r="F32" s="175"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="175"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
+      <c r="B32" s="181"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="181"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
     </row>
     <row r="33" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -12790,18 +12787,18 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="174" t="s">
+      <c r="A38" s="180" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="175"/>
-      <c r="C38" s="175"/>
-      <c r="D38" s="175"/>
-      <c r="E38" s="175"/>
-      <c r="F38" s="175"/>
-      <c r="G38" s="175"/>
-      <c r="H38" s="175"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
+      <c r="B38" s="181"/>
+      <c r="C38" s="181"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="181"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="181"/>
+      <c r="J38" s="181"/>
     </row>
     <row r="39" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20">
@@ -12970,18 +12967,18 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="174" t="s">
+      <c r="A45" s="180" t="s">
         <v>185</v>
       </c>
-      <c r="B45" s="175"/>
-      <c r="C45" s="175"/>
-      <c r="D45" s="175"/>
-      <c r="E45" s="175"/>
-      <c r="F45" s="175"/>
-      <c r="G45" s="175"/>
-      <c r="H45" s="175"/>
-      <c r="I45" s="175"/>
-      <c r="J45" s="175"/>
+      <c r="B45" s="181"/>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="181"/>
+      <c r="F45" s="181"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="181"/>
     </row>
     <row r="46" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="20">
@@ -13096,18 +13093,18 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="174" t="s">
+      <c r="A50" s="180" t="s">
         <v>186</v>
       </c>
-      <c r="B50" s="175"/>
-      <c r="C50" s="175"/>
-      <c r="D50" s="175"/>
-      <c r="E50" s="175"/>
-      <c r="F50" s="175"/>
-      <c r="G50" s="175"/>
-      <c r="H50" s="175"/>
-      <c r="I50" s="175"/>
-      <c r="J50" s="175"/>
+      <c r="B50" s="181"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
+      <c r="F50" s="181"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="181"/>
     </row>
     <row r="51" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="20">
@@ -13222,18 +13219,18 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="180" t="s">
         <v>187</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
-      <c r="H55" s="175"/>
-      <c r="I55" s="175"/>
-      <c r="J55" s="175"/>
+      <c r="B55" s="181"/>
+      <c r="C55" s="181"/>
+      <c r="D55" s="181"/>
+      <c r="E55" s="181"/>
+      <c r="F55" s="181"/>
+      <c r="G55" s="181"/>
+      <c r="H55" s="181"/>
+      <c r="I55" s="181"/>
+      <c r="J55" s="181"/>
     </row>
     <row r="56" spans="1:11" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20">

--- a/TestData/Testcase.xlsx
+++ b/TestData/Testcase.xlsx
@@ -62,7 +62,7 @@
             <color indexed="81"/>
             <sz val="10"/>
           </rPr>
-          <t>_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
+          <t>_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
         </r>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
             <color indexed="81"/>
             <sz val="10"/>
           </rPr>
-          <t xml:space="preserve"> Những TCs phải được thực thi trong bất kỳ tình huống nào_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
+          <t xml:space="preserve"> Những TCs phải được thực thi trong bất kỳ tình huống nào_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
         </r>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
             <color indexed="81"/>
             <sz val="10"/>
           </rPr>
-          <t xml:space="preserve"> Những TCs có thể được thực thi nếu thời gian cho phép._x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
+          <t xml:space="preserve"> Những TCs có thể được thực thi nếu thời gian cho phép._x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_</t>
         </r>
         <r>
           <rPr>
@@ -142,7 +142,7 @@
             <color indexed="81"/>
             <sz val="9"/>
           </rPr>
-          <t>_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_Number of test cases to validate the specific test requirement</t>
+          <t>_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x000A_Number of test cases to validate the specific test requirement</t>
         </r>
       </text>
     </comment>
@@ -1025,7 +1025,7 @@
   </si>
   <si>
     <t xml:space="preserve">Transfer Complete!_x000D_
-$100.00 has been transferred from account #13677 to account #13899._x000D_
+$100.00 has been transferred from account #13899 to account #14121._x000D_
 See Account Activity for more details.</t>
   </si>
   <si>
